--- a/2026/O HIGGINS 1157/Julio/Julio ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Julio/Julio ohiggins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516457F1-C033-4553-874E-B4F4AC97BA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE81B44F-9D31-4085-9BAE-4361071264F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$119</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="215">
   <si>
     <t>TOTAL</t>
   </si>
@@ -473,9 +478,6 @@
   </si>
   <si>
     <t>Plan de Pago ARCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustavo Padron -  Sr. Contador </t>
   </si>
   <si>
     <t>Nancy Llano</t>
@@ -564,39 +566,15 @@
     <t>Myryam Martinez Del Valle</t>
   </si>
   <si>
-    <t>Romanatti Carlos - Certificacion de copias digitales</t>
-  </si>
-  <si>
-    <t>Transf 19/06</t>
-  </si>
-  <si>
-    <t>Transf 02/06</t>
-  </si>
-  <si>
     <t>Abono de 2 meses</t>
   </si>
   <si>
-    <t>Debito 12/06</t>
-  </si>
-  <si>
-    <t>Cuota 15/24</t>
-  </si>
-  <si>
-    <t>Debito 16/06</t>
-  </si>
-  <si>
-    <t>Debito 30/06</t>
-  </si>
-  <si>
     <t>Haberes + SAC</t>
   </si>
   <si>
     <t>Abono ascensor - ADS - No enviaron la factura</t>
   </si>
   <si>
-    <t>Se adeuda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gastos bancarios </t>
   </si>
   <si>
@@ -612,19 +590,7 @@
     <t>Brisa Agüero</t>
   </si>
   <si>
-    <t xml:space="preserve">Transferencia ya identificada mes anterior </t>
-  </si>
-  <si>
     <t>Punitorios mal cobrados</t>
-  </si>
-  <si>
-    <t>Deposito 29/06</t>
-  </si>
-  <si>
-    <t>Ingreso correspondiente a finalizacion de P. Fijo 05/06</t>
-  </si>
-  <si>
-    <t>Egreso a FCI super ahorro plus inversion - 19/06</t>
   </si>
   <si>
     <t>FCI Super ahorro plus</t>
@@ -658,9 +624,6 @@
     <t>PERÍODO: JULIO</t>
   </si>
   <si>
-    <t>Honorarios administracion - Se adeuda Mitad de JUNIO Y JULIO</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -695,6 +658,36 @@
   </si>
   <si>
     <t>Transf 22/07</t>
+  </si>
+  <si>
+    <t>Debito 13/07</t>
+  </si>
+  <si>
+    <t>Gustavo Padron -  Sr. Contador - Se adeuda Mayo y Junio</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adeuda Mitad de MAYO Y JULIO (ENTERO)</t>
+  </si>
+  <si>
+    <t>Transf 15/07</t>
+  </si>
+  <si>
+    <t>Cuota 16/24</t>
+  </si>
+  <si>
+    <t>Debito 16/07</t>
+  </si>
+  <si>
+    <t>Transf 27/07</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Conectado de trifasica en gabinete porta NH - Traslado de medidor trifasico - Extraccion de cableado intero - Extraccion de tablero trifasico interior</t>
+  </si>
+  <si>
+    <t>Rescate 27/07</t>
+  </si>
+  <si>
+    <t>Rescate FCI</t>
   </si>
 </sst>
 </file>
@@ -711,7 +704,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -867,6 +860,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -955,18 +955,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1463,12 +1463,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1671,12 +1680,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="12" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1716,16 +1719,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1760,9 +1759,6 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="15" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="13" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1780,195 +1776,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1976,6 +1787,207 @@
     </xf>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="12" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="16" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="16" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="16" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="16" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="16" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2060,9 +2072,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2100,9 +2112,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2135,9 +2147,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2170,9 +2199,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2346,32 +2392,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M120"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M118"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="212" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="210"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="213"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>45</v>
@@ -2380,16 +2426,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="211" t="s">
+      <c r="B3" s="216" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
-      <c r="E3" s="212"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="217"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2400,12 +2446,12 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2413,9 +2459,9 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2424,62 +2470,62 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="213" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" s="213"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="213"/>
-      <c r="C9" s="213"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="213"/>
-      <c r="C10" s="213"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="218"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="218"/>
+      <c r="C9" s="218"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="214" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="219" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="214"/>
-      <c r="C13" s="214"/>
-      <c r="D13" s="214"/>
-      <c r="E13" s="214"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="214"/>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="214"/>
-      <c r="B15" s="214"/>
-      <c r="C15" s="214"/>
-      <c r="D15" s="214"/>
-      <c r="E15" s="214"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="214"/>
-      <c r="B16" s="214"/>
-      <c r="C16" s="214"/>
-      <c r="D16" s="214"/>
-      <c r="E16" s="214"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="219"/>
+      <c r="C13" s="219"/>
+      <c r="D13" s="219"/>
+      <c r="E13" s="219"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="219"/>
+      <c r="B14" s="219"/>
+      <c r="C14" s="219"/>
+      <c r="D14" s="219"/>
+      <c r="E14" s="219"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="219"/>
+      <c r="B15" s="219"/>
+      <c r="C15" s="219"/>
+      <c r="D15" s="219"/>
+      <c r="E15" s="219"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="219"/>
+      <c r="B16" s="219"/>
+      <c r="C16" s="219"/>
+      <c r="D16" s="219"/>
+      <c r="E16" s="219"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>7</v>
       </c>
@@ -2488,7 +2534,7 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
@@ -2497,50 +2543,50 @@
       <c r="D21" s="81"/>
       <c r="E21" s="97"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="215" t="s">
-        <v>183</v>
-      </c>
-      <c r="B22" s="216"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="220" t="s">
+        <v>175</v>
+      </c>
+      <c r="B22" s="221"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="134">
+      <c r="D22" s="197">
         <v>1987270.86</v>
       </c>
       <c r="E22" s="98"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="205" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="214" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="206"/>
-      <c r="C23" s="154"/>
-      <c r="D23" s="134">
+      <c r="B23" s="215"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="197">
         <v>-432231.42</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="38"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="205" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="214" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="206"/>
-      <c r="C24" s="154"/>
-      <c r="D24" s="135">
+      <c r="B24" s="215"/>
+      <c r="C24" s="152"/>
+      <c r="D24" s="198">
         <v>0.34</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="38"/>
       <c r="H24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="155" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="155"/>
-      <c r="C25" s="155"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
       <c r="D25" s="22"/>
       <c r="E25" s="99">
         <f>SUM(D22:D24)</f>
@@ -2548,46 +2594,46 @@
       </c>
       <c r="F25" s="38"/>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="155" t="s">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="153" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="155"/>
-      <c r="C26" s="155"/>
+      <c r="B26" s="153"/>
+      <c r="C26" s="153"/>
       <c r="D26" s="22"/>
       <c r="E26" s="100"/>
       <c r="F26" s="38"/>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="154"/>
-      <c r="B27" s="154"/>
-      <c r="C27" s="154"/>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="152"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="152"/>
       <c r="D27" s="28"/>
       <c r="E27" s="111"/>
       <c r="F27" s="38"/>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="154"/>
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="152"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="152"/>
       <c r="D28" s="28"/>
       <c r="E28" s="111"/>
       <c r="F28" s="38"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="154"/>
-      <c r="B29" s="154"/>
-      <c r="C29" s="154"/>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="152"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="152"/>
       <c r="D29" s="28"/>
       <c r="E29" s="111"/>
       <c r="F29" s="38"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="155" t="s">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="156"/>
-      <c r="C30" s="156"/>
+      <c r="B30" s="154"/>
+      <c r="C30" s="154"/>
       <c r="D30" s="71"/>
       <c r="E30" s="102">
         <f>SUM(D27:D29)</f>
@@ -2595,100 +2641,100 @@
       </c>
       <c r="F30" s="38"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="155"/>
-      <c r="C31" s="155"/>
+      <c r="B31" s="153"/>
+      <c r="C31" s="153"/>
       <c r="D31" s="22"/>
       <c r="E31" s="100"/>
       <c r="F31" s="38"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="154" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="152" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="157"/>
-      <c r="C32" s="157"/>
-      <c r="D32" s="263">
+      <c r="B32" s="155"/>
+      <c r="C32" s="155"/>
+      <c r="D32" s="193">
         <v>977145.51</v>
       </c>
       <c r="E32" s="101" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="154" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="152" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="154" t="s">
-        <v>180</v>
-      </c>
-      <c r="C33" s="157"/>
-      <c r="D33" s="28">
+      <c r="B33" s="152" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="155"/>
+      <c r="D33" s="193">
         <v>182823.01</v>
       </c>
       <c r="E33" s="101" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="154" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="157"/>
-      <c r="C34" s="157"/>
-      <c r="D34" s="263">
+      <c r="B34" s="155"/>
+      <c r="C34" s="155"/>
+      <c r="D34" s="193">
         <v>89427.19</v>
       </c>
       <c r="E34" s="101" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="154" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="152" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="157"/>
-      <c r="C35" s="157"/>
-      <c r="D35" s="263">
+      <c r="B35" s="155"/>
+      <c r="C35" s="155"/>
+      <c r="D35" s="193">
         <v>9936.35</v>
       </c>
       <c r="E35" s="101" t="str">
         <f>E34</f>
-        <v>Debito 12/06</v>
+        <v>Debito 13/07</v>
       </c>
       <c r="F35" s="38"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="154" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="157"/>
-      <c r="C36" s="157"/>
-      <c r="D36" s="263">
+      <c r="B36" s="155"/>
+      <c r="C36" s="155"/>
+      <c r="D36" s="193">
         <v>160769.26</v>
       </c>
       <c r="E36" s="101" t="str">
         <f>E34</f>
-        <v>Debito 12/06</v>
+        <v>Debito 13/07</v>
       </c>
       <c r="F36" s="38"/>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="155" t="s">
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="155"/>
-      <c r="C37" s="155"/>
+      <c r="B37" s="153"/>
+      <c r="C37" s="153"/>
       <c r="D37" s="22"/>
       <c r="E37" s="32">
         <f>SUM(D32:D36)</f>
@@ -2696,23 +2742,23 @@
       </c>
       <c r="F37" s="38"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="155"/>
-      <c r="C38" s="155"/>
+      <c r="B38" s="153"/>
+      <c r="C38" s="153"/>
       <c r="D38" s="23"/>
       <c r="E38" s="102"/>
       <c r="F38" s="38"/>
     </row>
-    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="217" t="s">
+    <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="222" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="218"/>
-      <c r="C39" s="158"/>
-      <c r="D39" s="159">
+      <c r="B39" s="223"/>
+      <c r="C39" s="156"/>
+      <c r="D39" s="196">
         <v>205033.71</v>
       </c>
       <c r="E39" s="21" t="s">
@@ -2720,14 +2766,15 @@
       </c>
       <c r="F39" s="38"/>
     </row>
-    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="217" t="s">
+    <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="222" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="218"/>
-      <c r="C40" s="158"/>
-      <c r="D40" s="159">
-        <v>12020</v>
+      <c r="B40" s="223"/>
+      <c r="C40" s="156"/>
+      <c r="D40" s="196">
+        <f>1285.32+12020</f>
+        <v>13305.32</v>
       </c>
       <c r="E40" s="21" t="str">
         <f>E39</f>
@@ -2735,115 +2782,115 @@
       </c>
       <c r="F40" s="38"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="155" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="153" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="155"/>
-      <c r="C41" s="155"/>
+      <c r="B41" s="153"/>
+      <c r="C41" s="153"/>
       <c r="D41" s="22"/>
       <c r="E41" s="32">
         <f>SUM(D39:D40)</f>
-        <v>217053.71</v>
+        <v>218339.03</v>
       </c>
       <c r="F41" s="38"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="156"/>
-      <c r="C42" s="156"/>
+      <c r="B42" s="154"/>
+      <c r="C42" s="154"/>
       <c r="D42" s="25"/>
       <c r="E42" s="103"/>
       <c r="F42" s="38"/>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
         <v>145</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="262">
+      <c r="D43" s="192">
         <v>1705199.42</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="F43" s="38"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="160"/>
+      <c r="B44" s="157"/>
       <c r="C44" s="33"/>
-      <c r="D44" s="262">
+      <c r="D44" s="192">
         <v>7098.03</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F44" s="38"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="217" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="222" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="218"/>
+      <c r="B45" s="223"/>
       <c r="C45" s="33"/>
-      <c r="D45" s="262">
-        <v>511264.75</v>
+      <c r="D45" s="192">
+        <v>517937.8</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F45" s="38"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="161" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="158" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="162" t="s">
-        <v>178</v>
+      <c r="B46" s="159" t="s">
+        <v>174</v>
       </c>
       <c r="C46" s="33"/>
-      <c r="D46" s="262">
+      <c r="D46" s="192">
         <v>33772.550000000003</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F46" s="38"/>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="155" t="s">
+    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="B47" s="155"/>
-      <c r="C47" s="155"/>
+      <c r="B47" s="153"/>
+      <c r="C47" s="153"/>
       <c r="D47" s="26"/>
       <c r="E47" s="104">
         <f>SUM(D43:D46)</f>
-        <v>2257334.75</v>
+        <v>2264007.7999999998</v>
       </c>
       <c r="F47" s="38"/>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="155"/>
-      <c r="C48" s="155"/>
+      <c r="B48" s="153"/>
+      <c r="C48" s="153"/>
       <c r="D48" s="22"/>
       <c r="E48" s="105"/>
       <c r="F48" s="38"/>
     </row>
-    <row r="49" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="205" t="s">
-        <v>184</v>
-      </c>
-      <c r="B49" s="206"/>
+    <row r="49" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="214" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" s="215"/>
       <c r="C49" s="33"/>
       <c r="D49" s="133">
         <v>0</v>
@@ -2851,106 +2898,106 @@
       <c r="E49" s="27"/>
       <c r="F49" s="38"/>
     </row>
-    <row r="50" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="163" t="s">
-        <v>175</v>
-      </c>
-      <c r="B50" s="164"/>
-      <c r="C50" s="154"/>
-      <c r="D50" s="133">
-        <v>332362.82</v>
+    <row r="50" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="226" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" s="227"/>
+      <c r="C50" s="152"/>
+      <c r="D50" s="192">
+        <v>290000</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="F50" s="136"/>
-    </row>
-    <row r="51" spans="1:6" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="217" t="s">
-        <v>212</v>
-      </c>
-      <c r="B51" s="218"/>
-      <c r="C51" s="154"/>
-      <c r="D51" s="262">
+        <v>211</v>
+      </c>
+      <c r="F50" s="134"/>
+    </row>
+    <row r="51" spans="1:6" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="222" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="223"/>
+      <c r="C51" s="152"/>
+      <c r="D51" s="192">
         <v>110000</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F51" s="136"/>
-    </row>
-    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="219" t="s">
-        <v>210</v>
-      </c>
-      <c r="B52" s="220"/>
-      <c r="C52" s="154"/>
-      <c r="D52" s="262">
+        <v>195</v>
+      </c>
+      <c r="F51" s="134"/>
+    </row>
+    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="224" t="s">
+        <v>196</v>
+      </c>
+      <c r="B52" s="225"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="192">
         <v>95000</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F52" s="136"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="219" t="s">
-        <v>211</v>
-      </c>
-      <c r="B53" s="220"/>
-      <c r="C53" s="154"/>
-      <c r="D53" s="262">
+        <v>195</v>
+      </c>
+      <c r="F52" s="134"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="224" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" s="225"/>
+      <c r="C53" s="152"/>
+      <c r="D53" s="192">
         <v>35000</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F53" s="38"/>
-    </row>
-    <row r="54" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="161" t="s">
-        <v>217</v>
-      </c>
-      <c r="B54" s="196"/>
-      <c r="C54" s="154"/>
-      <c r="D54" s="262">
+        <v>195</v>
+      </c>
+      <c r="F53" s="134"/>
+    </row>
+    <row r="54" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="222" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="223"/>
+      <c r="C54" s="152"/>
+      <c r="D54" s="192">
         <v>390000</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="F54" s="38"/>
     </row>
-    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="205" t="s">
-        <v>215</v>
-      </c>
-      <c r="B55" s="206"/>
-      <c r="C55" s="154"/>
-      <c r="D55" s="262">
+    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="214" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="215"/>
+      <c r="C55" s="152"/>
+      <c r="D55" s="192">
         <v>100000</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F55" s="38"/>
     </row>
-    <row r="56" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="165" t="s">
+    <row r="56" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="161" t="s">
+        <v>194</v>
+      </c>
+      <c r="B56" s="160"/>
+      <c r="C56" s="152"/>
+      <c r="D56" s="192">
+        <v>261000</v>
+      </c>
+      <c r="E56" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="B56" s="164"/>
-      <c r="C56" s="154"/>
-      <c r="D56" s="262">
-        <v>261000</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="F56" s="136"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="155" t="s">
+      <c r="F56" s="134"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="153" t="s">
         <v>0</v>
       </c>
       <c r="B57" s="29"/>
@@ -2958,11 +3005,11 @@
       <c r="D57" s="29"/>
       <c r="E57" s="32">
         <f>SUM(D49:D56)</f>
-        <v>1323362.82</v>
+        <v>1281000</v>
       </c>
       <c r="F57" s="38"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
         <v>13</v>
       </c>
@@ -2972,38 +3019,36 @@
       <c r="E58" s="97"/>
       <c r="F58" s="38"/>
     </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="205" t="s">
-        <v>206</v>
-      </c>
-      <c r="B59" s="206"/>
-      <c r="C59" s="154"/>
-      <c r="D59" s="264">
+    <row r="59" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="214" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" s="215"/>
+      <c r="C59" s="152"/>
+      <c r="D59" s="194">
         <v>420000</v>
       </c>
       <c r="E59" s="98"/>
       <c r="F59" s="38"/>
     </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="165" t="s">
-        <v>148</v>
-      </c>
-      <c r="B60" s="164" t="s">
-        <v>185</v>
-      </c>
-      <c r="C60" s="154"/>
-      <c r="D60" s="265">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="161" t="s">
+        <v>206</v>
+      </c>
+      <c r="B60" s="160"/>
+      <c r="C60" s="152"/>
+      <c r="D60" s="195">
         <v>50000</v>
       </c>
       <c r="E60" s="98"/>
       <c r="F60" s="38"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="155" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="155"/>
-      <c r="C61" s="155"/>
+      <c r="B61" s="153"/>
+      <c r="C61" s="153"/>
       <c r="D61" s="22"/>
       <c r="E61" s="99">
         <f>SUM(D59:D60)</f>
@@ -3011,46 +3056,46 @@
       </c>
       <c r="F61" s="38"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B62" s="166"/>
-      <c r="C62" s="155"/>
+      <c r="B62" s="162"/>
+      <c r="C62" s="153"/>
       <c r="D62" s="30"/>
       <c r="E62" s="32"/>
       <c r="F62" s="38"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="167"/>
-      <c r="C63" s="167"/>
-      <c r="D63" s="168">
+      <c r="B63" s="163"/>
+      <c r="C63" s="163"/>
+      <c r="D63" s="164">
         <v>69000</v>
       </c>
       <c r="E63" s="106"/>
       <c r="F63" s="38"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="B64" s="167"/>
-      <c r="C64" s="167"/>
-      <c r="D64" s="168">
+        <v>177</v>
+      </c>
+      <c r="B64" s="163"/>
+      <c r="C64" s="163"/>
+      <c r="D64" s="164">
         <v>109681.94</v>
       </c>
       <c r="E64" s="106"/>
       <c r="F64" s="38"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="169" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="169"/>
-      <c r="C65" s="169"/>
+      <c r="B65" s="165"/>
+      <c r="C65" s="165"/>
       <c r="D65" s="31"/>
       <c r="E65" s="32">
         <f>SUM(D63:D64)</f>
@@ -3058,7 +3103,7 @@
       </c>
       <c r="F65" s="38"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="33"/>
       <c r="B66" s="33"/>
       <c r="C66" s="33"/>
@@ -3066,39 +3111,39 @@
       <c r="E66" s="34"/>
       <c r="F66" s="38"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="170" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="170"/>
-      <c r="C67" s="170"/>
+      <c r="B67" s="166"/>
+      <c r="C67" s="166"/>
       <c r="D67" s="35"/>
       <c r="E67" s="36"/>
       <c r="F67" s="38"/>
     </row>
-    <row r="68" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="171"/>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="167"/>
       <c r="B68" s="38"/>
       <c r="C68" s="38"/>
       <c r="D68" s="38"/>
       <c r="E68" s="39"/>
-      <c r="F68" s="136"/>
-    </row>
-    <row r="69" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="172" t="s">
+      <c r="F68" s="134"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="B69" s="173"/>
+      <c r="B69" s="169"/>
       <c r="C69" s="41"/>
       <c r="D69" s="41"/>
       <c r="E69" s="42">
         <f>(SUM(E21:E67))</f>
-        <v>7421574.3200000012</v>
-      </c>
-      <c r="F69" s="174"/>
+        <v>7387169.8700000001</v>
+      </c>
+      <c r="F69" s="170"/>
       <c r="G69" s="40"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="38"/>
       <c r="B70" s="38"/>
       <c r="C70" s="38"/>
@@ -3106,7 +3151,7 @@
       <c r="E70" s="38"/>
       <c r="F70" s="38"/>
     </row>
-    <row r="71" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="38"/>
       <c r="B71" s="38"/>
       <c r="C71" s="38"/>
@@ -3115,25 +3160,25 @@
       <c r="F71" s="38"/>
       <c r="H71" s="44"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="175" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="B72" s="176"/>
-      <c r="C72" s="177"/>
+      <c r="B72" s="172"/>
+      <c r="C72" s="173"/>
       <c r="D72" s="45"/>
       <c r="E72" s="46"/>
       <c r="F72" s="38"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="207"/>
-      <c r="B73" s="208"/>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="229"/>
+      <c r="B73" s="227"/>
       <c r="C73" s="33"/>
-      <c r="D73" s="178"/>
+      <c r="D73" s="174"/>
       <c r="E73" s="120"/>
       <c r="F73" s="38"/>
     </row>
-    <row r="74" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="38"/>
       <c r="B74" s="38"/>
       <c r="C74" s="38"/>
@@ -3141,20 +3186,20 @@
       <c r="E74" s="33"/>
       <c r="F74" s="38"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="179"/>
-      <c r="B75" s="180"/>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="175"/>
+      <c r="B75" s="176"/>
       <c r="C75" s="33"/>
       <c r="D75" s="28"/>
       <c r="E75" s="47"/>
       <c r="F75" s="38"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="181" t="s">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="177" t="s">
         <v>44</v>
       </c>
-      <c r="B76" s="182"/>
-      <c r="C76" s="182"/>
+      <c r="B76" s="178"/>
+      <c r="C76" s="178"/>
       <c r="D76" s="80"/>
       <c r="E76" s="107">
         <f>SUM(D73:D75)</f>
@@ -3162,7 +3207,7 @@
       </c>
       <c r="F76" s="38"/>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="38"/>
       <c r="B77" s="38"/>
       <c r="C77" s="38"/>
@@ -3170,19 +3215,19 @@
       <c r="E77" s="38"/>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="170" t="s">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B78" s="170"/>
-      <c r="C78" s="170"/>
+      <c r="B78" s="166"/>
+      <c r="C78" s="166"/>
       <c r="D78" s="35"/>
       <c r="E78" s="110">
         <v>0</v>
       </c>
       <c r="F78" s="38"/>
     </row>
-    <row r="79" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="38"/>
       <c r="B79" s="38"/>
       <c r="C79" s="38"/>
@@ -3190,11 +3235,11 @@
       <c r="E79" s="38"/>
       <c r="F79" s="38"/>
     </row>
-    <row r="80" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="172" t="s">
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="B80" s="173"/>
+      <c r="B80" s="169"/>
       <c r="C80" s="41"/>
       <c r="D80" s="41"/>
       <c r="E80" s="42">
@@ -3203,7 +3248,7 @@
       </c>
       <c r="F80" s="38"/>
     </row>
-    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="38"/>
       <c r="B81" s="38"/>
       <c r="C81" s="38"/>
@@ -3211,37 +3256,37 @@
       <c r="E81" s="38"/>
       <c r="F81" s="38"/>
     </row>
-    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="183" t="s">
+    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="184">
+      <c r="B82" s="180">
         <f>E69</f>
-        <v>7421574.3200000012</v>
+        <v>7387169.8700000001</v>
       </c>
       <c r="C82" s="38"/>
       <c r="D82" s="38"/>
       <c r="E82" s="38"/>
       <c r="F82" s="38"/>
     </row>
-    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="183" t="s">
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="179" t="s">
         <v>21</v>
       </c>
-      <c r="B83" s="184">
+      <c r="B83" s="180">
         <f>E69-E67</f>
-        <v>7421574.3200000012</v>
+        <v>7387169.8700000001</v>
       </c>
       <c r="C83" s="38"/>
       <c r="D83" s="38"/>
       <c r="E83" s="38"/>
       <c r="F83" s="38"/>
     </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="183" t="s">
+    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="179" t="s">
         <v>22</v>
       </c>
-      <c r="B84" s="184">
+      <c r="B84" s="180">
         <f>E80-E78</f>
         <v>0</v>
       </c>
@@ -3250,11 +3295,11 @@
       <c r="E84" s="38"/>
       <c r="F84" s="38"/>
     </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="183" t="s">
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="179" t="s">
         <v>23</v>
       </c>
-      <c r="B85" s="184">
+      <c r="B85" s="180">
         <f>E80</f>
         <v>0</v>
       </c>
@@ -3263,7 +3308,7 @@
       <c r="E85" s="38"/>
       <c r="F85" s="38"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="38"/>
       <c r="B86" s="38"/>
       <c r="C86" s="38"/>
@@ -3271,7 +3316,7 @@
       <c r="E86" s="38"/>
       <c r="F86" s="38"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="38"/>
       <c r="B87" s="38"/>
       <c r="C87" s="38"/>
@@ -3279,11 +3324,11 @@
       <c r="E87" s="38"/>
       <c r="F87" s="38"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="185" t="s">
-        <v>196</v>
-      </c>
-      <c r="B88" s="186">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="112" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" s="181">
         <v>0</v>
       </c>
       <c r="C88" s="38"/>
@@ -3291,11 +3336,11 @@
       <c r="E88" s="38"/>
       <c r="F88" s="38"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="158" t="s">
-        <v>197</v>
-      </c>
-      <c r="B89" s="187">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="156" t="s">
+        <v>184</v>
+      </c>
+      <c r="B89" s="182">
         <v>6500000</v>
       </c>
       <c r="C89" s="38"/>
@@ -3303,19 +3348,23 @@
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="158"/>
-      <c r="B90" s="137"/>
+    <row r="90" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="156" t="s">
+        <v>213</v>
+      </c>
+      <c r="B90" s="135">
+        <v>-1501954.93</v>
+      </c>
       <c r="C90" s="38"/>
       <c r="D90" s="38"/>
       <c r="E90" s="38"/>
       <c r="F90" s="38"/>
     </row>
-    <row r="91" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="188" t="s">
-        <v>188</v>
-      </c>
-      <c r="B91" s="189">
+    <row r="91" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="183" t="s">
+        <v>179</v>
+      </c>
+      <c r="B91" s="184">
         <f>B89</f>
         <v>6500000</v>
       </c>
@@ -3324,27 +3373,27 @@
       <c r="E91" s="38"/>
       <c r="F91" s="38"/>
     </row>
-    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="190"/>
-      <c r="B92" s="191"/>
+    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="185"/>
+      <c r="B92" s="186"/>
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
       <c r="F92" s="38"/>
     </row>
-    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="190"/>
-      <c r="B93" s="191"/>
+    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="185"/>
+      <c r="B93" s="186"/>
       <c r="C93" s="38"/>
       <c r="D93" s="38"/>
       <c r="E93" s="38"/>
       <c r="F93" s="38"/>
     </row>
-    <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="185" t="s">
-        <v>161</v>
-      </c>
-      <c r="B94" s="186">
+    <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="112" t="s">
+        <v>160</v>
+      </c>
+      <c r="B94" s="51">
         <v>231400</v>
       </c>
       <c r="C94" s="38"/>
@@ -3352,11 +3401,11 @@
       <c r="E94" s="38"/>
       <c r="F94" s="38"/>
     </row>
-    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="158" t="s">
-        <v>162</v>
-      </c>
-      <c r="B95" s="187">
+    <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B95" s="182">
         <v>0</v>
       </c>
       <c r="C95" s="38"/>
@@ -3364,21 +3413,21 @@
       <c r="E95" s="38"/>
       <c r="F95" s="38"/>
     </row>
-    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="158" t="s">
-        <v>163</v>
-      </c>
-      <c r="B96" s="137"/>
+    <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="156" t="s">
+        <v>162</v>
+      </c>
+      <c r="B96" s="135"/>
       <c r="C96" s="38"/>
       <c r="D96" s="38"/>
       <c r="E96" s="38"/>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="188" t="s">
-        <v>188</v>
-      </c>
-      <c r="B97" s="189">
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="183" t="s">
+        <v>179</v>
+      </c>
+      <c r="B97" s="184">
         <f>SUM(B94:B96)</f>
         <v>231400</v>
       </c>
@@ -3387,19 +3436,19 @@
       <c r="E97" s="38"/>
       <c r="F97" s="38"/>
     </row>
-    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="190"/>
-      <c r="B98" s="191"/>
+    <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="185"/>
+      <c r="B98" s="186"/>
       <c r="C98" s="38"/>
       <c r="D98" s="38"/>
       <c r="E98" s="38"/>
       <c r="F98" s="38"/>
     </row>
-    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="185" t="s">
-        <v>164</v>
-      </c>
-      <c r="B99" s="186">
+    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="112" t="s">
+        <v>163</v>
+      </c>
+      <c r="B99" s="51">
         <v>64328</v>
       </c>
       <c r="C99" s="38"/>
@@ -3407,11 +3456,11 @@
       <c r="E99" s="38"/>
       <c r="F99" s="38"/>
     </row>
-    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="158" t="s">
-        <v>162</v>
-      </c>
-      <c r="B100" s="187">
+    <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B100" s="182">
         <v>0</v>
       </c>
       <c r="C100" s="38"/>
@@ -3419,41 +3468,41 @@
       <c r="E100" s="38"/>
       <c r="F100" s="38"/>
     </row>
-    <row r="101" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="158" t="s">
-        <v>198</v>
-      </c>
-      <c r="B101" s="137">
-        <v>-5910</v>
+    <row r="101" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="156" t="s">
+        <v>185</v>
+      </c>
+      <c r="B101" s="135">
+        <v>0</v>
       </c>
       <c r="C101" s="38"/>
       <c r="D101" s="38"/>
       <c r="E101" s="38"/>
       <c r="F101" s="38"/>
     </row>
-    <row r="102" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="188" t="s">
-        <v>188</v>
-      </c>
-      <c r="B102" s="189">
+    <row r="102" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="183" t="s">
+        <v>179</v>
+      </c>
+      <c r="B102" s="184">
         <f>SUM(B99:B101)</f>
-        <v>58418</v>
+        <v>64328</v>
       </c>
       <c r="C102" s="38"/>
       <c r="D102" s="38"/>
       <c r="E102" s="38"/>
       <c r="F102" s="38"/>
     </row>
-    <row r="103" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="B103" s="48"/>
       <c r="C103" s="49"/>
       <c r="D103" s="108"/>
       <c r="E103" s="108"/>
     </row>
-    <row r="104" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="112" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B104" s="51">
         <v>3986543.73</v>
@@ -3462,150 +3511,123 @@
       <c r="D104" s="109"/>
       <c r="E104" s="109"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B105" s="138">
+      <c r="B105" s="136">
         <f>-B83-B84</f>
-        <v>-7421574.3200000012</v>
+        <v>-7387169.8700000001</v>
       </c>
       <c r="D105" s="38"/>
       <c r="E105" s="38"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="24" t="s">
         <v>24</v>
       </c>
       <c r="B106" s="52">
-        <f>B119</f>
-        <v>160000</v>
+        <f>B117</f>
+        <v>0</v>
       </c>
       <c r="D106" s="38"/>
       <c r="E106" s="38"/>
       <c r="F106" s="48"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B107" s="53">
         <f>PRORRATEO!G61</f>
-        <v>6991775.4199999999</v>
+        <v>5479535.0300000003</v>
       </c>
       <c r="D107" s="38"/>
       <c r="E107" s="38"/>
       <c r="F107" s="48"/>
     </row>
-    <row r="108" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B108" s="96">
-        <v>-6500000</v>
+        <v>0</v>
       </c>
       <c r="D108" s="38"/>
       <c r="E108" s="38"/>
       <c r="F108" s="48"/>
     </row>
-    <row r="109" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="B109" s="137">
-        <v>2026301.37</v>
-      </c>
-      <c r="D109" s="38"/>
+        <v>214</v>
+      </c>
+      <c r="B109" s="135">
+        <f>-B90</f>
+        <v>1501954.93</v>
+      </c>
+      <c r="D109" s="134"/>
       <c r="E109" s="38"/>
       <c r="F109" s="48"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="B110" s="96">
-        <v>-4703</v>
-      </c>
-      <c r="D110" s="38"/>
-      <c r="E110" s="38"/>
-      <c r="F110" s="48"/>
-    </row>
-    <row r="111" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="B111" s="96">
-        <v>-156782</v>
-      </c>
-      <c r="D111" s="136"/>
-      <c r="E111" s="38"/>
-      <c r="F111" s="48"/>
-    </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="54" t="s">
+    <row r="110" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="B112" s="55">
-        <f>SUM(B104:C111)</f>
-        <v>-918438.80000000121</v>
-      </c>
-      <c r="D112" s="48"/>
+      <c r="B110" s="55">
+        <f>SUM(B104:C109)</f>
+        <v>3580863.8200000003</v>
+      </c>
+      <c r="D110" s="48"/>
+      <c r="E110" s="40"/>
+      <c r="F110" s="40"/>
+    </row>
+    <row r="111" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="137" t="s">
+        <v>164</v>
+      </c>
+      <c r="B112" s="138">
+        <f>B110+B97</f>
+        <v>3812263.8200000003</v>
+      </c>
+      <c r="D112" s="40"/>
       <c r="E112" s="40"/>
-      <c r="F112" s="40"/>
-    </row>
-    <row r="113" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="114" spans="1:13" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="139" t="s">
-        <v>165</v>
-      </c>
-      <c r="B114" s="140">
-        <f>B112+B97</f>
-        <v>-687038.80000000121</v>
-      </c>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
-    </row>
-    <row r="115" spans="1:13" ht="21.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="204" t="s">
+    </row>
+    <row r="113" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="228" t="s">
         <v>25</v>
       </c>
-      <c r="B116" s="204"/>
-      <c r="C116" s="204"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="204"/>
-      <c r="B117" s="204"/>
-      <c r="C117" s="204"/>
-    </row>
-    <row r="118" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="56" t="s">
-        <v>193</v>
-      </c>
-      <c r="B118" s="79">
-        <v>160000</v>
-      </c>
-      <c r="C118" s="57"/>
-      <c r="D118" s="43"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B119" s="59">
-        <f>SUM(B118:B118)</f>
-        <v>160000</v>
-      </c>
-      <c r="C119" s="60"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M120" s="61"/>
+      <c r="B114" s="228"/>
+      <c r="C114" s="228"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="228"/>
+      <c r="B115" s="228"/>
+      <c r="C115" s="228"/>
+    </row>
+    <row r="116" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="56"/>
+      <c r="B116" s="79"/>
+      <c r="C116" s="57"/>
+      <c r="D116" s="43"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B117" s="59">
+        <f>SUM(B116:B116)</f>
+        <v>0</v>
+      </c>
+      <c r="C117" s="60"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M118" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A116:C117"/>
+  <mergeCells count="20">
+    <mergeCell ref="A114:C115"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A55:B55"/>
@@ -3621,6 +3643,10 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3631,28 +3657,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" customWidth="1"/>
-    <col min="17" max="17" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="8.5703125" customWidth="1"/>
     <col min="18" max="18" width="19" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="66"/>
       <c r="B1" s="127"/>
       <c r="C1" s="67"/>
@@ -3662,50 +3688,50 @@
       <c r="G1" s="127"/>
       <c r="H1" s="127"/>
       <c r="I1" s="127"/>
-      <c r="J1" s="221" t="str">
+      <c r="J1" s="256" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
-      <c r="M1" s="221"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="221"/>
-      <c r="P1" s="222"/>
-    </row>
-    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="256"/>
+      <c r="L1" s="256"/>
+      <c r="M1" s="256"/>
+      <c r="N1" s="256"/>
+      <c r="O1" s="256"/>
+      <c r="P1" s="257"/>
+    </row>
+    <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B2" s="128"/>
-      <c r="C2" s="142">
+      <c r="C2" s="140">
         <f>6219841.65-C5</f>
         <v>4906689.78</v>
       </c>
       <c r="D2" s="68"/>
       <c r="E2" s="68"/>
-      <c r="F2" s="231"/>
-      <c r="G2" s="231"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
-      <c r="M2" s="223"/>
-      <c r="N2" s="223"/>
-      <c r="O2" s="223"/>
-      <c r="P2" s="224"/>
+      <c r="J2" s="258"/>
+      <c r="K2" s="258"/>
+      <c r="L2" s="258"/>
+      <c r="M2" s="258"/>
+      <c r="N2" s="258"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
       <c r="Q2" s="62"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="128"/>
-      <c r="C3" s="142">
+      <c r="C3" s="140">
         <v>0</v>
       </c>
       <c r="D3" s="68"/>
@@ -3714,22 +3740,22 @@
       <c r="G3" s="132"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="223"/>
-      <c r="K3" s="223"/>
-      <c r="L3" s="223"/>
-      <c r="M3" s="223"/>
-      <c r="N3" s="223"/>
-      <c r="O3" s="223"/>
-      <c r="P3" s="224"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="258"/>
+      <c r="L3" s="258"/>
+      <c r="M3" s="258"/>
+      <c r="N3" s="258"/>
+      <c r="O3" s="258"/>
+      <c r="P3" s="259"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4" s="128"/>
-      <c r="C4" s="142">
+      <c r="C4" s="140">
         <v>182823.01</v>
       </c>
       <c r="D4" s="68"/>
@@ -3738,22 +3764,22 @@
       <c r="G4" s="132"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="224"/>
+      <c r="J4" s="258"/>
+      <c r="K4" s="258"/>
+      <c r="L4" s="258"/>
+      <c r="M4" s="258"/>
+      <c r="N4" s="258"/>
+      <c r="O4" s="258"/>
+      <c r="P4" s="259"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="141" t="s">
-        <v>167</v>
+    <row r="5" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="139" t="s">
+        <v>166</v>
       </c>
       <c r="B5" s="129"/>
-      <c r="C5" s="143">
+      <c r="C5" s="141">
         <v>1313151.8700000001</v>
       </c>
       <c r="D5" s="69"/>
@@ -3762,112 +3788,112 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
-      <c r="M5" s="225"/>
-      <c r="N5" s="225"/>
-      <c r="O5" s="225"/>
-      <c r="P5" s="226"/>
+      <c r="J5" s="260"/>
+      <c r="K5" s="260"/>
+      <c r="L5" s="260"/>
+      <c r="M5" s="260"/>
+      <c r="N5" s="260"/>
+      <c r="O5" s="260"/>
+      <c r="P5" s="261"/>
       <c r="Q5" s="62"/>
     </row>
-    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="233" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="234"/>
-      <c r="C6" s="235"/>
-      <c r="D6" s="235"/>
-      <c r="E6" s="235"/>
-      <c r="F6" s="235"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="235"/>
-      <c r="I6" s="235"/>
-      <c r="J6" s="235"/>
-      <c r="K6" s="235"/>
-      <c r="L6" s="235"/>
-      <c r="M6" s="235"/>
-      <c r="N6" s="235"/>
-      <c r="O6" s="235"/>
-      <c r="P6" s="236"/>
+    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="231" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="232"/>
+      <c r="C6" s="233"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="233"/>
+      <c r="H6" s="233"/>
+      <c r="I6" s="233"/>
+      <c r="J6" s="233"/>
+      <c r="K6" s="233"/>
+      <c r="L6" s="233"/>
+      <c r="M6" s="233"/>
+      <c r="N6" s="233"/>
+      <c r="O6" s="233"/>
+      <c r="P6" s="234"/>
       <c r="Q6" s="62"/>
     </row>
-    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="237"/>
-      <c r="B7" s="238"/>
-      <c r="C7" s="238"/>
-      <c r="D7" s="238"/>
-      <c r="E7" s="238"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238"/>
-      <c r="H7" s="238"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="238"/>
-      <c r="K7" s="238"/>
-      <c r="L7" s="238"/>
-      <c r="M7" s="238"/>
-      <c r="N7" s="238"/>
-      <c r="O7" s="238"/>
-      <c r="P7" s="239"/>
+    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="235"/>
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="236"/>
+      <c r="K7" s="236"/>
+      <c r="L7" s="236"/>
+      <c r="M7" s="236"/>
+      <c r="N7" s="236"/>
+      <c r="O7" s="236"/>
+      <c r="P7" s="237"/>
       <c r="Q7" s="62"/>
     </row>
-    <row r="8" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="237"/>
-      <c r="B8" s="238"/>
-      <c r="C8" s="238"/>
-      <c r="D8" s="238"/>
-      <c r="E8" s="238"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="238"/>
-      <c r="I8" s="238"/>
-      <c r="J8" s="238"/>
-      <c r="K8" s="238"/>
-      <c r="L8" s="238"/>
-      <c r="M8" s="238"/>
-      <c r="N8" s="238"/>
-      <c r="O8" s="238"/>
-      <c r="P8" s="239"/>
+    <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="235"/>
+      <c r="B8" s="236"/>
+      <c r="C8" s="236"/>
+      <c r="D8" s="236"/>
+      <c r="E8" s="236"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="236"/>
+      <c r="I8" s="236"/>
+      <c r="J8" s="236"/>
+      <c r="K8" s="236"/>
+      <c r="L8" s="236"/>
+      <c r="M8" s="236"/>
+      <c r="N8" s="236"/>
+      <c r="O8" s="236"/>
+      <c r="P8" s="237"/>
       <c r="Q8" s="62"/>
     </row>
-    <row r="9" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="237"/>
-      <c r="B9" s="238"/>
-      <c r="C9" s="238"/>
-      <c r="D9" s="238"/>
-      <c r="E9" s="238"/>
-      <c r="F9" s="238"/>
-      <c r="G9" s="238"/>
-      <c r="H9" s="238"/>
-      <c r="I9" s="238"/>
-      <c r="J9" s="238"/>
-      <c r="K9" s="238"/>
-      <c r="L9" s="238"/>
-      <c r="M9" s="238"/>
-      <c r="N9" s="238"/>
-      <c r="O9" s="238"/>
-      <c r="P9" s="239"/>
+    <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="235"/>
+      <c r="B9" s="236"/>
+      <c r="C9" s="236"/>
+      <c r="D9" s="236"/>
+      <c r="E9" s="236"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="237"/>
       <c r="Q9" s="62"/>
     </row>
-    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="240"/>
-      <c r="B10" s="241"/>
-      <c r="C10" s="241"/>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="241"/>
-      <c r="H10" s="241"/>
-      <c r="I10" s="241"/>
-      <c r="J10" s="241"/>
-      <c r="K10" s="241"/>
-      <c r="L10" s="241"/>
-      <c r="M10" s="241"/>
-      <c r="N10" s="241"/>
-      <c r="O10" s="241"/>
-      <c r="P10" s="242"/>
-    </row>
-    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="238"/>
+      <c r="B10" s="239"/>
+      <c r="C10" s="239"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="239"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+      <c r="N10" s="239"/>
+      <c r="O10" s="239"/>
+      <c r="P10" s="240"/>
+    </row>
+    <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="249" t="s">
         <v>46</v>
       </c>
@@ -3887,78 +3913,78 @@
       <c r="O11" s="250"/>
       <c r="P11" s="251"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="243" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="241" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="254" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="245" t="s">
+      <c r="C12" s="243" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="245" t="s">
+      <c r="D12" s="243" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="245" t="s">
+      <c r="E12" s="243" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="227" t="s">
+      <c r="F12" s="245" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="245" t="s">
+      <c r="G12" s="243" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="247" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="227" t="s">
+      <c r="I12" s="245" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="227" t="s">
+      <c r="J12" s="245" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="227" t="s">
+      <c r="K12" s="245" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="254" t="s">
-        <v>171</v>
-      </c>
-      <c r="M12" s="227" t="s">
-        <v>168</v>
+        <v>170</v>
+      </c>
+      <c r="M12" s="245" t="s">
+        <v>167</v>
       </c>
       <c r="N12" s="252" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="229" t="s">
+      <c r="P12" s="262" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="244"/>
+    <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="242"/>
       <c r="B13" s="255"/>
-      <c r="C13" s="246"/>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="228"/>
-      <c r="G13" s="246"/>
+      <c r="C13" s="244"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="244"/>
       <c r="H13" s="248"/>
-      <c r="I13" s="228"/>
-      <c r="J13" s="228"/>
-      <c r="K13" s="228"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
       <c r="L13" s="255"/>
-      <c r="M13" s="228"/>
+      <c r="M13" s="246"/>
       <c r="N13" s="253"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="P13" s="230"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="263"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="83">
         <v>1</v>
       </c>
@@ -3973,15 +3999,15 @@
         <v>5.22</v>
       </c>
       <c r="F14" s="63">
-        <v>388500.01</v>
-      </c>
-      <c r="G14" s="63">
-        <f>400155.01</f>
-        <v>400155.01</v>
+        <v>322564.01</v>
+      </c>
+      <c r="G14" s="199">
+        <f t="shared" ref="G14" si="0">F14</f>
+        <v>322564.01</v>
       </c>
       <c r="H14" s="75">
-        <f t="shared" ref="H14:H59" si="0">F14-G14</f>
-        <v>-11655</v>
+        <f t="shared" ref="H14:H59" si="1">F14-G14</f>
+        <v>0</v>
       </c>
       <c r="I14" s="75">
         <f>IF(H14&gt;0,H14*3%,0)</f>
@@ -3992,7 +4018,7 @@
         <v>256129.20651600001</v>
       </c>
       <c r="K14" s="82">
-        <f t="shared" ref="K14:K45" si="1">F$2*E14/100</f>
+        <f t="shared" ref="K14:K45" si="2">F$2*E14/100</f>
         <v>0</v>
       </c>
       <c r="L14" s="82">
@@ -4006,17 +4032,17 @@
       <c r="N14" s="82"/>
       <c r="O14" s="76">
         <f>ROUND(SUM(H14:N14),0) + Q14</f>
-        <v>322564.01</v>
+        <v>334219.01</v>
       </c>
       <c r="P14" s="91">
-        <f t="shared" ref="P14:P34" si="2">ROUND(O14*3%,0) + O14</f>
-        <v>332241.01</v>
+        <f t="shared" ref="P14:P34" si="3">ROUND(O14*3%,0) + O14</f>
+        <v>344246.01</v>
       </c>
       <c r="Q14" s="40">
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="83">
         <v>2</v>
       </c>
@@ -4027,57 +4053,54 @@
         <v>118</v>
       </c>
       <c r="D15" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15" s="74">
         <v>3.4</v>
       </c>
       <c r="F15" s="63">
-        <v>257906.02</v>
-      </c>
-      <c r="G15" s="63">
-        <f>F15+204243.28-F41</f>
-        <v>442321.02</v>
-      </c>
+        <v>33276.019999999997</v>
+      </c>
+      <c r="G15" s="63"/>
       <c r="H15" s="75">
-        <f t="shared" si="0"/>
-        <v>-184415.00000000003</v>
+        <f t="shared" si="1"/>
+        <v>33276.019999999997</v>
       </c>
       <c r="I15" s="75">
-        <f t="shared" ref="I15:I59" si="3">IF(H15&gt;0,H15*3%,0)</f>
-        <v>0</v>
+        <f t="shared" ref="I15:I59" si="4">IF(H15&gt;0,H15*3%,0)</f>
+        <v>998.28059999999982</v>
       </c>
       <c r="J15" s="82">
-        <f t="shared" ref="J15:J59" si="4">C$2*E15/100</f>
+        <f t="shared" ref="J15:J59" si="5">C$2*E15/100</f>
         <v>166827.45251999999</v>
       </c>
       <c r="K15" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L15" s="82">
-        <f t="shared" ref="L15:L59" si="5">C$4*E15/100</f>
+        <f t="shared" ref="L15:L59" si="6">C$4*E15/100</f>
         <v>6215.9823400000005</v>
       </c>
       <c r="M15" s="82">
-        <f t="shared" ref="M15:M59" si="6">C$5*E15/100</f>
+        <f t="shared" ref="M15:M59" si="7">C$5*E15/100</f>
         <v>44647.16358</v>
       </c>
       <c r="N15" s="82"/>
       <c r="O15" s="76">
-        <f t="shared" ref="O15:O59" si="7">ROUND(SUM(H15:N15),0) + Q15</f>
-        <v>33276.019999999997</v>
+        <f t="shared" ref="O15:O59" si="8">ROUND(SUM(H15:N15),0) + Q15</f>
+        <v>251965.02</v>
       </c>
       <c r="P15" s="91">
-        <f t="shared" si="2"/>
-        <v>34274.019999999997</v>
+        <f t="shared" si="3"/>
+        <v>259524.02</v>
       </c>
       <c r="Q15" s="40">
         <f>Q14+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="83">
         <v>3</v>
       </c>
@@ -4088,59 +4111,60 @@
         <v>119</v>
       </c>
       <c r="D16" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E16" s="74">
         <v>2.54</v>
       </c>
       <c r="F16" s="63">
-        <v>190304.03</v>
-      </c>
-      <c r="G16" s="63">
-        <v>192000</v>
+        <v>160932.03</v>
+      </c>
+      <c r="G16" s="199">
+        <f>F16</f>
+        <v>160932.03</v>
       </c>
       <c r="H16" s="75">
-        <f t="shared" si="0"/>
-        <v>-1695.9700000000012</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I16" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J16" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124629.92041200001</v>
       </c>
       <c r="K16" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L16" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
       <c r="M16" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>33354.057498000002</v>
       </c>
       <c r="N16" s="82"/>
       <c r="O16" s="76">
-        <f t="shared" si="7"/>
-        <v>160932.03</v>
+        <f t="shared" si="8"/>
+        <v>162628.03</v>
       </c>
       <c r="P16" s="91">
-        <f t="shared" si="2"/>
-        <v>165760.03</v>
+        <f t="shared" si="3"/>
+        <v>167507.03</v>
       </c>
       <c r="Q16" s="40">
-        <f t="shared" ref="Q16:Q31" si="8">Q15+0.01</f>
+        <f t="shared" ref="Q16:Q31" si="9">Q15+0.01</f>
         <v>0.03</v>
       </c>
       <c r="R16" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="83">
         <v>4</v>
       </c>
@@ -4151,121 +4175,121 @@
         <v>120</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E17" s="74">
         <v>5.19</v>
       </c>
       <c r="F17" s="63">
-        <v>384603.04</v>
-      </c>
-      <c r="G17" s="63">
-        <f>449413-G55-G44</f>
-        <v>379957.27</v>
+        <v>337083.04</v>
+      </c>
+      <c r="G17" s="199">
+        <f>403280-G55-G44</f>
+        <v>348856.27</v>
       </c>
       <c r="H17" s="75">
-        <f t="shared" si="0"/>
-        <v>4645.7699999999604</v>
+        <f t="shared" si="1"/>
+        <v>-11773.23000000004</v>
       </c>
       <c r="I17" s="75">
-        <f t="shared" si="3"/>
-        <v>139.3730999999988</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="J17" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>254657.19958200003</v>
       </c>
       <c r="K17" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L17" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
       <c r="M17" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>68152.58205300002</v>
       </c>
       <c r="N17" s="82"/>
       <c r="O17" s="76">
-        <f t="shared" si="7"/>
-        <v>337083.04</v>
+        <f t="shared" si="8"/>
+        <v>320525.03999999998</v>
       </c>
       <c r="P17" s="91">
-        <f t="shared" si="2"/>
-        <v>347195.04</v>
+        <f t="shared" si="3"/>
+        <v>330141.03999999998</v>
       </c>
       <c r="Q17" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
       <c r="R17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="197">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="83">
         <v>5</v>
       </c>
-      <c r="B18" s="198" t="s">
+      <c r="B18" s="130" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="199" t="s">
+      <c r="C18" s="72" t="s">
         <v>121</v>
       </c>
       <c r="D18" s="77" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E18" s="74">
         <v>3.4</v>
       </c>
       <c r="F18" s="63">
-        <v>255000.05</v>
-      </c>
-      <c r="G18" s="63">
-        <f>F18</f>
-        <v>255000.05</v>
+        <v>217691.05</v>
+      </c>
+      <c r="G18" s="199">
+        <f>77540+140500</f>
+        <v>218040</v>
       </c>
       <c r="H18" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>-348.95000000001164</v>
       </c>
       <c r="I18" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J18" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>166827.45251999999</v>
       </c>
       <c r="K18" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L18" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
       <c r="M18" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44647.16358</v>
       </c>
       <c r="N18" s="82"/>
       <c r="O18" s="76">
-        <f t="shared" si="7"/>
-        <v>217691.05</v>
+        <f t="shared" si="8"/>
+        <v>217342.05</v>
       </c>
       <c r="P18" s="91">
-        <f t="shared" si="2"/>
-        <v>224222.05</v>
+        <f t="shared" si="3"/>
+        <v>223862.05</v>
       </c>
       <c r="Q18" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="83">
         <v>6</v>
       </c>
@@ -4276,57 +4300,57 @@
         <v>118</v>
       </c>
       <c r="D19" s="72" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E19" s="74">
         <v>2.54</v>
       </c>
       <c r="F19" s="63">
-        <v>351985.06</v>
-      </c>
-      <c r="G19" s="63">
-        <f>156782+190500.06+4703</f>
-        <v>351985.06</v>
+        <v>162628.06</v>
+      </c>
+      <c r="G19" s="199">
+        <f>F19</f>
+        <v>162628.06</v>
       </c>
       <c r="H19" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I19" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J19" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124629.92041200001</v>
       </c>
       <c r="K19" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L19" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
       <c r="M19" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>33354.057498000002</v>
       </c>
       <c r="N19" s="82"/>
       <c r="O19" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>162628.06</v>
       </c>
       <c r="P19" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>167507.06</v>
       </c>
       <c r="Q19" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="83">
         <v>7</v>
       </c>
@@ -4341,51 +4365,51 @@
         <v>5.19</v>
       </c>
       <c r="F20" s="63">
-        <v>389250.07</v>
-      </c>
-      <c r="G20" s="63">
-        <f t="shared" ref="G20:G25" si="9">F20</f>
-        <v>389250.07</v>
+        <v>332298.07</v>
+      </c>
+      <c r="G20" s="199">
+        <f t="shared" ref="G20:G25" si="10">F20</f>
+        <v>332298.07</v>
       </c>
       <c r="H20" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I20" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J20" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>254657.19958200003</v>
       </c>
       <c r="K20" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L20" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
       <c r="M20" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>68152.58205300002</v>
       </c>
       <c r="N20" s="82"/>
       <c r="O20" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>332298.07</v>
       </c>
       <c r="P20" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>342267.07</v>
       </c>
       <c r="Q20" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="83">
         <v>8</v>
       </c>
@@ -4400,51 +4424,51 @@
         <v>3.4</v>
       </c>
       <c r="F21" s="63">
-        <v>255000.08</v>
-      </c>
-      <c r="G21" s="63">
-        <f t="shared" si="9"/>
-        <v>255000.08</v>
+        <v>217691.08</v>
+      </c>
+      <c r="G21" s="199">
+        <f t="shared" si="10"/>
+        <v>217691.08</v>
       </c>
       <c r="H21" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I21" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J21" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>166827.45251999999</v>
       </c>
       <c r="K21" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L21" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
       <c r="M21" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44647.16358</v>
       </c>
       <c r="N21" s="82"/>
       <c r="O21" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>217691.08</v>
       </c>
       <c r="P21" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>224222.07999999999</v>
       </c>
       <c r="Q21" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="83">
         <v>9</v>
       </c>
@@ -4455,57 +4479,57 @@
         <v>118</v>
       </c>
       <c r="D22" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E22" s="74">
         <v>2.54</v>
       </c>
       <c r="F22" s="63">
-        <v>190500.09</v>
-      </c>
-      <c r="G22" s="63">
-        <f t="shared" si="9"/>
-        <v>190500.09</v>
+        <v>162628.09</v>
+      </c>
+      <c r="G22" s="199">
+        <f t="shared" si="10"/>
+        <v>162628.09</v>
       </c>
       <c r="H22" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I22" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J22" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124629.92041200001</v>
       </c>
       <c r="K22" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L22" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
       <c r="M22" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>33354.057498000002</v>
       </c>
       <c r="N22" s="82"/>
       <c r="O22" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>162628.09</v>
       </c>
       <c r="P22" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>167507.09</v>
       </c>
       <c r="Q22" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="83">
         <v>10</v>
       </c>
@@ -4520,51 +4544,51 @@
         <v>5.19</v>
       </c>
       <c r="F23" s="63">
-        <v>389250.1</v>
-      </c>
-      <c r="G23" s="63">
-        <f t="shared" si="9"/>
-        <v>389250.1</v>
+        <v>332298.09999999998</v>
+      </c>
+      <c r="G23" s="199">
+        <f t="shared" si="10"/>
+        <v>332298.09999999998</v>
       </c>
       <c r="H23" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I23" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J23" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>254657.19958200003</v>
       </c>
       <c r="K23" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L23" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
       <c r="M23" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>68152.58205300002</v>
       </c>
       <c r="N23" s="82"/>
       <c r="O23" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>332298.09999999998</v>
       </c>
       <c r="P23" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>342267.1</v>
       </c>
       <c r="Q23" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="83">
         <v>11</v>
       </c>
@@ -4575,57 +4599,57 @@
         <v>125</v>
       </c>
       <c r="D24" s="77" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E24" s="74">
         <v>3.4</v>
       </c>
       <c r="F24" s="63">
-        <v>255000.11</v>
-      </c>
-      <c r="G24" s="63">
-        <f t="shared" si="9"/>
-        <v>255000.11</v>
+        <v>217691.11</v>
+      </c>
+      <c r="G24" s="199">
+        <f t="shared" si="10"/>
+        <v>217691.11</v>
       </c>
       <c r="H24" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I24" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J24" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>166827.45251999999</v>
       </c>
       <c r="K24" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L24" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
       <c r="M24" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44647.16358</v>
       </c>
       <c r="N24" s="82"/>
       <c r="O24" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>217691.11</v>
       </c>
       <c r="P24" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>224222.11</v>
       </c>
       <c r="Q24" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="83">
         <v>12</v>
       </c>
@@ -4636,175 +4660,175 @@
         <v>126</v>
       </c>
       <c r="D25" s="77" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" s="74">
         <v>2.54</v>
       </c>
       <c r="F25" s="63">
-        <v>190500.12</v>
-      </c>
-      <c r="G25" s="63">
-        <f t="shared" si="9"/>
-        <v>190500.12</v>
+        <v>162628.12</v>
+      </c>
+      <c r="G25" s="199">
+        <f t="shared" si="10"/>
+        <v>162628.12</v>
       </c>
       <c r="H25" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I25" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J25" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124629.92041200001</v>
       </c>
       <c r="K25" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L25" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
       <c r="M25" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>33354.057498000002</v>
       </c>
       <c r="N25" s="82"/>
       <c r="O25" s="76">
+        <f t="shared" si="8"/>
+        <v>162628.12</v>
+      </c>
+      <c r="P25" s="91">
+        <f t="shared" si="3"/>
+        <v>167507.12</v>
+      </c>
+      <c r="Q25" s="40">
+        <f t="shared" si="9"/>
+        <v>0.11999999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="142">
+        <v>13</v>
+      </c>
+      <c r="B26" s="143" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="144" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="145"/>
+      <c r="E26" s="146">
+        <v>5.19</v>
+      </c>
+      <c r="F26" s="147">
+        <v>320441.13</v>
+      </c>
+      <c r="G26" s="211">
+        <f>335330.44-G45</f>
+        <v>330208.12</v>
+      </c>
+      <c r="H26" s="148">
+        <f t="shared" si="1"/>
+        <v>-9766.9899999999907</v>
+      </c>
+      <c r="I26" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="149">
+        <f t="shared" si="5"/>
+        <v>254657.19958200003</v>
+      </c>
+      <c r="K26" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="149">
+        <f t="shared" si="6"/>
+        <v>9488.5142190000006</v>
+      </c>
+      <c r="M26" s="149">
         <f t="shared" si="7"/>
-        <v>162628.12</v>
-      </c>
-      <c r="P25" s="91">
+        <v>68152.58205300002</v>
+      </c>
+      <c r="N26" s="149"/>
+      <c r="O26" s="150">
+        <f t="shared" si="8"/>
+        <v>322531.13</v>
+      </c>
+      <c r="P26" s="151">
+        <f t="shared" si="3"/>
+        <v>332207.13</v>
+      </c>
+      <c r="Q26" s="40">
+        <f t="shared" si="9"/>
+        <v>0.12999999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="142">
+        <v>14</v>
+      </c>
+      <c r="B27" s="143" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="145"/>
+      <c r="E27" s="146">
+        <v>3.4</v>
+      </c>
+      <c r="F27" s="147">
+        <v>217691.14</v>
+      </c>
+      <c r="G27" s="211">
+        <f>288191.52-G51</f>
+        <v>226085.14</v>
+      </c>
+      <c r="H27" s="148">
+        <f t="shared" si="1"/>
+        <v>-8394</v>
+      </c>
+      <c r="I27" s="148">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="149">
+        <f t="shared" si="5"/>
+        <v>166827.45251999999</v>
+      </c>
+      <c r="K27" s="149">
         <f t="shared" si="2"/>
-        <v>167507.12</v>
-      </c>
-      <c r="Q25" s="40">
+        <v>0</v>
+      </c>
+      <c r="L27" s="149">
+        <f t="shared" si="6"/>
+        <v>6215.9823400000005</v>
+      </c>
+      <c r="M27" s="149">
+        <f t="shared" si="7"/>
+        <v>44647.16358</v>
+      </c>
+      <c r="N27" s="149"/>
+      <c r="O27" s="150">
         <f t="shared" si="8"/>
-        <v>0.11999999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="144">
-        <v>13</v>
-      </c>
-      <c r="B26" s="145" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="146" t="s">
-        <v>189</v>
-      </c>
-      <c r="D26" s="147"/>
-      <c r="E26" s="148">
-        <v>5.19</v>
-      </c>
-      <c r="F26" s="149">
-        <v>389250.13</v>
-      </c>
-      <c r="G26" s="149">
-        <f>407108-G45</f>
-        <v>401107.68</v>
-      </c>
-      <c r="H26" s="150">
-        <f t="shared" si="0"/>
-        <v>-11857.549999999988</v>
-      </c>
-      <c r="I26" s="150">
+        <v>209297.14</v>
+      </c>
+      <c r="P27" s="151">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="151">
-        <f t="shared" si="4"/>
-        <v>254657.19958200003</v>
-      </c>
-      <c r="K26" s="151">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="151">
-        <f t="shared" si="5"/>
-        <v>9488.5142190000006</v>
-      </c>
-      <c r="M26" s="151">
-        <f t="shared" si="6"/>
-        <v>68152.58205300002</v>
-      </c>
-      <c r="N26" s="151"/>
-      <c r="O26" s="152">
-        <f t="shared" si="7"/>
-        <v>320441.13</v>
-      </c>
-      <c r="P26" s="153">
-        <f t="shared" si="2"/>
-        <v>330054.13</v>
-      </c>
-      <c r="Q26" s="40">
-        <f t="shared" si="8"/>
-        <v>0.12999999999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="144">
-        <v>14</v>
-      </c>
-      <c r="B27" s="145" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="146" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="147"/>
-      <c r="E27" s="148">
-        <v>3.4</v>
-      </c>
-      <c r="F27" s="149">
-        <v>255618.14</v>
-      </c>
-      <c r="G27" s="149">
-        <f>328368.22-G51</f>
-        <v>255617.83999999997</v>
-      </c>
-      <c r="H27" s="150">
-        <f t="shared" si="0"/>
-        <v>0.30000000004656613</v>
-      </c>
-      <c r="I27" s="150">
-        <f t="shared" si="3"/>
-        <v>9.0000000013969843E-3</v>
-      </c>
-      <c r="J27" s="151">
-        <f t="shared" si="4"/>
-        <v>166827.45251999999</v>
-      </c>
-      <c r="K27" s="151">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="151">
-        <f t="shared" si="5"/>
-        <v>6215.9823400000005</v>
-      </c>
-      <c r="M27" s="151">
-        <f t="shared" si="6"/>
-        <v>44647.16358</v>
-      </c>
-      <c r="N27" s="151"/>
-      <c r="O27" s="152">
-        <f t="shared" si="7"/>
-        <v>217691.14</v>
-      </c>
-      <c r="P27" s="153">
-        <f t="shared" si="2"/>
-        <v>224222.14</v>
+        <v>215576.14</v>
       </c>
       <c r="Q27" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="83">
         <v>15</v>
       </c>
@@ -4815,57 +4839,57 @@
         <v>129</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E28" s="74">
         <v>2.54</v>
       </c>
       <c r="F28" s="63">
-        <v>225645.15</v>
-      </c>
-      <c r="G28" s="63">
+        <v>162628.15</v>
+      </c>
+      <c r="G28" s="199">
         <f>F28</f>
-        <v>225645.15</v>
+        <v>162628.15</v>
       </c>
       <c r="H28" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I28" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J28" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124629.92041200001</v>
       </c>
       <c r="K28" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L28" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
       <c r="M28" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>33354.057498000002</v>
       </c>
       <c r="N28" s="82"/>
       <c r="O28" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>162628.15</v>
       </c>
       <c r="P28" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>167507.15</v>
       </c>
       <c r="Q28" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="83">
         <v>16</v>
       </c>
@@ -4880,51 +4904,51 @@
         <v>5.19</v>
       </c>
       <c r="F29" s="63">
-        <v>389250.16</v>
-      </c>
-      <c r="G29" s="63">
+        <v>332298.15999999997</v>
+      </c>
+      <c r="G29" s="199">
         <f>F29</f>
-        <v>389250.16</v>
+        <v>332298.15999999997</v>
       </c>
       <c r="H29" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I29" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J29" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>254657.19958200003</v>
       </c>
       <c r="K29" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L29" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
       <c r="M29" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>68152.58205300002</v>
       </c>
       <c r="N29" s="82"/>
       <c r="O29" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>332298.15999999997</v>
       </c>
       <c r="P29" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>342267.16</v>
       </c>
       <c r="Q29" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="83">
         <v>17</v>
       </c>
@@ -4935,57 +4959,57 @@
         <v>131</v>
       </c>
       <c r="D30" s="77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E30" s="74">
         <v>3.4</v>
       </c>
       <c r="F30" s="63">
-        <v>269008.17</v>
-      </c>
-      <c r="G30" s="63">
-        <f>326761-G53</f>
-        <v>269010.59999999998</v>
+        <v>217688.17</v>
+      </c>
+      <c r="G30" s="199">
+        <f>268481-G53</f>
+        <v>219179.6</v>
       </c>
       <c r="H30" s="75">
-        <f t="shared" si="0"/>
-        <v>-2.4299999999930151</v>
+        <f t="shared" si="1"/>
+        <v>-1491.429999999993</v>
       </c>
       <c r="I30" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J30" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>166827.45251999999</v>
       </c>
       <c r="K30" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L30" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
       <c r="M30" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>44647.16358</v>
       </c>
       <c r="N30" s="82"/>
       <c r="O30" s="76">
-        <f t="shared" si="7"/>
-        <v>217688.17</v>
+        <f t="shared" si="8"/>
+        <v>216199.17</v>
       </c>
       <c r="P30" s="91">
-        <f t="shared" si="2"/>
-        <v>224219.17</v>
+        <f t="shared" si="3"/>
+        <v>222685.17</v>
       </c>
       <c r="Q30" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="83">
         <v>18</v>
       </c>
@@ -5000,48 +5024,48 @@
         <v>2.54</v>
       </c>
       <c r="F31" s="63">
-        <v>1410658.18</v>
+        <v>1615606.18</v>
       </c>
       <c r="G31" s="63"/>
       <c r="H31" s="75">
-        <f t="shared" si="0"/>
-        <v>1410658.18</v>
+        <f t="shared" si="1"/>
+        <v>1615606.18</v>
       </c>
       <c r="I31" s="75">
-        <f t="shared" si="3"/>
-        <v>42319.7454</v>
+        <f t="shared" si="4"/>
+        <v>48468.185399999995</v>
       </c>
       <c r="J31" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124629.92041200001</v>
       </c>
       <c r="K31" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L31" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
       <c r="M31" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>33354.057498000002</v>
       </c>
       <c r="N31" s="82"/>
       <c r="O31" s="76">
-        <f t="shared" si="7"/>
-        <v>1615606.18</v>
+        <f t="shared" si="8"/>
+        <v>1826702.18</v>
       </c>
       <c r="P31" s="91">
-        <f t="shared" si="2"/>
-        <v>1664074.18</v>
+        <f t="shared" si="3"/>
+        <v>1881503.18</v>
       </c>
       <c r="Q31" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="83">
         <v>19</v>
       </c>
@@ -5056,108 +5080,108 @@
         <v>5.19</v>
       </c>
       <c r="F32" s="63">
-        <v>745476.19</v>
+        <v>1143639.19</v>
       </c>
       <c r="G32" s="63">
         <v>0</v>
       </c>
       <c r="H32" s="75">
-        <f t="shared" si="0"/>
-        <v>745476.19</v>
+        <f t="shared" si="1"/>
+        <v>1143639.19</v>
       </c>
       <c r="I32" s="75">
-        <f t="shared" si="3"/>
-        <v>22364.285699999997</v>
+        <f t="shared" si="4"/>
+        <v>34309.1757</v>
       </c>
       <c r="J32" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>254657.19958200003</v>
       </c>
       <c r="K32" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L32" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9488.5142190000006</v>
       </c>
       <c r="M32" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>68152.58205300002</v>
       </c>
       <c r="N32" s="82">
         <v>43500</v>
       </c>
       <c r="O32" s="76">
-        <f t="shared" si="7"/>
-        <v>1143639.19</v>
+        <f t="shared" si="8"/>
+        <v>1553747.19</v>
       </c>
       <c r="P32" s="91">
-        <f t="shared" si="2"/>
-        <v>1177948.19</v>
+        <f t="shared" si="3"/>
+        <v>1600359.19</v>
       </c>
       <c r="Q32" s="40">
         <f>Q31+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="83">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="200">
         <v>20</v>
       </c>
-      <c r="B33" s="130" t="s">
+      <c r="B33" s="201" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="72" t="s">
+      <c r="C33" s="202" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="77"/>
-      <c r="E33" s="74">
+      <c r="D33" s="203"/>
+      <c r="E33" s="204">
         <v>3.4</v>
       </c>
-      <c r="F33" s="63">
-        <v>255000.2</v>
-      </c>
-      <c r="G33" s="63">
-        <f>261000.54-G47</f>
-        <v>255000.2</v>
-      </c>
-      <c r="H33" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="75"/>
-      <c r="J33" s="82">
-        <f t="shared" si="4"/>
+      <c r="F33" s="205">
+        <v>217691.2</v>
+      </c>
+      <c r="G33" s="206">
+        <f>229946.49-G47</f>
+        <v>224824.15</v>
+      </c>
+      <c r="H33" s="207">
+        <f t="shared" si="1"/>
+        <v>-7132.9499999999825</v>
+      </c>
+      <c r="I33" s="207"/>
+      <c r="J33" s="208">
+        <f t="shared" si="5"/>
         <v>166827.45251999999</v>
       </c>
-      <c r="K33" s="82">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="82">
-        <f t="shared" si="5"/>
+      <c r="K33" s="208">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="208">
+        <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="82">
-        <f t="shared" si="6"/>
+      <c r="M33" s="208">
+        <f t="shared" si="7"/>
         <v>44647.16358</v>
       </c>
-      <c r="N33" s="82"/>
-      <c r="O33" s="76">
-        <f t="shared" si="7"/>
-        <v>217691.2</v>
-      </c>
-      <c r="P33" s="91">
-        <f t="shared" si="2"/>
-        <v>224222.2</v>
+      <c r="N33" s="208"/>
+      <c r="O33" s="209">
+        <f t="shared" si="8"/>
+        <v>210558.2</v>
+      </c>
+      <c r="P33" s="210">
+        <f t="shared" si="3"/>
+        <v>216875.2</v>
       </c>
       <c r="Q33" s="40">
-        <f t="shared" ref="Q33:Q59" si="10">Q32+0.01</f>
+        <f t="shared" ref="Q33:Q59" si="11">Q32+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="83">
         <v>21</v>
       </c>
@@ -5168,57 +5192,57 @@
         <v>121</v>
       </c>
       <c r="D34" s="77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E34" s="74">
         <v>2.54</v>
       </c>
       <c r="F34" s="63">
-        <v>190500.21</v>
-      </c>
-      <c r="G34" s="63">
-        <f>F34</f>
-        <v>190500.21</v>
+        <v>162628.21</v>
+      </c>
+      <c r="G34" s="199">
+        <f t="shared" ref="G34:G35" si="12">F34</f>
+        <v>162628.21</v>
       </c>
       <c r="H34" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I34" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J34" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124629.92041200001</v>
       </c>
       <c r="K34" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L34" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4643.7044540000006</v>
       </c>
       <c r="M34" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>33354.057498000002</v>
       </c>
       <c r="N34" s="82"/>
       <c r="O34" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>162628.21</v>
       </c>
       <c r="P34" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>167507.21</v>
       </c>
       <c r="Q34" s="40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="83">
         <f>A34+1</f>
         <v>22</v>
@@ -5230,59 +5254,59 @@
         <v>135</v>
       </c>
       <c r="D35" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E35" s="74">
         <v>4.9400000000000004</v>
       </c>
       <c r="F35" s="63">
-        <v>370500.22</v>
-      </c>
-      <c r="G35" s="63">
-        <f>F35</f>
-        <v>370500.22</v>
+        <v>316292.21999999997</v>
+      </c>
+      <c r="G35" s="199">
+        <f t="shared" si="12"/>
+        <v>316292.21999999997</v>
       </c>
       <c r="H35" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I35" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J35" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>242390.47513200005</v>
       </c>
       <c r="K35" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L35" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9031.4566940000004</v>
       </c>
       <c r="M35" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>64869.702378000009</v>
       </c>
       <c r="N35" s="82"/>
       <c r="O35" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>316292.21999999997</v>
       </c>
       <c r="P35" s="91">
-        <f t="shared" ref="P35:P59" si="11">ROUND(O35*3%,0) + O35</f>
+        <f t="shared" ref="P35:P59" si="13">ROUND(O35*3%,0) + O35</f>
         <v>325781.21999999997</v>
       </c>
       <c r="Q35" s="40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="83">
-        <f t="shared" ref="A36:A59" si="12">A35+1</f>
+        <f t="shared" ref="A36:A59" si="14">A35+1</f>
         <v>23</v>
       </c>
       <c r="B36" s="130" t="s">
@@ -5292,58 +5316,58 @@
         <v>136</v>
       </c>
       <c r="D36" s="77" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E36" s="74">
         <v>3.28</v>
       </c>
       <c r="F36" s="63">
-        <v>246844.23</v>
-      </c>
-      <c r="G36" s="63">
-        <v>246000</v>
+        <v>210877.23</v>
+      </c>
+      <c r="G36" s="199">
+        <v>217223</v>
       </c>
       <c r="H36" s="75">
-        <f t="shared" si="0"/>
-        <v>844.23000000001048</v>
+        <f t="shared" si="1"/>
+        <v>-6345.7699999999895</v>
       </c>
       <c r="I36" s="75">
-        <f t="shared" si="3"/>
-        <v>25.326900000000315</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="J36" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>160939.424784</v>
       </c>
       <c r="K36" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L36" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5996.594728</v>
       </c>
       <c r="M36" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>43071.381336000006</v>
       </c>
       <c r="N36" s="82"/>
       <c r="O36" s="76">
-        <f t="shared" si="7"/>
-        <v>210877.23</v>
+        <f t="shared" si="8"/>
+        <v>203662.23</v>
       </c>
       <c r="P36" s="91">
+        <f t="shared" si="13"/>
+        <v>209772.23</v>
+      </c>
+      <c r="Q36" s="40">
         <f t="shared" si="11"/>
-        <v>217203.23</v>
-      </c>
-      <c r="Q36" s="40">
-        <f t="shared" si="10"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="B37" s="130" t="s">
@@ -5357,59 +5381,58 @@
         <v>2.41</v>
       </c>
       <c r="F37" s="63">
-        <v>180750.24</v>
-      </c>
-      <c r="G37" s="63">
-        <f>F37</f>
-        <v>180750.24</v>
+        <v>154304.24</v>
+      </c>
+      <c r="G37" s="199">
+        <v>158933.24</v>
       </c>
       <c r="H37" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>-4629</v>
       </c>
       <c r="I37" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J37" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118251.22369800002</v>
       </c>
       <c r="K37" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L37" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4406.034541</v>
       </c>
       <c r="M37" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>31646.960067000004</v>
       </c>
       <c r="N37" s="82"/>
       <c r="O37" s="76">
-        <f t="shared" si="7"/>
-        <v>154304.24</v>
+        <f t="shared" si="8"/>
+        <v>149675.24</v>
       </c>
       <c r="P37" s="91">
+        <f t="shared" si="13"/>
+        <v>154165.24</v>
+      </c>
+      <c r="Q37" s="40">
         <f t="shared" si="11"/>
-        <v>158933.24</v>
-      </c>
-      <c r="Q37" s="40">
-        <f t="shared" si="10"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="193">
-        <f t="shared" si="12"/>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="83">
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="B38" s="194" t="s">
+      <c r="B38" s="130" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="195" t="s">
+      <c r="C38" s="78" t="s">
         <v>136</v>
       </c>
       <c r="D38" s="77"/>
@@ -5417,55 +5440,53 @@
         <v>0.44</v>
       </c>
       <c r="F38" s="63">
-        <v>24889.25</v>
-      </c>
-      <c r="G38" s="63">
-        <v>0</v>
-      </c>
+        <v>53808.25</v>
+      </c>
+      <c r="G38" s="199"/>
       <c r="H38" s="75">
-        <f t="shared" si="0"/>
-        <v>24889.25</v>
+        <f t="shared" si="1"/>
+        <v>53808.25</v>
       </c>
       <c r="I38" s="75">
-        <f t="shared" si="3"/>
-        <v>746.67750000000001</v>
+        <f t="shared" si="4"/>
+        <v>1614.2474999999999</v>
       </c>
       <c r="J38" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>21589.435032000001</v>
       </c>
       <c r="K38" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L38" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>804.421244</v>
       </c>
       <c r="M38" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5777.8682280000012</v>
       </c>
       <c r="N38" s="82"/>
       <c r="O38" s="76">
-        <f t="shared" si="7"/>
-        <v>53808.25</v>
+        <f t="shared" si="8"/>
+        <v>83594.25</v>
       </c>
       <c r="P38" s="91">
+        <f t="shared" si="13"/>
+        <v>86102.25</v>
+      </c>
+      <c r="Q38" s="40">
         <f t="shared" si="11"/>
-        <v>55422.25</v>
-      </c>
-      <c r="Q38" s="40">
-        <f t="shared" si="10"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="R38" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>26</v>
       </c>
       <c r="B39" s="130" t="s">
@@ -5479,53 +5500,53 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F39" s="63">
-        <v>41250.26</v>
-      </c>
-      <c r="G39" s="63">
-        <f>F39</f>
-        <v>41250.26</v>
+        <v>35215.26</v>
+      </c>
+      <c r="G39" s="199">
+        <f t="shared" ref="G39:G40" si="15">F39</f>
+        <v>35215.26</v>
       </c>
       <c r="H39" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I39" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J39" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26986.793790000003</v>
       </c>
       <c r="K39" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L39" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1005.526555</v>
       </c>
       <c r="M39" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7222.335285000001</v>
       </c>
       <c r="N39" s="82"/>
       <c r="O39" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>35215.26</v>
       </c>
       <c r="P39" s="91">
+        <f t="shared" si="13"/>
+        <v>36271.26</v>
+      </c>
+      <c r="Q39" s="40">
         <f t="shared" si="11"/>
-        <v>36271.26</v>
-      </c>
-      <c r="Q39" s="40">
-        <f t="shared" si="10"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>27</v>
       </c>
       <c r="B40" s="130" t="s">
@@ -5539,52 +5560,53 @@
         <v>0.53</v>
       </c>
       <c r="F40" s="63">
-        <v>39750.269999999997</v>
-      </c>
-      <c r="G40" s="63">
-        <v>40943.269999999997</v>
+        <v>32741.27</v>
+      </c>
+      <c r="G40" s="199">
+        <f t="shared" si="15"/>
+        <v>32741.27</v>
       </c>
       <c r="H40" s="75">
-        <f t="shared" si="0"/>
-        <v>-1193</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I40" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J40" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26005.455834000004</v>
       </c>
       <c r="K40" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L40" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>968.96195300000011</v>
       </c>
       <c r="M40" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6959.7049110000007</v>
       </c>
       <c r="N40" s="82"/>
       <c r="O40" s="76">
-        <f t="shared" si="7"/>
-        <v>32741.27</v>
+        <f t="shared" si="8"/>
+        <v>33934.269999999997</v>
       </c>
       <c r="P40" s="91">
+        <f t="shared" si="13"/>
+        <v>34952.269999999997</v>
+      </c>
+      <c r="Q40" s="40">
         <f t="shared" si="11"/>
-        <v>33723.270000000004</v>
-      </c>
-      <c r="Q40" s="40">
-        <f t="shared" si="10"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="B41" s="130" t="s">
@@ -5594,59 +5616,56 @@
         <v>138</v>
       </c>
       <c r="D41" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E41" s="74">
         <v>0.28999999999999998</v>
       </c>
       <c r="F41" s="63">
-        <v>19828.28</v>
-      </c>
-      <c r="G41" s="63">
-        <f>F41</f>
-        <v>19828.28</v>
-      </c>
+        <v>18568.28</v>
+      </c>
+      <c r="G41" s="63"/>
       <c r="H41" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>18568.28</v>
       </c>
       <c r="I41" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>557.0483999999999</v>
       </c>
       <c r="J41" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14229.400362</v>
       </c>
       <c r="K41" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L41" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>530.18672900000001</v>
       </c>
       <c r="M41" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3808.1404230000003</v>
       </c>
       <c r="N41" s="82"/>
       <c r="O41" s="76">
-        <f t="shared" si="7"/>
-        <v>18568.28</v>
+        <f t="shared" si="8"/>
+        <v>37693.279999999999</v>
       </c>
       <c r="P41" s="91">
+        <f t="shared" si="13"/>
+        <v>38824.28</v>
+      </c>
+      <c r="Q41" s="40">
         <f t="shared" si="11"/>
-        <v>19125.28</v>
-      </c>
-      <c r="Q41" s="40">
-        <f t="shared" si="10"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
       <c r="B42" s="130" t="s">
@@ -5656,59 +5675,59 @@
         <v>125</v>
       </c>
       <c r="D42" s="77" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E42" s="74">
         <v>0.08</v>
       </c>
       <c r="F42" s="63">
-        <v>6000.29</v>
-      </c>
-      <c r="G42" s="63">
-        <f>F42</f>
-        <v>6000.29</v>
+        <v>5122.29</v>
+      </c>
+      <c r="G42" s="199">
+        <f t="shared" ref="G42:G43" si="16">F42</f>
+        <v>5122.29</v>
       </c>
       <c r="H42" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I42" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J42" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3925.3518240000003</v>
       </c>
       <c r="K42" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L42" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
       <c r="M42" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1050.5214960000001</v>
       </c>
       <c r="N42" s="82"/>
       <c r="O42" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5122.29</v>
       </c>
       <c r="P42" s="91">
+        <f t="shared" si="13"/>
+        <v>5276.29</v>
+      </c>
+      <c r="Q42" s="40">
         <f t="shared" si="11"/>
-        <v>5276.29</v>
-      </c>
-      <c r="Q42" s="40">
-        <f t="shared" si="10"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B43" s="130" t="s">
@@ -5722,52 +5741,53 @@
         <v>0.08</v>
       </c>
       <c r="F43" s="63">
-        <v>6000.3</v>
-      </c>
-      <c r="G43" s="63">
-        <v>6180.3</v>
+        <v>4942.3</v>
+      </c>
+      <c r="G43" s="199">
+        <f t="shared" si="16"/>
+        <v>4942.3</v>
       </c>
       <c r="H43" s="75">
-        <f t="shared" si="0"/>
-        <v>-180</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I43" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J43" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3925.3518240000003</v>
       </c>
       <c r="K43" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L43" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
       <c r="M43" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1050.5214960000001</v>
       </c>
       <c r="N43" s="82"/>
       <c r="O43" s="76">
-        <f t="shared" si="7"/>
-        <v>4942.3</v>
+        <f t="shared" si="8"/>
+        <v>5122.3</v>
       </c>
       <c r="P43" s="91">
+        <f t="shared" si="13"/>
+        <v>5276.3</v>
+      </c>
+      <c r="Q43" s="40">
         <f t="shared" si="11"/>
-        <v>5090.3</v>
-      </c>
-      <c r="Q43" s="40">
-        <f t="shared" si="10"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>31</v>
       </c>
       <c r="B44" s="130" t="s">
@@ -5777,62 +5797,62 @@
         <v>120</v>
       </c>
       <c r="D44" s="77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E44" s="74">
         <v>0.08</v>
       </c>
       <c r="F44" s="63">
-        <v>11705.31</v>
-      </c>
-      <c r="G44" s="63">
+        <v>5122.3100000000004</v>
+      </c>
+      <c r="G44" s="199">
         <f>F44</f>
-        <v>11705.31</v>
+        <v>5122.3100000000004</v>
       </c>
       <c r="H44" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I44" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J44" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3925.3518240000003</v>
       </c>
       <c r="K44" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L44" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
       <c r="M44" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1050.5214960000001</v>
       </c>
       <c r="N44" s="82"/>
       <c r="O44" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5122.3100000000004</v>
       </c>
       <c r="P44" s="91">
+        <f t="shared" si="13"/>
+        <v>5276.31</v>
+      </c>
+      <c r="Q44" s="40">
         <f t="shared" si="11"/>
-        <v>5276.31</v>
-      </c>
-      <c r="Q44" s="40">
-        <f t="shared" si="10"/>
         <v>0.31000000000000011</v>
       </c>
       <c r="R44" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>32</v>
       </c>
       <c r="B45" s="130" t="s">
@@ -5846,53 +5866,53 @@
         <v>0.08</v>
       </c>
       <c r="F45" s="63">
-        <v>6000.32</v>
-      </c>
-      <c r="G45" s="63">
+        <v>5122.32</v>
+      </c>
+      <c r="G45" s="199">
         <f>F45</f>
-        <v>6000.32</v>
+        <v>5122.32</v>
       </c>
       <c r="H45" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I45" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J45" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3925.3518240000003</v>
       </c>
       <c r="K45" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L45" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
       <c r="M45" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1050.5214960000001</v>
       </c>
       <c r="N45" s="82"/>
       <c r="O45" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5122.32</v>
       </c>
       <c r="P45" s="91">
+        <f t="shared" si="13"/>
+        <v>5276.32</v>
+      </c>
+      <c r="Q45" s="40">
         <f t="shared" si="11"/>
-        <v>5276.32</v>
-      </c>
-      <c r="Q45" s="40">
-        <f t="shared" si="10"/>
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>33</v>
       </c>
       <c r="B46" s="130" t="s">
@@ -5906,47 +5926,47 @@
         <v>0.08</v>
       </c>
       <c r="F46" s="63">
-        <v>18312.330000000002</v>
+        <v>23434.33</v>
       </c>
       <c r="G46" s="63"/>
       <c r="H46" s="75">
-        <f t="shared" si="0"/>
-        <v>18312.330000000002</v>
+        <f t="shared" si="1"/>
+        <v>23434.33</v>
       </c>
       <c r="I46" s="75"/>
       <c r="J46" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3925.3518240000003</v>
       </c>
       <c r="K46" s="82">
-        <f t="shared" ref="K46:K59" si="13">F$2*E46/100</f>
+        <f t="shared" ref="K46:K59" si="17">F$2*E46/100</f>
         <v>0</v>
       </c>
       <c r="L46" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
       <c r="M46" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1050.5214960000001</v>
       </c>
       <c r="N46" s="82"/>
       <c r="O46" s="76">
-        <f t="shared" si="7"/>
-        <v>23434.33</v>
+        <f t="shared" si="8"/>
+        <v>28556.33</v>
       </c>
       <c r="P46" s="91">
+        <f t="shared" si="13"/>
+        <v>29413.33</v>
+      </c>
+      <c r="Q46" s="40">
         <f t="shared" si="11"/>
-        <v>24137.33</v>
-      </c>
-      <c r="Q46" s="40">
-        <f t="shared" si="10"/>
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>34</v>
       </c>
       <c r="B47" s="130" t="s">
@@ -5960,53 +5980,53 @@
         <v>0.08</v>
       </c>
       <c r="F47" s="63">
-        <v>6000.34</v>
-      </c>
-      <c r="G47" s="63">
+        <v>5122.34</v>
+      </c>
+      <c r="G47" s="199">
         <f>F47</f>
-        <v>6000.34</v>
+        <v>5122.34</v>
       </c>
       <c r="H47" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I47" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J47" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3925.3518240000003</v>
       </c>
       <c r="K47" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L47" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>146.25840800000003</v>
       </c>
       <c r="M47" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1050.5214960000001</v>
       </c>
       <c r="N47" s="82"/>
       <c r="O47" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5122.34</v>
       </c>
       <c r="P47" s="91">
+        <f t="shared" si="13"/>
+        <v>5276.34</v>
+      </c>
+      <c r="Q47" s="40">
         <f t="shared" si="11"/>
-        <v>5276.34</v>
-      </c>
-      <c r="Q47" s="40">
-        <f t="shared" si="10"/>
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="121">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>35</v>
       </c>
       <c r="B48" s="130" t="s">
@@ -6020,52 +6040,50 @@
         <v>0.09</v>
       </c>
       <c r="F48" s="63">
-        <v>13563.35</v>
-      </c>
-      <c r="G48" s="63">
-        <v>13563.35</v>
-      </c>
+        <v>5762.35</v>
+      </c>
+      <c r="G48" s="63"/>
       <c r="H48" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>5762.35</v>
       </c>
       <c r="I48" s="125">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>172.87049999999999</v>
       </c>
       <c r="J48" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4416.020802</v>
       </c>
       <c r="K48" s="126">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L48" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>164.54070899999999</v>
       </c>
       <c r="M48" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1181.836683</v>
       </c>
       <c r="N48" s="126"/>
       <c r="O48" s="76">
-        <f t="shared" si="7"/>
-        <v>5762.35</v>
+        <f t="shared" si="8"/>
+        <v>11698.35</v>
       </c>
       <c r="P48" s="91">
+        <f t="shared" si="13"/>
+        <v>12049.35</v>
+      </c>
+      <c r="Q48" s="40">
         <f t="shared" si="11"/>
-        <v>5935.35</v>
-      </c>
-      <c r="Q48" s="40">
-        <f t="shared" si="10"/>
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="B49" s="130" t="s">
@@ -6079,53 +6097,53 @@
         <v>0.79</v>
       </c>
       <c r="F49" s="63">
-        <v>59250.36</v>
-      </c>
-      <c r="G49" s="63">
+        <v>50581.36</v>
+      </c>
+      <c r="G49" s="199">
         <f>F49</f>
-        <v>59250.36</v>
+        <v>50581.36</v>
       </c>
       <c r="H49" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I49" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J49" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>38762.849262000003</v>
       </c>
       <c r="K49" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L49" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1444.3017790000001</v>
       </c>
       <c r="M49" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10373.899773000001</v>
       </c>
       <c r="N49" s="82"/>
       <c r="O49" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50581.36</v>
       </c>
       <c r="P49" s="91">
+        <f t="shared" si="13"/>
+        <v>52098.36</v>
+      </c>
+      <c r="Q49" s="40">
         <f t="shared" si="11"/>
-        <v>52098.36</v>
-      </c>
-      <c r="Q49" s="40">
-        <f t="shared" si="10"/>
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>37</v>
       </c>
       <c r="B50" s="130" t="s">
@@ -6139,50 +6157,50 @@
         <v>1</v>
       </c>
       <c r="F50" s="63">
-        <v>233509.37</v>
+        <v>304541.37</v>
       </c>
       <c r="G50" s="63"/>
       <c r="H50" s="75">
-        <f t="shared" si="0"/>
-        <v>233509.37</v>
+        <f t="shared" si="1"/>
+        <v>304541.37</v>
       </c>
       <c r="I50" s="75">
-        <f t="shared" si="3"/>
-        <v>7005.2810999999992</v>
+        <f t="shared" si="4"/>
+        <v>9136.2410999999993</v>
       </c>
       <c r="J50" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>49066.897800000006</v>
       </c>
       <c r="K50" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L50" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1828.2301</v>
       </c>
       <c r="M50" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13131.518700000001</v>
       </c>
       <c r="N50" s="82"/>
       <c r="O50" s="76">
-        <f t="shared" si="7"/>
-        <v>304541.37</v>
+        <f t="shared" si="8"/>
+        <v>377704.37</v>
       </c>
       <c r="P50" s="91">
+        <f t="shared" si="13"/>
+        <v>389035.37</v>
+      </c>
+      <c r="Q50" s="40">
         <f t="shared" si="11"/>
-        <v>313677.37</v>
-      </c>
-      <c r="Q50" s="40">
-        <f t="shared" si="10"/>
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>38</v>
       </c>
       <c r="B51" s="130" t="s">
@@ -6196,53 +6214,53 @@
         <v>0.97</v>
       </c>
       <c r="F51" s="63">
-        <v>72750.38</v>
-      </c>
-      <c r="G51" s="63">
+        <v>62106.38</v>
+      </c>
+      <c r="G51" s="199">
         <f>F51</f>
-        <v>72750.38</v>
+        <v>62106.38</v>
       </c>
       <c r="H51" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I51" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J51" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>47594.890866000002</v>
       </c>
       <c r="K51" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L51" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1773.3831969999999</v>
       </c>
       <c r="M51" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12737.573139000002</v>
       </c>
       <c r="N51" s="82"/>
       <c r="O51" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>62106.38</v>
       </c>
       <c r="P51" s="91">
+        <f t="shared" si="13"/>
+        <v>63969.38</v>
+      </c>
+      <c r="Q51" s="40">
         <f t="shared" si="11"/>
-        <v>63969.38</v>
-      </c>
-      <c r="Q51" s="40">
-        <f t="shared" si="10"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>39</v>
       </c>
       <c r="B52" s="130" t="s">
@@ -6256,55 +6274,55 @@
         <v>0.77</v>
       </c>
       <c r="F52" s="63">
-        <v>58231.39</v>
-      </c>
-      <c r="G52" s="63">
-        <v>0</v>
+        <v>109279.39</v>
+      </c>
+      <c r="G52" s="199">
+        <v>8160</v>
       </c>
       <c r="H52" s="75">
-        <f t="shared" si="0"/>
-        <v>58231.39</v>
+        <f t="shared" si="1"/>
+        <v>101119.39</v>
       </c>
       <c r="I52" s="75">
-        <f t="shared" si="3"/>
-        <v>1746.9416999999999</v>
+        <f t="shared" si="4"/>
+        <v>3033.5816999999997</v>
       </c>
       <c r="J52" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37781.511306</v>
       </c>
       <c r="K52" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L52" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
       <c r="M52" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10111.269399000001</v>
       </c>
       <c r="N52" s="82"/>
       <c r="O52" s="76">
-        <f t="shared" si="7"/>
-        <v>109279.39</v>
+        <f t="shared" si="8"/>
+        <v>153453.39000000001</v>
       </c>
       <c r="P52" s="91">
+        <f t="shared" si="13"/>
+        <v>158057.39000000001</v>
+      </c>
+      <c r="Q52" s="40">
         <f t="shared" si="11"/>
-        <v>112557.39</v>
-      </c>
-      <c r="Q52" s="40">
-        <f t="shared" si="10"/>
         <v>0.39000000000000018</v>
       </c>
       <c r="R52" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>40</v>
       </c>
       <c r="B53" s="130" t="s">
@@ -6314,59 +6332,59 @@
         <v>142</v>
       </c>
       <c r="D53" s="77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E53" s="74">
         <v>0.77</v>
       </c>
       <c r="F53" s="63">
-        <v>57750.400000000001</v>
-      </c>
-      <c r="G53" s="63">
+        <v>49301.4</v>
+      </c>
+      <c r="G53" s="199">
         <f>F53</f>
-        <v>57750.400000000001</v>
+        <v>49301.4</v>
       </c>
       <c r="H53" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I53" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J53" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37781.511306</v>
       </c>
       <c r="K53" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L53" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
       <c r="M53" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10111.269399000001</v>
       </c>
       <c r="N53" s="82"/>
       <c r="O53" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>49301.4</v>
       </c>
       <c r="P53" s="91">
+        <f t="shared" si="13"/>
+        <v>50780.4</v>
+      </c>
+      <c r="Q53" s="40">
         <f t="shared" si="11"/>
-        <v>50780.4</v>
-      </c>
-      <c r="Q53" s="40">
-        <f t="shared" si="10"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>41</v>
       </c>
       <c r="B54" s="130" t="s">
@@ -6376,59 +6394,58 @@
         <v>121</v>
       </c>
       <c r="D54" s="77" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E54" s="74">
         <v>0.81</v>
       </c>
       <c r="F54" s="63">
-        <v>60750.41</v>
+        <v>51862.41</v>
       </c>
       <c r="G54" s="63">
-        <f>F54</f>
-        <v>60750.41</v>
+        <v>0</v>
       </c>
       <c r="H54" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>51862.41</v>
       </c>
       <c r="I54" s="75">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1555.8723</v>
       </c>
       <c r="J54" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39744.187218000006</v>
       </c>
       <c r="K54" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L54" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1480.866381</v>
       </c>
       <c r="M54" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10636.530147000001</v>
       </c>
       <c r="N54" s="82"/>
       <c r="O54" s="76">
-        <f t="shared" si="7"/>
-        <v>51862.41</v>
+        <f t="shared" si="8"/>
+        <v>105280.41</v>
       </c>
       <c r="P54" s="91">
+        <f t="shared" si="13"/>
+        <v>108438.41</v>
+      </c>
+      <c r="Q54" s="40">
         <f t="shared" si="11"/>
-        <v>53418.41</v>
-      </c>
-      <c r="Q54" s="40">
-        <f t="shared" si="10"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="B55" s="130" t="s">
@@ -6438,59 +6455,59 @@
         <v>142</v>
       </c>
       <c r="D55" s="77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E55" s="74">
         <v>0.77</v>
       </c>
       <c r="F55" s="63">
-        <v>57750.42</v>
-      </c>
-      <c r="G55" s="63">
+        <v>49301.42</v>
+      </c>
+      <c r="G55" s="199">
         <f>F55</f>
-        <v>57750.42</v>
+        <v>49301.42</v>
       </c>
       <c r="H55" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I55" s="75"/>
       <c r="J55" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37781.511306</v>
       </c>
       <c r="K55" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L55" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
       <c r="M55" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10111.269399000001</v>
       </c>
       <c r="N55" s="82"/>
       <c r="O55" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>49301.42</v>
       </c>
       <c r="P55" s="91">
+        <f t="shared" si="13"/>
+        <v>50780.42</v>
+      </c>
+      <c r="Q55" s="40">
         <f t="shared" si="11"/>
-        <v>50780.42</v>
-      </c>
-      <c r="Q55" s="40">
-        <f t="shared" si="10"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="R55" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>43</v>
       </c>
       <c r="B56" s="130" t="s">
@@ -6504,50 +6521,50 @@
         <v>0.77</v>
       </c>
       <c r="F56" s="63">
-        <v>177845.43</v>
+        <v>232481.43</v>
       </c>
       <c r="G56" s="63"/>
       <c r="H56" s="75">
-        <f t="shared" si="0"/>
-        <v>177845.43</v>
+        <f t="shared" si="1"/>
+        <v>232481.43</v>
       </c>
       <c r="I56" s="75">
-        <f t="shared" si="3"/>
-        <v>5335.3628999999992</v>
+        <f t="shared" si="4"/>
+        <v>6974.4428999999991</v>
       </c>
       <c r="J56" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37781.511306</v>
       </c>
       <c r="K56" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L56" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
       <c r="M56" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10111.269399000001</v>
       </c>
       <c r="N56" s="82"/>
       <c r="O56" s="76">
-        <f t="shared" si="7"/>
-        <v>232481.43</v>
+        <f t="shared" si="8"/>
+        <v>288756.43</v>
       </c>
       <c r="P56" s="91">
+        <f t="shared" si="13"/>
+        <v>297419.43</v>
+      </c>
+      <c r="Q56" s="40">
         <f t="shared" si="11"/>
-        <v>239455.43</v>
-      </c>
-      <c r="Q56" s="40">
-        <f t="shared" si="10"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>44</v>
       </c>
       <c r="B57" s="130" t="s">
@@ -6561,50 +6578,50 @@
         <v>0.77</v>
       </c>
       <c r="F57" s="63">
-        <v>112564.44</v>
+        <v>165242.44</v>
       </c>
       <c r="G57" s="63"/>
       <c r="H57" s="75">
-        <f t="shared" si="0"/>
-        <v>112564.44</v>
+        <f t="shared" si="1"/>
+        <v>165242.44</v>
       </c>
       <c r="I57" s="75">
-        <f t="shared" si="3"/>
-        <v>3376.9331999999999</v>
+        <f t="shared" si="4"/>
+        <v>4957.2731999999996</v>
       </c>
       <c r="J57" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37781.511306</v>
       </c>
       <c r="K57" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L57" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
       <c r="M57" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10111.269399000001</v>
       </c>
       <c r="N57" s="82"/>
       <c r="O57" s="76">
-        <f t="shared" si="7"/>
-        <v>165242.44</v>
+        <f t="shared" si="8"/>
+        <v>219500.44</v>
       </c>
       <c r="P57" s="91">
+        <f t="shared" si="13"/>
+        <v>226085.44</v>
+      </c>
+      <c r="Q57" s="40">
         <f t="shared" si="11"/>
-        <v>170199.44</v>
-      </c>
-      <c r="Q57" s="40">
-        <f t="shared" si="10"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>45</v>
       </c>
       <c r="B58" s="130" t="s">
@@ -6614,59 +6631,59 @@
         <v>121</v>
       </c>
       <c r="D58" s="77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E58" s="74">
         <v>0.77</v>
       </c>
       <c r="F58" s="63">
-        <v>57750.45</v>
-      </c>
-      <c r="G58" s="63">
-        <f>F58</f>
-        <v>57750.45</v>
+        <v>49301.45</v>
+      </c>
+      <c r="G58" s="199">
+        <f t="shared" ref="G58" si="18">F58</f>
+        <v>49301.45</v>
       </c>
       <c r="H58" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I58" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J58" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37781.511306</v>
       </c>
       <c r="K58" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L58" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1407.737177</v>
       </c>
       <c r="M58" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10111.269399000001</v>
       </c>
       <c r="N58" s="82"/>
       <c r="O58" s="76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>49301.45</v>
       </c>
       <c r="P58" s="91">
+        <f t="shared" si="13"/>
+        <v>50780.45</v>
+      </c>
+      <c r="Q58" s="40">
         <f t="shared" si="11"/>
-        <v>50780.45</v>
-      </c>
-      <c r="Q58" s="40">
-        <f t="shared" si="10"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>46</v>
       </c>
       <c r="B59" s="130" t="s">
@@ -6680,53 +6697,54 @@
         <v>0.86</v>
       </c>
       <c r="F59" s="63">
-        <v>71628.460000000006</v>
-      </c>
-      <c r="G59" s="63">
-        <v>0</v>
+        <v>128840.46</v>
+      </c>
+      <c r="G59" s="199">
+        <f>137000-8160</f>
+        <v>128840</v>
       </c>
       <c r="H59" s="75">
-        <f t="shared" si="0"/>
-        <v>71628.460000000006</v>
+        <f t="shared" si="1"/>
+        <v>0.46000000000640284</v>
       </c>
       <c r="I59" s="75">
-        <f t="shared" si="3"/>
-        <v>2148.8538000000003</v>
+        <f t="shared" si="4"/>
+        <v>1.3800000000192084E-2</v>
       </c>
       <c r="J59" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>42197.532108000007</v>
       </c>
       <c r="K59" s="82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L59" s="82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1572.2778860000001</v>
       </c>
       <c r="M59" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11293.106082000002</v>
       </c>
       <c r="N59" s="82"/>
       <c r="O59" s="76">
-        <f t="shared" si="7"/>
-        <v>128840.46</v>
+        <f t="shared" si="8"/>
+        <v>55063.46</v>
       </c>
       <c r="P59" s="91">
+        <f t="shared" si="13"/>
+        <v>56715.46</v>
+      </c>
+      <c r="Q59" s="40">
         <f t="shared" si="11"/>
-        <v>132705.46000000002</v>
-      </c>
-      <c r="Q59" s="40">
-        <f t="shared" si="10"/>
         <v>0.46000000000000024</v>
       </c>
       <c r="R59" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="83"/>
       <c r="B60" s="130"/>
       <c r="C60" s="72"/>
@@ -6745,160 +6763,156 @@
       <c r="P60" s="91"/>
       <c r="Q60" s="40"/>
     </row>
-    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="84"/>
       <c r="B61" s="131"/>
       <c r="C61" s="85"/>
       <c r="D61" s="85"/>
       <c r="E61" s="86">
-        <f t="shared" ref="E61:M61" si="14">SUM(E14:E60)</f>
+        <f t="shared" ref="E61:M61" si="19">SUM(E14:E60)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="F61" s="87">
-        <f t="shared" si="14"/>
-        <v>9639381.8099999987</v>
+        <f t="shared" si="19"/>
+        <v>9178994.8100000005</v>
       </c>
       <c r="G61" s="88">
         <f>SUM(G14:G60)</f>
-        <v>6991775.4199999999</v>
+        <v>5479535.0300000003</v>
       </c>
       <c r="H61" s="88">
-        <f t="shared" si="14"/>
-        <v>2647606.39</v>
+        <f t="shared" si="19"/>
+        <v>3699459.7800000003</v>
       </c>
       <c r="I61" s="88">
-        <f t="shared" si="14"/>
-        <v>85208.790299999979</v>
+        <f t="shared" si="19"/>
+        <v>111777.23309999998</v>
       </c>
       <c r="J61" s="89">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>4906689.7799999956</v>
       </c>
       <c r="K61" s="89">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L61" s="89">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>182823.00999999992</v>
       </c>
       <c r="M61" s="89">
-        <f t="shared" si="14"/>
+        <f t="shared" si="19"/>
         <v>1313151.8700000008</v>
       </c>
       <c r="N61" s="90"/>
       <c r="O61" s="95">
         <f>SUM(O14:O60)</f>
-        <v>9178994.8100000005</v>
+        <v>10257414.809999999</v>
       </c>
       <c r="P61" s="92">
         <f>SUM(P14:P60)</f>
-        <v>9454363.8100000005</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10565140.810000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="64"/>
       <c r="D62" s="64"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C64" s="232" t="s">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="232"/>
-      <c r="E64" s="232"/>
-      <c r="F64" s="232"/>
-      <c r="G64" s="232"/>
-      <c r="H64" s="232"/>
-      <c r="I64" s="232"/>
-      <c r="J64" s="232"/>
-      <c r="K64" s="232"/>
-      <c r="L64" s="232"/>
-      <c r="M64" s="232"/>
-      <c r="N64" s="232"/>
-      <c r="O64" s="232"/>
-    </row>
-    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="232"/>
-      <c r="D65" s="232"/>
-      <c r="E65" s="232"/>
-      <c r="F65" s="232"/>
-      <c r="G65" s="232"/>
-      <c r="H65" s="232"/>
-      <c r="I65" s="232"/>
-      <c r="J65" s="232"/>
-      <c r="K65" s="232"/>
-      <c r="L65" s="232"/>
-      <c r="M65" s="232"/>
-      <c r="N65" s="232"/>
-      <c r="O65" s="232"/>
-    </row>
-    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="232"/>
-      <c r="D66" s="232"/>
-      <c r="E66" s="232"/>
-      <c r="F66" s="232"/>
-      <c r="G66" s="232"/>
-      <c r="H66" s="232"/>
-      <c r="I66" s="232"/>
-      <c r="J66" s="232"/>
-      <c r="K66" s="232"/>
-      <c r="L66" s="232"/>
-      <c r="M66" s="232"/>
-      <c r="N66" s="232"/>
-      <c r="O66" s="232"/>
-    </row>
-    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="232"/>
-      <c r="D67" s="232"/>
-      <c r="E67" s="232"/>
-      <c r="F67" s="232"/>
-      <c r="G67" s="232"/>
-      <c r="H67" s="232"/>
-      <c r="I67" s="232"/>
-      <c r="J67" s="232"/>
-      <c r="K67" s="232"/>
-      <c r="L67" s="232"/>
-      <c r="M67" s="232"/>
-      <c r="N67" s="232"/>
-      <c r="O67" s="232"/>
-    </row>
-    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="232"/>
-      <c r="D68" s="232"/>
-      <c r="E68" s="232"/>
-      <c r="F68" s="232"/>
-      <c r="G68" s="232"/>
-      <c r="H68" s="232"/>
-      <c r="I68" s="232"/>
-      <c r="J68" s="232"/>
-      <c r="K68" s="232"/>
-      <c r="L68" s="232"/>
-      <c r="M68" s="232"/>
-      <c r="N68" s="232"/>
-      <c r="O68" s="232"/>
-    </row>
-    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="232"/>
-      <c r="D69" s="232"/>
-      <c r="E69" s="232"/>
-      <c r="F69" s="232"/>
-      <c r="G69" s="232"/>
-      <c r="H69" s="232"/>
-      <c r="I69" s="232"/>
-      <c r="J69" s="232"/>
-      <c r="K69" s="232"/>
-      <c r="L69" s="232"/>
-      <c r="M69" s="232"/>
-      <c r="N69" s="232"/>
-      <c r="O69" s="232"/>
+      <c r="D64" s="230"/>
+      <c r="E64" s="230"/>
+      <c r="F64" s="230"/>
+      <c r="G64" s="230"/>
+      <c r="H64" s="230"/>
+      <c r="I64" s="230"/>
+      <c r="J64" s="230"/>
+      <c r="K64" s="230"/>
+      <c r="L64" s="230"/>
+      <c r="M64" s="230"/>
+      <c r="N64" s="230"/>
+      <c r="O64" s="230"/>
+    </row>
+    <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="230"/>
+      <c r="D65" s="230"/>
+      <c r="E65" s="230"/>
+      <c r="F65" s="230"/>
+      <c r="G65" s="230"/>
+      <c r="H65" s="230"/>
+      <c r="I65" s="230"/>
+      <c r="J65" s="230"/>
+      <c r="K65" s="230"/>
+      <c r="L65" s="230"/>
+      <c r="M65" s="230"/>
+      <c r="N65" s="230"/>
+      <c r="O65" s="230"/>
+    </row>
+    <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="230"/>
+      <c r="D66" s="230"/>
+      <c r="E66" s="230"/>
+      <c r="F66" s="230"/>
+      <c r="G66" s="230"/>
+      <c r="H66" s="230"/>
+      <c r="I66" s="230"/>
+      <c r="J66" s="230"/>
+      <c r="K66" s="230"/>
+      <c r="L66" s="230"/>
+      <c r="M66" s="230"/>
+      <c r="N66" s="230"/>
+      <c r="O66" s="230"/>
+    </row>
+    <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C67" s="230"/>
+      <c r="D67" s="230"/>
+      <c r="E67" s="230"/>
+      <c r="F67" s="230"/>
+      <c r="G67" s="230"/>
+      <c r="H67" s="230"/>
+      <c r="I67" s="230"/>
+      <c r="J67" s="230"/>
+      <c r="K67" s="230"/>
+      <c r="L67" s="230"/>
+      <c r="M67" s="230"/>
+      <c r="N67" s="230"/>
+      <c r="O67" s="230"/>
+    </row>
+    <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="230"/>
+      <c r="D68" s="230"/>
+      <c r="E68" s="230"/>
+      <c r="F68" s="230"/>
+      <c r="G68" s="230"/>
+      <c r="H68" s="230"/>
+      <c r="I68" s="230"/>
+      <c r="J68" s="230"/>
+      <c r="K68" s="230"/>
+      <c r="L68" s="230"/>
+      <c r="M68" s="230"/>
+      <c r="N68" s="230"/>
+      <c r="O68" s="230"/>
+    </row>
+    <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="230"/>
+      <c r="D69" s="230"/>
+      <c r="E69" s="230"/>
+      <c r="F69" s="230"/>
+      <c r="G69" s="230"/>
+      <c r="H69" s="230"/>
+      <c r="I69" s="230"/>
+      <c r="J69" s="230"/>
+      <c r="K69" s="230"/>
+      <c r="L69" s="230"/>
+      <c r="M69" s="230"/>
+      <c r="N69" s="230"/>
+      <c r="O69" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -6915,6 +6929,10 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6925,16 +6943,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="C3:L17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="20"/>
     </row>
-    <row r="4" spans="3:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:12" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="116" t="s">
         <v>51</v>
       </c>
@@ -6950,7 +6968,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="3:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="118" t="s">
         <v>52</v>
       </c>
@@ -6962,10 +6980,10 @@
         <v>54</v>
       </c>
       <c r="J5" s="115"/>
-      <c r="K5" s="192"/>
+      <c r="K5" s="187"/>
       <c r="L5" s="20"/>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C6" s="118" t="s">
         <v>55</v>
       </c>
@@ -6979,51 +6997,51 @@
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="J6" s="115"/>
-      <c r="K6" s="192"/>
+      <c r="K6" s="187"/>
       <c r="L6" s="20"/>
     </row>
-    <row r="7" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C7" s="37" t="s">
         <v>58</v>
       </c>
       <c r="J7" s="115"/>
-      <c r="K7" s="192"/>
+      <c r="K7" s="187"/>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C8" s="256" t="s">
-        <v>202</v>
-      </c>
-      <c r="D8" s="257"/>
-      <c r="E8" s="257"/>
-      <c r="F8" s="257"/>
-      <c r="G8" s="257"/>
-      <c r="H8" s="257"/>
-      <c r="I8" s="257"/>
-      <c r="J8" s="258"/>
-      <c r="K8" s="192"/>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C8" s="265" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="266"/>
+      <c r="E8" s="266"/>
+      <c r="F8" s="266"/>
+      <c r="G8" s="266"/>
+      <c r="H8" s="266"/>
+      <c r="I8" s="266"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="187"/>
       <c r="L8" s="20"/>
     </row>
-    <row r="9" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="259"/>
-      <c r="D9" s="260"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="260"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="260"/>
-      <c r="I9" s="260"/>
-      <c r="J9" s="261"/>
-      <c r="K9" s="192"/>
-    </row>
-    <row r="11" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="200" t="s">
+    <row r="9" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="268"/>
+      <c r="D9" s="269"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="269"/>
+      <c r="G9" s="269"/>
+      <c r="H9" s="269"/>
+      <c r="I9" s="269"/>
+      <c r="J9" s="270"/>
+      <c r="K9" s="187"/>
+    </row>
+    <row r="11" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C12" s="188" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="201">
+      <c r="D12" s="189">
         <v>1</v>
       </c>
       <c r="E12" s="113"/>
@@ -7033,11 +7051,11 @@
       <c r="I12" s="113"/>
       <c r="J12" s="114"/>
     </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="202" t="s">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C13" s="190" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="203"/>
+      <c r="D13" s="191"/>
       <c r="E13" t="s">
         <v>53</v>
       </c>
@@ -7046,11 +7064,11 @@
       </c>
       <c r="J13" s="115"/>
     </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="202" t="s">
+    <row r="14" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="190" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="203" t="s">
+      <c r="D14" s="191" t="s">
         <v>56</v>
       </c>
       <c r="E14" t="s">
@@ -7064,33 +7082,33 @@
       </c>
       <c r="J14" s="115"/>
     </row>
-    <row r="15" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="37" t="s">
         <v>58</v>
       </c>
       <c r="J15" s="115"/>
     </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="256" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="257"/>
-      <c r="E16" s="257"/>
-      <c r="F16" s="257"/>
-      <c r="G16" s="257"/>
-      <c r="H16" s="257"/>
-      <c r="I16" s="257"/>
-      <c r="J16" s="258"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="259"/>
-      <c r="D17" s="260"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="260"/>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="I17" s="260"/>
-      <c r="J17" s="261"/>
+    <row r="16" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C16" s="265" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="266"/>
+      <c r="E16" s="266"/>
+      <c r="F16" s="266"/>
+      <c r="G16" s="266"/>
+      <c r="H16" s="266"/>
+      <c r="I16" s="266"/>
+      <c r="J16" s="267"/>
+    </row>
+    <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="268"/>
+      <c r="D17" s="269"/>
+      <c r="E17" s="269"/>
+      <c r="F17" s="269"/>
+      <c r="G17" s="269"/>
+      <c r="H17" s="269"/>
+      <c r="I17" s="269"/>
+      <c r="J17" s="270"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/O HIGGINS 1157/Julio/Julio ohiggins.xlsx
+++ b/2026/O HIGGINS 1157/Julio/Julio ohiggins.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\O HIGGINS 1157\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE81B44F-9D31-4085-9BAE-4361071264F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E004368-406D-4024-B3E9-450980F850AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$69</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$119</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="219">
   <si>
     <t>TOTAL</t>
   </si>
@@ -572,9 +572,6 @@
     <t>Haberes + SAC</t>
   </si>
   <si>
-    <t>Abono ascensor - ADS - No enviaron la factura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gastos bancarios </t>
   </si>
   <si>
@@ -594,9 +591,6 @@
   </si>
   <si>
     <t>FCI Super ahorro plus</t>
-  </si>
-  <si>
-    <t>Inicio 19/06/2026</t>
   </si>
   <si>
     <t>Egreso pago de metrogas</t>
@@ -688,6 +682,24 @@
   </si>
   <si>
     <t>Rescate FCI</t>
+  </si>
+  <si>
+    <t>Abono ascensor - ADS - Se abona el mes 5, se adeuda mes 6 y 7</t>
+  </si>
+  <si>
+    <t>Transf 30/07</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Interes generados</t>
+  </si>
+  <si>
+    <t>Inicio del mes</t>
+  </si>
+  <si>
+    <t>La caja nos da una diferencia de $60.000 pesos aprox que Cabrera le debe al consorcio de ohgiggins</t>
   </si>
 </sst>
 </file>
@@ -704,7 +716,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,13 +872,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -1477,7 +1482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1780,22 +1785,6 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="12" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="12" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1806,24 +1795,37 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="18" fillId="16" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="16" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="16" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="16" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="16" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="16" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="14" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1857,14 +1859,38 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1911,12 +1937,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1944,33 +1964,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1988,6 +1981,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="12" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2392,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2410,12 +2422,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="212" t="s">
+      <c r="B1" s="209" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
-      <c r="E1" s="213"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="210"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -2428,12 +2440,12 @@
     </row>
     <row r="3" spans="1:5" ht="56.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="216" t="s">
+      <c r="B3" s="211" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="216"/>
-      <c r="D3" s="216"/>
-      <c r="E3" s="217"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="211"/>
+      <c r="E3" s="212"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -2451,7 +2463,7 @@
         <v>59</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2461,7 +2473,7 @@
     </row>
     <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2471,54 +2483,54 @@
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="218" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="218"/>
+      <c r="B8" s="213" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="213"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="218"/>
-      <c r="C9" s="218"/>
+      <c r="B9" s="213"/>
+      <c r="C9" s="213"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="218"/>
-      <c r="C10" s="218"/>
+      <c r="B10" s="213"/>
+      <c r="C10" s="213"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="219" t="s">
+      <c r="A13" s="214" t="s">
         <v>144</v>
       </c>
-      <c r="B13" s="219"/>
-      <c r="C13" s="219"/>
-      <c r="D13" s="219"/>
-      <c r="E13" s="219"/>
+      <c r="B13" s="214"/>
+      <c r="C13" s="214"/>
+      <c r="D13" s="214"/>
+      <c r="E13" s="214"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="219"/>
-      <c r="B14" s="219"/>
-      <c r="C14" s="219"/>
-      <c r="D14" s="219"/>
-      <c r="E14" s="219"/>
+      <c r="A14" s="214"/>
+      <c r="B14" s="214"/>
+      <c r="C14" s="214"/>
+      <c r="D14" s="214"/>
+      <c r="E14" s="214"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="219"/>
-      <c r="B15" s="219"/>
-      <c r="C15" s="219"/>
-      <c r="D15" s="219"/>
-      <c r="E15" s="219"/>
+      <c r="A15" s="214"/>
+      <c r="B15" s="214"/>
+      <c r="C15" s="214"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="214"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="219"/>
-      <c r="B16" s="219"/>
-      <c r="C16" s="219"/>
-      <c r="D16" s="219"/>
-      <c r="E16" s="219"/>
+      <c r="A16" s="214"/>
+      <c r="B16" s="214"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="214"/>
+      <c r="E16" s="214"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2544,39 +2556,37 @@
       <c r="E21" s="97"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="220" t="s">
+      <c r="A22" s="215" t="s">
         <v>175</v>
       </c>
-      <c r="B22" s="221"/>
+      <c r="B22" s="216"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="197">
-        <v>1987270.86</v>
+      <c r="D22" s="263">
+        <v>1369114.12</v>
       </c>
       <c r="E22" s="98"/>
       <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="214" t="s">
+      <c r="A23" s="205" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="215"/>
+      <c r="B23" s="206"/>
       <c r="C23" s="152"/>
-      <c r="D23" s="197">
-        <v>-432231.42</v>
+      <c r="D23" s="263">
+        <v>-297782.12</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="38"/>
       <c r="H23" s="20"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="205" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="215"/>
+      <c r="B24" s="206"/>
       <c r="C24" s="152"/>
-      <c r="D24" s="198">
-        <v>0.34</v>
-      </c>
+      <c r="D24" s="264"/>
       <c r="E24" s="21"/>
       <c r="F24" s="38"/>
       <c r="H24" s="20"/>
@@ -2590,7 +2600,7 @@
       <c r="D25" s="22"/>
       <c r="E25" s="99">
         <f>SUM(D22:D24)</f>
-        <v>1555039.7800000003</v>
+        <v>1071332</v>
       </c>
       <c r="F25" s="38"/>
     </row>
@@ -2657,11 +2667,11 @@
       </c>
       <c r="B32" s="155"/>
       <c r="C32" s="155"/>
-      <c r="D32" s="193">
+      <c r="D32" s="28">
         <v>977145.51</v>
       </c>
       <c r="E32" s="101" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F32" s="38"/>
       <c r="G32" s="48"/>
@@ -2671,14 +2681,14 @@
         <v>147</v>
       </c>
       <c r="B33" s="152" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C33" s="155"/>
-      <c r="D33" s="193">
+      <c r="D33" s="28">
         <v>182823.01</v>
       </c>
       <c r="E33" s="101" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="48"/>
@@ -2689,11 +2699,11 @@
       </c>
       <c r="B34" s="155"/>
       <c r="C34" s="155"/>
-      <c r="D34" s="193">
+      <c r="D34" s="28">
         <v>89427.19</v>
       </c>
       <c r="E34" s="101" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="48"/>
@@ -2704,7 +2714,7 @@
       </c>
       <c r="B35" s="155"/>
       <c r="C35" s="155"/>
-      <c r="D35" s="193">
+      <c r="D35" s="28">
         <v>9936.35</v>
       </c>
       <c r="E35" s="101" t="str">
@@ -2720,7 +2730,7 @@
       </c>
       <c r="B36" s="155"/>
       <c r="C36" s="155"/>
-      <c r="D36" s="193">
+      <c r="D36" s="28">
         <v>160769.26</v>
       </c>
       <c r="E36" s="101" t="str">
@@ -2753,12 +2763,12 @@
       <c r="F38" s="38"/>
     </row>
     <row r="39" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="222" t="s">
+      <c r="A39" s="217" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="223"/>
+      <c r="B39" s="218"/>
       <c r="C39" s="156"/>
-      <c r="D39" s="196">
+      <c r="D39" s="265">
         <v>205033.71</v>
       </c>
       <c r="E39" s="21" t="s">
@@ -2767,12 +2777,12 @@
       <c r="F39" s="38"/>
     </row>
     <row r="40" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="222" t="s">
+      <c r="A40" s="217" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="223"/>
+      <c r="B40" s="218"/>
       <c r="C40" s="156"/>
-      <c r="D40" s="196">
+      <c r="D40" s="265">
         <f>1285.32+12020</f>
         <v>13305.32</v>
       </c>
@@ -2811,11 +2821,11 @@
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="192">
+      <c r="D43" s="133">
         <v>1705199.42</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F43" s="38"/>
     </row>
@@ -2825,25 +2835,25 @@
       </c>
       <c r="B44" s="157"/>
       <c r="C44" s="33"/>
-      <c r="D44" s="192">
+      <c r="D44" s="133">
         <v>7098.03</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F44" s="38"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="222" t="s">
+      <c r="A45" s="217" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="223"/>
+      <c r="B45" s="218"/>
       <c r="C45" s="33"/>
-      <c r="D45" s="192">
+      <c r="D45" s="133">
         <v>517937.8</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F45" s="38"/>
     </row>
@@ -2855,11 +2865,11 @@
         <v>174</v>
       </c>
       <c r="C46" s="33"/>
-      <c r="D46" s="192">
+      <c r="D46" s="133">
         <v>33772.550000000003</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F46" s="38"/>
     </row>
@@ -2887,383 +2897,386 @@
       <c r="F48" s="38"/>
     </row>
     <row r="49" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="214" t="s">
-        <v>176</v>
-      </c>
-      <c r="B49" s="215"/>
+      <c r="A49" s="205" t="s">
+        <v>213</v>
+      </c>
+      <c r="B49" s="206"/>
       <c r="C49" s="33"/>
       <c r="D49" s="133">
-        <v>0</v>
-      </c>
-      <c r="E49" s="27"/>
+        <v>298200</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>214</v>
+      </c>
       <c r="F49" s="38"/>
     </row>
     <row r="50" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="226" t="s">
-        <v>212</v>
-      </c>
-      <c r="B50" s="227"/>
+      <c r="A50" s="221" t="s">
+        <v>210</v>
+      </c>
+      <c r="B50" s="208"/>
       <c r="C50" s="152"/>
-      <c r="D50" s="192">
+      <c r="D50" s="133">
         <v>290000</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F50" s="134"/>
     </row>
     <row r="51" spans="1:6" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="222" t="s">
-        <v>198</v>
-      </c>
-      <c r="B51" s="223"/>
+      <c r="A51" s="217" t="s">
+        <v>196</v>
+      </c>
+      <c r="B51" s="218"/>
       <c r="C51" s="152"/>
-      <c r="D51" s="192">
+      <c r="D51" s="133">
         <v>110000</v>
       </c>
       <c r="E51" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F51" s="134"/>
+    </row>
+    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="219" t="s">
+        <v>194</v>
+      </c>
+      <c r="B52" s="220"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="133">
+        <v>95000</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F52" s="134"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="219" t="s">
         <v>195</v>
       </c>
-      <c r="F51" s="134"/>
-    </row>
-    <row r="52" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="224" t="s">
-        <v>196</v>
-      </c>
-      <c r="B52" s="225"/>
-      <c r="C52" s="152"/>
-      <c r="D52" s="192">
-        <v>95000</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F52" s="134"/>
-    </row>
-    <row r="53" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="224" t="s">
-        <v>197</v>
-      </c>
-      <c r="B53" s="225"/>
+      <c r="B53" s="220"/>
       <c r="C53" s="152"/>
-      <c r="D53" s="192">
+      <c r="D53" s="133">
         <v>35000</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F53" s="134"/>
     </row>
     <row r="54" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="222" t="s">
-        <v>203</v>
-      </c>
-      <c r="B54" s="223"/>
+      <c r="A54" s="217" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" s="218"/>
       <c r="C54" s="152"/>
-      <c r="D54" s="192">
+      <c r="D54" s="133">
         <v>390000</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F54" s="38"/>
     </row>
     <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="214" t="s">
-        <v>201</v>
-      </c>
-      <c r="B55" s="215"/>
+      <c r="A55" s="205" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" s="206"/>
       <c r="C55" s="152"/>
-      <c r="D55" s="192">
+      <c r="D55" s="133">
         <v>100000</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F55" s="38"/>
     </row>
-    <row r="56" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="161" t="s">
-        <v>194</v>
-      </c>
-      <c r="B56" s="160"/>
+    <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="202" t="s">
+        <v>215</v>
+      </c>
+      <c r="B56" s="203"/>
       <c r="C56" s="152"/>
-      <c r="D56" s="192">
+      <c r="D56" s="133">
+        <v>123200</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="F56" s="38"/>
+    </row>
+    <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="161" t="s">
+        <v>192</v>
+      </c>
+      <c r="B57" s="160"/>
+      <c r="C57" s="152"/>
+      <c r="D57" s="133">
         <v>261000</v>
       </c>
-      <c r="E56" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="F56" s="134"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="153" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="32">
-        <f>SUM(D49:D56)</f>
-        <v>1281000</v>
-      </c>
-      <c r="F57" s="38"/>
+      <c r="E57" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="F57" s="134"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="29" t="s">
-        <v>13</v>
+      <c r="A58" s="153" t="s">
+        <v>0</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="97"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="32">
+        <f>SUM(D49:D57)</f>
+        <v>1702400</v>
+      </c>
       <c r="F58" s="38"/>
     </row>
-    <row r="59" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="214" t="s">
-        <v>207</v>
-      </c>
-      <c r="B59" s="215"/>
-      <c r="C59" s="152"/>
-      <c r="D59" s="194">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="97"/>
+      <c r="F59" s="38"/>
+    </row>
+    <row r="60" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="205" t="s">
+        <v>205</v>
+      </c>
+      <c r="B60" s="206"/>
+      <c r="C60" s="152"/>
+      <c r="D60" s="266">
         <v>420000</v>
-      </c>
-      <c r="E59" s="98"/>
-      <c r="F59" s="38"/>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="161" t="s">
-        <v>206</v>
-      </c>
-      <c r="B60" s="160"/>
-      <c r="C60" s="152"/>
-      <c r="D60" s="195">
-        <v>50000</v>
       </c>
       <c r="E60" s="98"/>
       <c r="F60" s="38"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="153" t="s">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="161" t="s">
+        <v>204</v>
+      </c>
+      <c r="B61" s="160"/>
+      <c r="C61" s="152"/>
+      <c r="D61" s="267">
+        <v>50000</v>
+      </c>
+      <c r="E61" s="98"/>
+      <c r="F61" s="38"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="153"/>
-      <c r="C61" s="153"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="99">
-        <f>SUM(D59:D60)</f>
+      <c r="B62" s="153"/>
+      <c r="C62" s="153"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="99">
+        <f>SUM(D60:D61)</f>
         <v>470000</v>
       </c>
-      <c r="F61" s="38"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="29" t="s">
+      <c r="F62" s="38"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B62" s="162"/>
-      <c r="C62" s="153"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="38"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="163"/>
-      <c r="C63" s="163"/>
-      <c r="D63" s="164">
-        <v>69000</v>
-      </c>
-      <c r="E63" s="106"/>
+      <c r="B63" s="162"/>
+      <c r="C63" s="153"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="32"/>
       <c r="F63" s="38"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
-        <v>177</v>
+        <v>69</v>
       </c>
       <c r="B64" s="163"/>
       <c r="C64" s="163"/>
       <c r="D64" s="164">
-        <v>109681.94</v>
+        <v>69000</v>
       </c>
       <c r="E64" s="106"/>
       <c r="F64" s="38"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="165" t="s">
+      <c r="A65" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B65" s="163"/>
+      <c r="C65" s="163"/>
+      <c r="D65" s="164">
+        <v>110424.89</v>
+      </c>
+      <c r="E65" s="106"/>
+      <c r="F65" s="38"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="165"/>
-      <c r="C65" s="165"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="32">
-        <f>SUM(D63:D64)</f>
-        <v>178681.94</v>
-      </c>
-      <c r="F65" s="38"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="33"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="33"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="34"/>
+      <c r="B66" s="165"/>
+      <c r="C66" s="165"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="32">
+        <f>SUM(D64:D65)</f>
+        <v>179424.89</v>
+      </c>
       <c r="F66" s="38"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="166" t="s">
+      <c r="A67" s="33"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="33"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="38"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="166"/>
-      <c r="C67" s="166"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="38"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="167"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="134"/>
+      <c r="B68" s="166"/>
+      <c r="C68" s="166"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="38"/>
     </row>
     <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="168" t="s">
+      <c r="A69" s="167"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="134"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="B69" s="169"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="42">
-        <f>(SUM(E21:E67))</f>
-        <v>7387169.8700000001</v>
-      </c>
-      <c r="F69" s="170"/>
-      <c r="G69" s="40"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="38"/>
-      <c r="B70" s="38"/>
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="169"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="42">
+        <f>(SUM(E21:E68))</f>
+        <v>7325605.04</v>
+      </c>
+      <c r="F70" s="170"/>
+      <c r="G70" s="40"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="38"/>
       <c r="B71" s="38"/>
       <c r="C71" s="38"/>
       <c r="D71" s="38"/>
       <c r="E71" s="38"/>
       <c r="F71" s="38"/>
-      <c r="H71" s="44"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="171" t="s">
+    </row>
+    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="38"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="H72" s="44"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="B72" s="172"/>
-      <c r="C72" s="173"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="38"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="229"/>
-      <c r="B73" s="227"/>
-      <c r="C73" s="33"/>
-      <c r="D73" s="174"/>
-      <c r="E73" s="120"/>
+      <c r="B73" s="172"/>
+      <c r="C73" s="173"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="46"/>
       <c r="F73" s="38"/>
     </row>
-    <row r="74" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="38"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="38"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33"/>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="207"/>
+      <c r="B74" s="208"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="174"/>
+      <c r="E74" s="120"/>
       <c r="F74" s="38"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="175"/>
-      <c r="B75" s="176"/>
-      <c r="C75" s="33"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="47"/>
+    <row r="75" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="38"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
       <c r="F75" s="38"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="177" t="s">
+      <c r="A76" s="175"/>
+      <c r="B76" s="176"/>
+      <c r="C76" s="33"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="47"/>
+      <c r="F76" s="38"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="177" t="s">
         <v>44</v>
       </c>
-      <c r="B76" s="178"/>
-      <c r="C76" s="178"/>
-      <c r="D76" s="80"/>
-      <c r="E76" s="107">
-        <f>SUM(D73:D75)</f>
-        <v>0</v>
-      </c>
-      <c r="F76" s="38"/>
-    </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="38"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
+      <c r="B77" s="178"/>
+      <c r="C77" s="178"/>
+      <c r="D77" s="80"/>
+      <c r="E77" s="107">
+        <f>SUM(D74:D76)</f>
+        <v>0</v>
+      </c>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="166" t="s">
+    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="38"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B78" s="166"/>
-      <c r="C78" s="166"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="110">
-        <v>0</v>
-      </c>
-      <c r="F78" s="38"/>
-    </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="38"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
+      <c r="B79" s="166"/>
+      <c r="C79" s="166"/>
+      <c r="D79" s="35"/>
+      <c r="E79" s="110">
+        <v>0</v>
+      </c>
       <c r="F79" s="38"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="168" t="s">
+      <c r="A80" s="38"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="B80" s="169"/>
-      <c r="C80" s="41"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="42">
-        <f>E76+E78</f>
-        <v>0</v>
-      </c>
-      <c r="F80" s="38"/>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="38"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
+      <c r="B81" s="169"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="42">
+        <f>E77+E79</f>
+        <v>0</v>
+      </c>
       <c r="F81" s="38"/>
     </row>
     <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="179" t="s">
-        <v>20</v>
-      </c>
-      <c r="B82" s="180">
-        <f>E69</f>
-        <v>7387169.8700000001</v>
-      </c>
+      <c r="A82" s="38"/>
+      <c r="B82" s="38"/>
       <c r="C82" s="38"/>
       <c r="D82" s="38"/>
       <c r="E82" s="38"/>
@@ -3271,11 +3284,11 @@
     </row>
     <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="179" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B83" s="180">
-        <f>E69-E67</f>
-        <v>7387169.8700000001</v>
+        <f>E70</f>
+        <v>7325605.04</v>
       </c>
       <c r="C83" s="38"/>
       <c r="D83" s="38"/>
@@ -3284,11 +3297,11 @@
     </row>
     <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B84" s="180">
-        <f>E80-E78</f>
-        <v>0</v>
+        <f>E70-E68</f>
+        <v>7325605.04</v>
       </c>
       <c r="C84" s="38"/>
       <c r="D84" s="38"/>
@@ -3297,10 +3310,10 @@
     </row>
     <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="179" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B85" s="180">
-        <f>E80</f>
+        <f>E81-E79</f>
         <v>0</v>
       </c>
       <c r="C85" s="38"/>
@@ -3308,9 +3321,14 @@
       <c r="E85" s="38"/>
       <c r="F85" s="38"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="38"/>
-      <c r="B86" s="38"/>
+    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="179" t="s">
+        <v>23</v>
+      </c>
+      <c r="B86" s="180">
+        <f>E81</f>
+        <v>0</v>
+      </c>
       <c r="C86" s="38"/>
       <c r="D86" s="38"/>
       <c r="E86" s="38"/>
@@ -3325,111 +3343,109 @@
       <c r="F87" s="38"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="112" t="s">
-        <v>183</v>
-      </c>
-      <c r="B88" s="181">
-        <v>0</v>
-      </c>
+      <c r="A88" s="38"/>
+      <c r="B88" s="38"/>
       <c r="C88" s="38"/>
       <c r="D88" s="38"/>
       <c r="E88" s="38"/>
       <c r="F88" s="38"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="156" t="s">
-        <v>184</v>
-      </c>
-      <c r="B89" s="182">
-        <v>6500000</v>
+      <c r="A89" s="112" t="s">
+        <v>182</v>
+      </c>
+      <c r="B89" s="181">
+        <v>0</v>
       </c>
       <c r="C89" s="38"/>
       <c r="D89" s="38"/>
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="156" t="s">
-        <v>213</v>
-      </c>
-      <c r="B90" s="135">
-        <v>-1501954.93</v>
+        <v>217</v>
+      </c>
+      <c r="B90" s="182">
+        <v>6500000</v>
       </c>
       <c r="C90" s="38"/>
       <c r="D90" s="38"/>
       <c r="E90" s="38"/>
       <c r="F90" s="38"/>
     </row>
-    <row r="91" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="183" t="s">
-        <v>179</v>
-      </c>
-      <c r="B91" s="184">
-        <f>B89</f>
-        <v>6500000</v>
+    <row r="91" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="156" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="135">
+        <v>-1501954.93</v>
       </c>
       <c r="C91" s="38"/>
       <c r="D91" s="38"/>
       <c r="E91" s="38"/>
       <c r="F91" s="38"/>
     </row>
-    <row r="92" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="185"/>
-      <c r="B92" s="186"/>
+    <row r="92" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="156" t="s">
+        <v>216</v>
+      </c>
+      <c r="B92" s="135">
+        <f>5125397.67-4998045.07</f>
+        <v>127352.59999999963</v>
+      </c>
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
       <c r="F92" s="38"/>
     </row>
-    <row r="93" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="185"/>
-      <c r="B93" s="186"/>
+    <row r="93" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="183" t="s">
+        <v>178</v>
+      </c>
+      <c r="B93" s="184">
+        <f>SUM(B89:B92)</f>
+        <v>5125397.67</v>
+      </c>
       <c r="C93" s="38"/>
       <c r="D93" s="38"/>
       <c r="E93" s="38"/>
       <c r="F93" s="38"/>
     </row>
     <row r="94" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="112" t="s">
-        <v>160</v>
-      </c>
-      <c r="B94" s="51">
-        <v>231400</v>
-      </c>
+      <c r="A94" s="185"/>
+      <c r="B94" s="186"/>
       <c r="C94" s="38"/>
       <c r="D94" s="38"/>
       <c r="E94" s="38"/>
       <c r="F94" s="38"/>
     </row>
     <row r="95" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="156" t="s">
-        <v>161</v>
-      </c>
-      <c r="B95" s="182">
-        <v>0</v>
-      </c>
+      <c r="A95" s="185"/>
+      <c r="B95" s="186"/>
       <c r="C95" s="38"/>
       <c r="D95" s="38"/>
       <c r="E95" s="38"/>
       <c r="F95" s="38"/>
     </row>
     <row r="96" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="156" t="s">
-        <v>162</v>
-      </c>
-      <c r="B96" s="135"/>
+      <c r="A96" s="112" t="s">
+        <v>160</v>
+      </c>
+      <c r="B96" s="51">
+        <v>231400</v>
+      </c>
       <c r="C96" s="38"/>
       <c r="D96" s="38"/>
       <c r="E96" s="38"/>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="183" t="s">
-        <v>179</v>
-      </c>
-      <c r="B97" s="184">
-        <f>SUM(B94:B96)</f>
-        <v>231400</v>
+    <row r="97" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B97" s="182">
+        <v>0</v>
       </c>
       <c r="C97" s="38"/>
       <c r="D97" s="38"/>
@@ -3437,19 +3453,22 @@
       <c r="F97" s="38"/>
     </row>
     <row r="98" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="185"/>
-      <c r="B98" s="186"/>
+      <c r="A98" s="156" t="s">
+        <v>162</v>
+      </c>
+      <c r="B98" s="135"/>
       <c r="C98" s="38"/>
       <c r="D98" s="38"/>
       <c r="E98" s="38"/>
       <c r="F98" s="38"/>
     </row>
-    <row r="99" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="112" t="s">
-        <v>163</v>
-      </c>
-      <c r="B99" s="51">
-        <v>64328</v>
+    <row r="99" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="183" t="s">
+        <v>178</v>
+      </c>
+      <c r="B99" s="184">
+        <f>SUM(B96:B98)</f>
+        <v>231400</v>
       </c>
       <c r="C99" s="38"/>
       <c r="D99" s="38"/>
@@ -3457,183 +3476,210 @@
       <c r="F99" s="38"/>
     </row>
     <row r="100" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="156" t="s">
-        <v>161</v>
-      </c>
-      <c r="B100" s="182">
-        <v>0</v>
-      </c>
+      <c r="A100" s="185"/>
+      <c r="B100" s="186"/>
       <c r="C100" s="38"/>
       <c r="D100" s="38"/>
       <c r="E100" s="38"/>
       <c r="F100" s="38"/>
     </row>
     <row r="101" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="156" t="s">
-        <v>185</v>
-      </c>
-      <c r="B101" s="135">
-        <v>0</v>
+      <c r="A101" s="112" t="s">
+        <v>163</v>
+      </c>
+      <c r="B101" s="51">
+        <v>58418</v>
       </c>
       <c r="C101" s="38"/>
       <c r="D101" s="38"/>
       <c r="E101" s="38"/>
       <c r="F101" s="38"/>
     </row>
-    <row r="102" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="183" t="s">
-        <v>179</v>
-      </c>
-      <c r="B102" s="184">
-        <f>SUM(B99:B101)</f>
-        <v>64328</v>
+    <row r="102" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B102" s="182">
+        <v>0</v>
       </c>
       <c r="C102" s="38"/>
       <c r="D102" s="38"/>
       <c r="E102" s="38"/>
       <c r="F102" s="38"/>
     </row>
-    <row r="103" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-      <c r="B103" s="48"/>
-      <c r="C103" s="49"/>
-      <c r="D103" s="108"/>
-      <c r="E103" s="108"/>
-    </row>
-    <row r="104" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="112" t="s">
+    <row r="103" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="156" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103" s="135">
+        <v>0</v>
+      </c>
+      <c r="C103" s="38"/>
+      <c r="D103" s="38"/>
+      <c r="E103" s="38"/>
+      <c r="F103" s="38"/>
+    </row>
+    <row r="104" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="183" t="s">
         <v>178</v>
       </c>
-      <c r="B104" s="51">
-        <v>3986543.73</v>
-      </c>
-      <c r="C104" s="49"/>
-      <c r="D104" s="109"/>
-      <c r="E104" s="109"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B105" s="136">
-        <f>-B83-B84</f>
-        <v>-7387169.8700000001</v>
-      </c>
-      <c r="D105" s="38"/>
-      <c r="E105" s="38"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B106" s="52">
-        <f>B117</f>
-        <v>0</v>
-      </c>
-      <c r="D106" s="38"/>
-      <c r="E106" s="38"/>
-      <c r="F106" s="48"/>
+      <c r="B104" s="184">
+        <f>SUM(B101:B103)</f>
+        <v>58418</v>
+      </c>
+      <c r="C104" s="38"/>
+      <c r="D104" s="38"/>
+      <c r="E104" s="38"/>
+      <c r="F104" s="38"/>
+    </row>
+    <row r="105" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105"/>
+      <c r="B105" s="48"/>
+      <c r="C105" s="49"/>
+      <c r="D105" s="108"/>
+      <c r="E105" s="108"/>
+    </row>
+    <row r="106" spans="1:6" s="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="112" t="s">
+        <v>177</v>
+      </c>
+      <c r="B106" s="51">
+        <v>281967.3499999987</v>
+      </c>
+      <c r="C106" s="49"/>
+      <c r="D106" s="109"/>
+      <c r="E106" s="109"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B107" s="53">
-        <f>PRORRATEO!G61</f>
-        <v>5479535.0300000003</v>
+        <v>43</v>
+      </c>
+      <c r="B107" s="136">
+        <f>-B84-B85</f>
+        <v>-7325605.04</v>
       </c>
       <c r="D107" s="38"/>
       <c r="E107" s="38"/>
-      <c r="F107" s="48"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B108" s="96">
+        <v>24</v>
+      </c>
+      <c r="B108" s="52">
+        <f>B119</f>
         <v>0</v>
       </c>
       <c r="D108" s="38"/>
       <c r="E108" s="38"/>
       <c r="F108" s="48"/>
     </row>
-    <row r="109" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="B109" s="135">
-        <f>-B90</f>
-        <v>1501954.93</v>
-      </c>
-      <c r="D109" s="134"/>
+        <v>2</v>
+      </c>
+      <c r="B109" s="53">
+        <f>PRORRATEO!G61</f>
+        <v>5479535.0300000003</v>
+      </c>
+      <c r="D109" s="38"/>
       <c r="E109" s="38"/>
       <c r="F109" s="48"/>
     </row>
-    <row r="110" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="54" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B110" s="96">
+        <v>0</v>
+      </c>
+      <c r="D110" s="38"/>
+      <c r="E110" s="38"/>
+      <c r="F110" s="48"/>
+    </row>
+    <row r="111" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="B111" s="135">
+        <f>-B91</f>
+        <v>1501954.93</v>
+      </c>
+      <c r="D111" s="134"/>
+      <c r="E111" s="38"/>
+      <c r="F111" s="48"/>
+    </row>
+    <row r="112" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="B110" s="55">
-        <f>SUM(B104:C109)</f>
-        <v>3580863.8200000003</v>
-      </c>
-      <c r="D110" s="48"/>
-      <c r="E110" s="40"/>
-      <c r="F110" s="40"/>
-    </row>
-    <row r="111" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:6" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="137" t="s">
+      <c r="B112" s="55">
+        <f>SUM(B106:C111)</f>
+        <v>-62147.730000001146</v>
+      </c>
+      <c r="D112" s="48"/>
+      <c r="E112" s="40"/>
+      <c r="F112" s="40"/>
+    </row>
+    <row r="113" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:13" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="137" t="s">
         <v>164</v>
       </c>
-      <c r="B112" s="138">
-        <f>B110+B97</f>
-        <v>3812263.8200000003</v>
-      </c>
-      <c r="D112" s="40"/>
-      <c r="E112" s="40"/>
-    </row>
-    <row r="113" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="228" t="s">
+      <c r="B114" s="138">
+        <f>B112+B99</f>
+        <v>169252.26999999885</v>
+      </c>
+      <c r="D114" s="40"/>
+      <c r="E114" s="40"/>
+      <c r="H114" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="204" t="s">
         <v>25</v>
       </c>
-      <c r="B114" s="228"/>
-      <c r="C114" s="228"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="228"/>
-      <c r="B115" s="228"/>
-      <c r="C115" s="228"/>
-    </row>
-    <row r="116" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="56"/>
-      <c r="B116" s="79"/>
-      <c r="C116" s="57"/>
-      <c r="D116" s="43"/>
+      <c r="B116" s="204"/>
+      <c r="C116" s="204"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B117" s="59">
-        <f>SUM(B116:B116)</f>
-        <v>0</v>
-      </c>
-      <c r="C117" s="60"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M118" s="61"/>
+      <c r="A117" s="204"/>
+      <c r="B117" s="204"/>
+      <c r="C117" s="204"/>
+    </row>
+    <row r="118" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="56"/>
+      <c r="B118" s="79"/>
+      <c r="C118" s="57"/>
+      <c r="D118" s="43"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="59">
+        <f>SUM(B118:B118)</f>
+        <v>0</v>
+      </c>
+      <c r="C119" s="60"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M120" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A114:C115"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A116:C117"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
@@ -3643,10 +3689,6 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3688,19 +3730,19 @@
       <c r="G1" s="127"/>
       <c r="H1" s="127"/>
       <c r="I1" s="127"/>
-      <c r="J1" s="256" t="str">
+      <c r="J1" s="222" t="str">
         <f>RESUMEN!B3</f>
         <v xml:space="preserve">Banco: Santander N.º de cuenta: 039-021152/7
 CBU: 0720039720000002115272
 Alias: EDIFICIO.AIRE.FRESCO
 </v>
       </c>
-      <c r="K1" s="256"/>
-      <c r="L1" s="256"/>
-      <c r="M1" s="256"/>
-      <c r="N1" s="256"/>
-      <c r="O1" s="256"/>
-      <c r="P1" s="257"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
+      <c r="P1" s="223"/>
     </row>
     <row r="2" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3708,22 +3750,22 @@
       </c>
       <c r="B2" s="128"/>
       <c r="C2" s="140">
-        <f>6219841.65-C5</f>
-        <v>4906689.78</v>
+        <f>7325605.04-C5-305000.04-15405.58</f>
+        <v>5300000</v>
       </c>
       <c r="D2" s="68"/>
       <c r="E2" s="68"/>
-      <c r="F2" s="264"/>
-      <c r="G2" s="264"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="232"/>
       <c r="H2" s="68"/>
       <c r="I2" s="68"/>
-      <c r="J2" s="258"/>
-      <c r="K2" s="258"/>
-      <c r="L2" s="258"/>
-      <c r="M2" s="258"/>
-      <c r="N2" s="258"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="224"/>
+      <c r="M2" s="224"/>
+      <c r="N2" s="224"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="225"/>
       <c r="Q2" s="62"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3740,13 +3782,13 @@
       <c r="G3" s="132"/>
       <c r="H3" s="68"/>
       <c r="I3" s="68"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="M3" s="258"/>
-      <c r="N3" s="258"/>
-      <c r="O3" s="258"/>
-      <c r="P3" s="259"/>
+      <c r="J3" s="224"/>
+      <c r="K3" s="224"/>
+      <c r="L3" s="224"/>
+      <c r="M3" s="224"/>
+      <c r="N3" s="224"/>
+      <c r="O3" s="224"/>
+      <c r="P3" s="225"/>
       <c r="Q3" s="62"/>
       <c r="R3" s="40"/>
     </row>
@@ -3764,13 +3806,13 @@
       <c r="G4" s="132"/>
       <c r="H4" s="68"/>
       <c r="I4" s="68"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="M4" s="258"/>
-      <c r="N4" s="258"/>
-      <c r="O4" s="258"/>
-      <c r="P4" s="259"/>
+      <c r="J4" s="224"/>
+      <c r="K4" s="224"/>
+      <c r="L4" s="224"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="225"/>
       <c r="Q4" s="62"/>
       <c r="R4" s="40"/>
     </row>
@@ -3780,7 +3822,7 @@
       </c>
       <c r="B5" s="129"/>
       <c r="C5" s="141">
-        <v>1313151.8700000001</v>
+        <v>1705199.42</v>
       </c>
       <c r="D5" s="69"/>
       <c r="E5" s="69"/>
@@ -3788,201 +3830,201 @@
       <c r="G5" s="70"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="260"/>
-      <c r="K5" s="260"/>
-      <c r="L5" s="260"/>
-      <c r="M5" s="260"/>
-      <c r="N5" s="260"/>
-      <c r="O5" s="260"/>
-      <c r="P5" s="261"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="226"/>
+      <c r="P5" s="227"/>
       <c r="Q5" s="62"/>
     </row>
     <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="231" t="s">
+      <c r="A6" s="234" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="232"/>
-      <c r="C6" s="233"/>
-      <c r="D6" s="233"/>
-      <c r="E6" s="233"/>
-      <c r="F6" s="233"/>
-      <c r="G6" s="233"/>
-      <c r="H6" s="233"/>
-      <c r="I6" s="233"/>
-      <c r="J6" s="233"/>
-      <c r="K6" s="233"/>
-      <c r="L6" s="233"/>
-      <c r="M6" s="233"/>
-      <c r="N6" s="233"/>
-      <c r="O6" s="233"/>
-      <c r="P6" s="234"/>
+      <c r="B6" s="235"/>
+      <c r="C6" s="236"/>
+      <c r="D6" s="236"/>
+      <c r="E6" s="236"/>
+      <c r="F6" s="236"/>
+      <c r="G6" s="236"/>
+      <c r="H6" s="236"/>
+      <c r="I6" s="236"/>
+      <c r="J6" s="236"/>
+      <c r="K6" s="236"/>
+      <c r="L6" s="236"/>
+      <c r="M6" s="236"/>
+      <c r="N6" s="236"/>
+      <c r="O6" s="236"/>
+      <c r="P6" s="237"/>
       <c r="Q6" s="62"/>
     </row>
     <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="235"/>
-      <c r="B7" s="236"/>
-      <c r="C7" s="236"/>
-      <c r="D7" s="236"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="236"/>
-      <c r="G7" s="236"/>
-      <c r="H7" s="236"/>
-      <c r="I7" s="236"/>
-      <c r="J7" s="236"/>
-      <c r="K7" s="236"/>
-      <c r="L7" s="236"/>
-      <c r="M7" s="236"/>
-      <c r="N7" s="236"/>
-      <c r="O7" s="236"/>
-      <c r="P7" s="237"/>
+      <c r="A7" s="238"/>
+      <c r="B7" s="239"/>
+      <c r="C7" s="239"/>
+      <c r="D7" s="239"/>
+      <c r="E7" s="239"/>
+      <c r="F7" s="239"/>
+      <c r="G7" s="239"/>
+      <c r="H7" s="239"/>
+      <c r="I7" s="239"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="239"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="240"/>
       <c r="Q7" s="62"/>
     </row>
     <row r="8" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="235"/>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="236"/>
-      <c r="E8" s="236"/>
-      <c r="F8" s="236"/>
-      <c r="G8" s="236"/>
-      <c r="H8" s="236"/>
-      <c r="I8" s="236"/>
-      <c r="J8" s="236"/>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
-      <c r="M8" s="236"/>
-      <c r="N8" s="236"/>
-      <c r="O8" s="236"/>
-      <c r="P8" s="237"/>
+      <c r="A8" s="238"/>
+      <c r="B8" s="239"/>
+      <c r="C8" s="239"/>
+      <c r="D8" s="239"/>
+      <c r="E8" s="239"/>
+      <c r="F8" s="239"/>
+      <c r="G8" s="239"/>
+      <c r="H8" s="239"/>
+      <c r="I8" s="239"/>
+      <c r="J8" s="239"/>
+      <c r="K8" s="239"/>
+      <c r="L8" s="239"/>
+      <c r="M8" s="239"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="240"/>
       <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="235"/>
-      <c r="B9" s="236"/>
-      <c r="C9" s="236"/>
-      <c r="D9" s="236"/>
-      <c r="E9" s="236"/>
-      <c r="F9" s="236"/>
-      <c r="G9" s="236"/>
-      <c r="H9" s="236"/>
-      <c r="I9" s="236"/>
-      <c r="J9" s="236"/>
-      <c r="K9" s="236"/>
-      <c r="L9" s="236"/>
-      <c r="M9" s="236"/>
-      <c r="N9" s="236"/>
-      <c r="O9" s="236"/>
-      <c r="P9" s="237"/>
+      <c r="A9" s="238"/>
+      <c r="B9" s="239"/>
+      <c r="C9" s="239"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="239"/>
+      <c r="H9" s="239"/>
+      <c r="I9" s="239"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
+      <c r="L9" s="239"/>
+      <c r="M9" s="239"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="239"/>
+      <c r="P9" s="240"/>
       <c r="Q9" s="62"/>
     </row>
     <row r="10" spans="1:18" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="238"/>
-      <c r="B10" s="239"/>
-      <c r="C10" s="239"/>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="239"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
-      <c r="M10" s="239"/>
-      <c r="N10" s="239"/>
-      <c r="O10" s="239"/>
-      <c r="P10" s="240"/>
+      <c r="A10" s="241"/>
+      <c r="B10" s="242"/>
+      <c r="C10" s="242"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="242"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="242"/>
+      <c r="J10" s="242"/>
+      <c r="K10" s="242"/>
+      <c r="L10" s="242"/>
+      <c r="M10" s="242"/>
+      <c r="N10" s="242"/>
+      <c r="O10" s="242"/>
+      <c r="P10" s="243"/>
     </row>
     <row r="11" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="249" t="s">
+      <c r="A11" s="250" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="250"/>
-      <c r="C11" s="250"/>
-      <c r="D11" s="250"/>
-      <c r="E11" s="250"/>
-      <c r="F11" s="250"/>
-      <c r="G11" s="250"/>
-      <c r="H11" s="250"/>
-      <c r="I11" s="250"/>
-      <c r="J11" s="250"/>
-      <c r="K11" s="250"/>
-      <c r="L11" s="250"/>
-      <c r="M11" s="250"/>
-      <c r="N11" s="250"/>
-      <c r="O11" s="250"/>
-      <c r="P11" s="251"/>
+      <c r="B11" s="251"/>
+      <c r="C11" s="251"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
+      <c r="M11" s="251"/>
+      <c r="N11" s="251"/>
+      <c r="O11" s="251"/>
+      <c r="P11" s="252"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="241" t="s">
+      <c r="A12" s="244" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="254" t="s">
+      <c r="B12" s="255" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="243" t="s">
+      <c r="C12" s="246" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="243" t="s">
+      <c r="D12" s="246" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="243" t="s">
+      <c r="E12" s="246" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="245" t="s">
+      <c r="F12" s="228" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="243" t="s">
+      <c r="G12" s="268" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="247" t="s">
+      <c r="H12" s="248" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="245" t="s">
+      <c r="I12" s="228" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="245" t="s">
+      <c r="J12" s="228" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="245" t="s">
+      <c r="K12" s="228" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="254" t="s">
+      <c r="L12" s="255" t="s">
         <v>170</v>
       </c>
-      <c r="M12" s="245" t="s">
+      <c r="M12" s="228" t="s">
         <v>167</v>
       </c>
-      <c r="N12" s="252" t="s">
-        <v>186</v>
+      <c r="N12" s="253" t="s">
+        <v>184</v>
       </c>
       <c r="O12" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="262" t="s">
+      <c r="P12" s="230" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="242"/>
-      <c r="B13" s="255"/>
-      <c r="C13" s="244"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="246"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="246"/>
-      <c r="J13" s="246"/>
-      <c r="K13" s="246"/>
-      <c r="L13" s="255"/>
-      <c r="M13" s="246"/>
-      <c r="N13" s="253"/>
+      <c r="A13" s="245"/>
+      <c r="B13" s="256"/>
+      <c r="C13" s="247"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="247"/>
+      <c r="F13" s="229"/>
+      <c r="G13" s="269"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="229"/>
+      <c r="J13" s="229"/>
+      <c r="K13" s="229"/>
+      <c r="L13" s="256"/>
+      <c r="M13" s="229"/>
+      <c r="N13" s="254"/>
       <c r="O13" s="94" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="P13" s="263"/>
+      <c r="P13" s="231"/>
     </row>
     <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="83">
@@ -4001,7 +4043,7 @@
       <c r="F14" s="63">
         <v>322564.01</v>
       </c>
-      <c r="G14" s="199">
+      <c r="G14" s="63">
         <f t="shared" ref="G14" si="0">F14</f>
         <v>322564.01</v>
       </c>
@@ -4015,7 +4057,7 @@
       </c>
       <c r="J14" s="82">
         <f>C$2*E14/100</f>
-        <v>256129.20651600001</v>
+        <v>276660</v>
       </c>
       <c r="K14" s="82">
         <f t="shared" ref="K14:K45" si="2">F$2*E14/100</f>
@@ -4027,16 +4069,16 @@
       </c>
       <c r="M14" s="82">
         <f>C$5*E14/100</f>
-        <v>68546.527614000006</v>
+        <v>89011.409723999983</v>
       </c>
       <c r="N14" s="82"/>
       <c r="O14" s="76">
         <f>ROUND(SUM(H14:N14),0) + Q14</f>
-        <v>334219.01</v>
+        <v>375215.01</v>
       </c>
       <c r="P14" s="91">
         <f t="shared" ref="P14:P34" si="3">ROUND(O14*3%,0) + O14</f>
-        <v>344246.01</v>
+        <v>386471.01</v>
       </c>
       <c r="Q14" s="40">
         <v>0.01</v>
@@ -4072,7 +4114,7 @@
       </c>
       <c r="J15" s="82">
         <f t="shared" ref="J15:J59" si="5">C$2*E15/100</f>
-        <v>166827.45251999999</v>
+        <v>180200</v>
       </c>
       <c r="K15" s="82">
         <f t="shared" si="2"/>
@@ -4084,16 +4126,16 @@
       </c>
       <c r="M15" s="82">
         <f t="shared" ref="M15:M59" si="7">C$5*E15/100</f>
-        <v>44647.16358</v>
+        <v>57976.780279999999</v>
       </c>
       <c r="N15" s="82"/>
       <c r="O15" s="76">
         <f t="shared" ref="O15:O59" si="8">ROUND(SUM(H15:N15),0) + Q15</f>
-        <v>251965.02</v>
+        <v>278667.02</v>
       </c>
       <c r="P15" s="91">
         <f t="shared" si="3"/>
-        <v>259524.02</v>
+        <v>287027.02</v>
       </c>
       <c r="Q15" s="40">
         <f>Q14+0.01</f>
@@ -4119,7 +4161,7 @@
       <c r="F16" s="63">
         <v>160932.03</v>
       </c>
-      <c r="G16" s="199">
+      <c r="G16" s="63">
         <f>F16</f>
         <v>160932.03</v>
       </c>
@@ -4133,7 +4175,7 @@
       </c>
       <c r="J16" s="82">
         <f t="shared" si="5"/>
-        <v>124629.92041200001</v>
+        <v>134620</v>
       </c>
       <c r="K16" s="82">
         <f t="shared" si="2"/>
@@ -4145,16 +4187,16 @@
       </c>
       <c r="M16" s="82">
         <f t="shared" si="7"/>
-        <v>33354.057498000002</v>
+        <v>43312.065267999998</v>
       </c>
       <c r="N16" s="82"/>
       <c r="O16" s="76">
         <f t="shared" si="8"/>
-        <v>162628.03</v>
+        <v>182576.03</v>
       </c>
       <c r="P16" s="91">
         <f t="shared" si="3"/>
-        <v>167507.03</v>
+        <v>188053.03</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" ref="Q16:Q31" si="9">Q15+0.01</f>
@@ -4183,7 +4225,7 @@
       <c r="F17" s="63">
         <v>337083.04</v>
       </c>
-      <c r="G17" s="199">
+      <c r="G17" s="63">
         <f>403280-G55-G44</f>
         <v>348856.27</v>
       </c>
@@ -4197,7 +4239,7 @@
       </c>
       <c r="J17" s="82">
         <f t="shared" si="5"/>
-        <v>254657.19958200003</v>
+        <v>275070.00000000006</v>
       </c>
       <c r="K17" s="82">
         <f t="shared" si="2"/>
@@ -4209,16 +4251,16 @@
       </c>
       <c r="M17" s="82">
         <f t="shared" si="7"/>
-        <v>68152.58205300002</v>
+        <v>88499.849898</v>
       </c>
       <c r="N17" s="82"/>
       <c r="O17" s="76">
         <f t="shared" si="8"/>
-        <v>320525.03999999998</v>
+        <v>361285.04</v>
       </c>
       <c r="P17" s="91">
         <f t="shared" si="3"/>
-        <v>330141.03999999998</v>
+        <v>372124.04</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="9"/>
@@ -4247,7 +4289,7 @@
       <c r="F18" s="63">
         <v>217691.05</v>
       </c>
-      <c r="G18" s="199">
+      <c r="G18" s="63">
         <f>77540+140500</f>
         <v>218040</v>
       </c>
@@ -4261,7 +4303,7 @@
       </c>
       <c r="J18" s="82">
         <f t="shared" si="5"/>
-        <v>166827.45251999999</v>
+        <v>180200</v>
       </c>
       <c r="K18" s="82">
         <f t="shared" si="2"/>
@@ -4273,16 +4315,16 @@
       </c>
       <c r="M18" s="82">
         <f t="shared" si="7"/>
-        <v>44647.16358</v>
+        <v>57976.780279999999</v>
       </c>
       <c r="N18" s="82"/>
       <c r="O18" s="76">
         <f t="shared" si="8"/>
-        <v>217342.05</v>
+        <v>244044.05</v>
       </c>
       <c r="P18" s="91">
         <f t="shared" si="3"/>
-        <v>223862.05</v>
+        <v>251365.05</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="9"/>
@@ -4300,7 +4342,7 @@
         <v>118</v>
       </c>
       <c r="D19" s="72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E19" s="74">
         <v>2.54</v>
@@ -4308,7 +4350,7 @@
       <c r="F19" s="63">
         <v>162628.06</v>
       </c>
-      <c r="G19" s="199">
+      <c r="G19" s="63">
         <f>F19</f>
         <v>162628.06</v>
       </c>
@@ -4322,7 +4364,7 @@
       </c>
       <c r="J19" s="82">
         <f t="shared" si="5"/>
-        <v>124629.92041200001</v>
+        <v>134620</v>
       </c>
       <c r="K19" s="82">
         <f t="shared" si="2"/>
@@ -4334,16 +4376,16 @@
       </c>
       <c r="M19" s="82">
         <f t="shared" si="7"/>
-        <v>33354.057498000002</v>
+        <v>43312.065267999998</v>
       </c>
       <c r="N19" s="82"/>
       <c r="O19" s="76">
         <f t="shared" si="8"/>
-        <v>162628.06</v>
+        <v>182576.06</v>
       </c>
       <c r="P19" s="91">
         <f t="shared" si="3"/>
-        <v>167507.06</v>
+        <v>188053.06</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="9"/>
@@ -4367,7 +4409,7 @@
       <c r="F20" s="63">
         <v>332298.07</v>
       </c>
-      <c r="G20" s="199">
+      <c r="G20" s="63">
         <f t="shared" ref="G20:G25" si="10">F20</f>
         <v>332298.07</v>
       </c>
@@ -4381,7 +4423,7 @@
       </c>
       <c r="J20" s="82">
         <f t="shared" si="5"/>
-        <v>254657.19958200003</v>
+        <v>275070.00000000006</v>
       </c>
       <c r="K20" s="82">
         <f t="shared" si="2"/>
@@ -4393,16 +4435,16 @@
       </c>
       <c r="M20" s="82">
         <f t="shared" si="7"/>
-        <v>68152.58205300002</v>
+        <v>88499.849898</v>
       </c>
       <c r="N20" s="82"/>
       <c r="O20" s="76">
         <f t="shared" si="8"/>
-        <v>332298.07</v>
+        <v>373058.07</v>
       </c>
       <c r="P20" s="91">
         <f t="shared" si="3"/>
-        <v>342267.07</v>
+        <v>384250.07</v>
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="9"/>
@@ -4426,7 +4468,7 @@
       <c r="F21" s="63">
         <v>217691.08</v>
       </c>
-      <c r="G21" s="199">
+      <c r="G21" s="63">
         <f t="shared" si="10"/>
         <v>217691.08</v>
       </c>
@@ -4440,7 +4482,7 @@
       </c>
       <c r="J21" s="82">
         <f t="shared" si="5"/>
-        <v>166827.45251999999</v>
+        <v>180200</v>
       </c>
       <c r="K21" s="82">
         <f t="shared" si="2"/>
@@ -4452,16 +4494,16 @@
       </c>
       <c r="M21" s="82">
         <f t="shared" si="7"/>
-        <v>44647.16358</v>
+        <v>57976.780279999999</v>
       </c>
       <c r="N21" s="82"/>
       <c r="O21" s="76">
         <f t="shared" si="8"/>
-        <v>217691.08</v>
+        <v>244393.08</v>
       </c>
       <c r="P21" s="91">
         <f t="shared" si="3"/>
-        <v>224222.07999999999</v>
+        <v>251725.08</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" si="9"/>
@@ -4487,7 +4529,7 @@
       <c r="F22" s="63">
         <v>162628.09</v>
       </c>
-      <c r="G22" s="199">
+      <c r="G22" s="63">
         <f t="shared" si="10"/>
         <v>162628.09</v>
       </c>
@@ -4501,7 +4543,7 @@
       </c>
       <c r="J22" s="82">
         <f t="shared" si="5"/>
-        <v>124629.92041200001</v>
+        <v>134620</v>
       </c>
       <c r="K22" s="82">
         <f t="shared" si="2"/>
@@ -4513,16 +4555,16 @@
       </c>
       <c r="M22" s="82">
         <f t="shared" si="7"/>
-        <v>33354.057498000002</v>
+        <v>43312.065267999998</v>
       </c>
       <c r="N22" s="82"/>
       <c r="O22" s="76">
         <f t="shared" si="8"/>
-        <v>162628.09</v>
+        <v>182576.09</v>
       </c>
       <c r="P22" s="91">
         <f t="shared" si="3"/>
-        <v>167507.09</v>
+        <v>188053.09</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="9"/>
@@ -4546,7 +4588,7 @@
       <c r="F23" s="63">
         <v>332298.09999999998</v>
       </c>
-      <c r="G23" s="199">
+      <c r="G23" s="63">
         <f t="shared" si="10"/>
         <v>332298.09999999998</v>
       </c>
@@ -4560,7 +4602,7 @@
       </c>
       <c r="J23" s="82">
         <f t="shared" si="5"/>
-        <v>254657.19958200003</v>
+        <v>275070.00000000006</v>
       </c>
       <c r="K23" s="82">
         <f t="shared" si="2"/>
@@ -4572,16 +4614,16 @@
       </c>
       <c r="M23" s="82">
         <f t="shared" si="7"/>
-        <v>68152.58205300002</v>
+        <v>88499.849898</v>
       </c>
       <c r="N23" s="82"/>
       <c r="O23" s="76">
         <f t="shared" si="8"/>
-        <v>332298.09999999998</v>
+        <v>373058.1</v>
       </c>
       <c r="P23" s="91">
         <f t="shared" si="3"/>
-        <v>342267.1</v>
+        <v>384250.1</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="9"/>
@@ -4607,7 +4649,7 @@
       <c r="F24" s="63">
         <v>217691.11</v>
       </c>
-      <c r="G24" s="199">
+      <c r="G24" s="63">
         <f t="shared" si="10"/>
         <v>217691.11</v>
       </c>
@@ -4621,7 +4663,7 @@
       </c>
       <c r="J24" s="82">
         <f t="shared" si="5"/>
-        <v>166827.45251999999</v>
+        <v>180200</v>
       </c>
       <c r="K24" s="82">
         <f t="shared" si="2"/>
@@ -4633,16 +4675,16 @@
       </c>
       <c r="M24" s="82">
         <f t="shared" si="7"/>
-        <v>44647.16358</v>
+        <v>57976.780279999999</v>
       </c>
       <c r="N24" s="82"/>
       <c r="O24" s="76">
         <f t="shared" si="8"/>
-        <v>217691.11</v>
+        <v>244393.11</v>
       </c>
       <c r="P24" s="91">
         <f t="shared" si="3"/>
-        <v>224222.11</v>
+        <v>251725.11</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" si="9"/>
@@ -4668,7 +4710,7 @@
       <c r="F25" s="63">
         <v>162628.12</v>
       </c>
-      <c r="G25" s="199">
+      <c r="G25" s="63">
         <f t="shared" si="10"/>
         <v>162628.12</v>
       </c>
@@ -4682,7 +4724,7 @@
       </c>
       <c r="J25" s="82">
         <f t="shared" si="5"/>
-        <v>124629.92041200001</v>
+        <v>134620</v>
       </c>
       <c r="K25" s="82">
         <f t="shared" si="2"/>
@@ -4694,16 +4736,16 @@
       </c>
       <c r="M25" s="82">
         <f t="shared" si="7"/>
-        <v>33354.057498000002</v>
+        <v>43312.065267999998</v>
       </c>
       <c r="N25" s="82"/>
       <c r="O25" s="76">
         <f t="shared" si="8"/>
-        <v>162628.12</v>
+        <v>182576.12</v>
       </c>
       <c r="P25" s="91">
         <f t="shared" si="3"/>
-        <v>167507.12</v>
+        <v>188053.12</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="9"/>
@@ -4718,7 +4760,7 @@
         <v>83</v>
       </c>
       <c r="C26" s="144" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D26" s="145"/>
       <c r="E26" s="146">
@@ -4727,7 +4769,7 @@
       <c r="F26" s="147">
         <v>320441.13</v>
       </c>
-      <c r="G26" s="211">
+      <c r="G26" s="147">
         <f>335330.44-G45</f>
         <v>330208.12</v>
       </c>
@@ -4741,7 +4783,7 @@
       </c>
       <c r="J26" s="149">
         <f t="shared" si="5"/>
-        <v>254657.19958200003</v>
+        <v>275070.00000000006</v>
       </c>
       <c r="K26" s="149">
         <f t="shared" si="2"/>
@@ -4753,16 +4795,16 @@
       </c>
       <c r="M26" s="149">
         <f t="shared" si="7"/>
-        <v>68152.58205300002</v>
+        <v>88499.849898</v>
       </c>
       <c r="N26" s="149"/>
       <c r="O26" s="150">
         <f t="shared" si="8"/>
-        <v>322531.13</v>
+        <v>363291.13</v>
       </c>
       <c r="P26" s="151">
         <f t="shared" si="3"/>
-        <v>332207.13</v>
+        <v>374190.13</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="9"/>
@@ -4786,7 +4828,7 @@
       <c r="F27" s="147">
         <v>217691.14</v>
       </c>
-      <c r="G27" s="211">
+      <c r="G27" s="147">
         <f>288191.52-G51</f>
         <v>226085.14</v>
       </c>
@@ -4800,7 +4842,7 @@
       </c>
       <c r="J27" s="149">
         <f t="shared" si="5"/>
-        <v>166827.45251999999</v>
+        <v>180200</v>
       </c>
       <c r="K27" s="149">
         <f t="shared" si="2"/>
@@ -4812,16 +4854,16 @@
       </c>
       <c r="M27" s="149">
         <f t="shared" si="7"/>
-        <v>44647.16358</v>
+        <v>57976.780279999999</v>
       </c>
       <c r="N27" s="149"/>
       <c r="O27" s="150">
         <f t="shared" si="8"/>
-        <v>209297.14</v>
+        <v>235999.14</v>
       </c>
       <c r="P27" s="151">
         <f t="shared" si="3"/>
-        <v>215576.14</v>
+        <v>243079.14</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="9"/>
@@ -4847,7 +4889,7 @@
       <c r="F28" s="63">
         <v>162628.15</v>
       </c>
-      <c r="G28" s="199">
+      <c r="G28" s="63">
         <f>F28</f>
         <v>162628.15</v>
       </c>
@@ -4861,7 +4903,7 @@
       </c>
       <c r="J28" s="82">
         <f t="shared" si="5"/>
-        <v>124629.92041200001</v>
+        <v>134620</v>
       </c>
       <c r="K28" s="82">
         <f t="shared" si="2"/>
@@ -4873,16 +4915,16 @@
       </c>
       <c r="M28" s="82">
         <f t="shared" si="7"/>
-        <v>33354.057498000002</v>
+        <v>43312.065267999998</v>
       </c>
       <c r="N28" s="82"/>
       <c r="O28" s="76">
         <f t="shared" si="8"/>
-        <v>162628.15</v>
+        <v>182576.15</v>
       </c>
       <c r="P28" s="91">
         <f t="shared" si="3"/>
-        <v>167507.15</v>
+        <v>188053.15</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" si="9"/>
@@ -4906,7 +4948,7 @@
       <c r="F29" s="63">
         <v>332298.15999999997</v>
       </c>
-      <c r="G29" s="199">
+      <c r="G29" s="63">
         <f>F29</f>
         <v>332298.15999999997</v>
       </c>
@@ -4920,7 +4962,7 @@
       </c>
       <c r="J29" s="82">
         <f t="shared" si="5"/>
-        <v>254657.19958200003</v>
+        <v>275070.00000000006</v>
       </c>
       <c r="K29" s="82">
         <f t="shared" si="2"/>
@@ -4932,16 +4974,16 @@
       </c>
       <c r="M29" s="82">
         <f t="shared" si="7"/>
-        <v>68152.58205300002</v>
+        <v>88499.849898</v>
       </c>
       <c r="N29" s="82"/>
       <c r="O29" s="76">
         <f t="shared" si="8"/>
-        <v>332298.15999999997</v>
+        <v>373058.16</v>
       </c>
       <c r="P29" s="91">
         <f t="shared" si="3"/>
-        <v>342267.16</v>
+        <v>384250.16</v>
       </c>
       <c r="Q29" s="40">
         <f t="shared" si="9"/>
@@ -4967,7 +5009,7 @@
       <c r="F30" s="63">
         <v>217688.17</v>
       </c>
-      <c r="G30" s="199">
+      <c r="G30" s="63">
         <f>268481-G53</f>
         <v>219179.6</v>
       </c>
@@ -4981,7 +5023,7 @@
       </c>
       <c r="J30" s="82">
         <f t="shared" si="5"/>
-        <v>166827.45251999999</v>
+        <v>180200</v>
       </c>
       <c r="K30" s="82">
         <f t="shared" si="2"/>
@@ -4993,16 +5035,16 @@
       </c>
       <c r="M30" s="82">
         <f t="shared" si="7"/>
-        <v>44647.16358</v>
+        <v>57976.780279999999</v>
       </c>
       <c r="N30" s="82"/>
       <c r="O30" s="76">
         <f t="shared" si="8"/>
-        <v>216199.17</v>
+        <v>242901.17</v>
       </c>
       <c r="P30" s="91">
         <f t="shared" si="3"/>
-        <v>222685.17</v>
+        <v>250188.17</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="9"/>
@@ -5037,7 +5079,7 @@
       </c>
       <c r="J31" s="82">
         <f t="shared" si="5"/>
-        <v>124629.92041200001</v>
+        <v>134620</v>
       </c>
       <c r="K31" s="82">
         <f t="shared" si="2"/>
@@ -5049,16 +5091,16 @@
       </c>
       <c r="M31" s="82">
         <f t="shared" si="7"/>
-        <v>33354.057498000002</v>
+        <v>43312.065267999998</v>
       </c>
       <c r="N31" s="82"/>
       <c r="O31" s="76">
         <f t="shared" si="8"/>
-        <v>1826702.18</v>
+        <v>1846650.18</v>
       </c>
       <c r="P31" s="91">
         <f t="shared" si="3"/>
-        <v>1881503.18</v>
+        <v>1902050.18</v>
       </c>
       <c r="Q31" s="40">
         <f t="shared" si="9"/>
@@ -5095,7 +5137,7 @@
       </c>
       <c r="J32" s="82">
         <f t="shared" si="5"/>
-        <v>254657.19958200003</v>
+        <v>275070.00000000006</v>
       </c>
       <c r="K32" s="82">
         <f t="shared" si="2"/>
@@ -5107,18 +5149,18 @@
       </c>
       <c r="M32" s="82">
         <f t="shared" si="7"/>
-        <v>68152.58205300002</v>
+        <v>88499.849898</v>
       </c>
       <c r="N32" s="82">
         <v>43500</v>
       </c>
       <c r="O32" s="76">
         <f t="shared" si="8"/>
-        <v>1553747.19</v>
+        <v>1594507.19</v>
       </c>
       <c r="P32" s="91">
         <f t="shared" si="3"/>
-        <v>1600359.19</v>
+        <v>1642342.19</v>
       </c>
       <c r="Q32" s="40">
         <f>Q31+0.01</f>
@@ -5126,55 +5168,55 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="200">
+      <c r="A33" s="192">
         <v>20</v>
       </c>
-      <c r="B33" s="201" t="s">
+      <c r="B33" s="193" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="202" t="s">
+      <c r="C33" s="194" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="203"/>
-      <c r="E33" s="204">
+      <c r="D33" s="195"/>
+      <c r="E33" s="196">
         <v>3.4</v>
       </c>
-      <c r="F33" s="205">
+      <c r="F33" s="197">
         <v>217691.2</v>
       </c>
-      <c r="G33" s="206">
+      <c r="G33" s="197">
         <f>229946.49-G47</f>
         <v>224824.15</v>
       </c>
-      <c r="H33" s="207">
+      <c r="H33" s="198">
         <f t="shared" si="1"/>
         <v>-7132.9499999999825</v>
       </c>
-      <c r="I33" s="207"/>
-      <c r="J33" s="208">
+      <c r="I33" s="198"/>
+      <c r="J33" s="199">
         <f t="shared" si="5"/>
-        <v>166827.45251999999</v>
-      </c>
-      <c r="K33" s="208">
+        <v>180200</v>
+      </c>
+      <c r="K33" s="199">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="208">
+      <c r="L33" s="199">
         <f t="shared" si="6"/>
         <v>6215.9823400000005</v>
       </c>
-      <c r="M33" s="208">
+      <c r="M33" s="199">
         <f t="shared" si="7"/>
-        <v>44647.16358</v>
-      </c>
-      <c r="N33" s="208"/>
-      <c r="O33" s="209">
+        <v>57976.780279999999</v>
+      </c>
+      <c r="N33" s="199"/>
+      <c r="O33" s="200">
         <f t="shared" si="8"/>
-        <v>210558.2</v>
-      </c>
-      <c r="P33" s="210">
+        <v>237260.2</v>
+      </c>
+      <c r="P33" s="201">
         <f t="shared" si="3"/>
-        <v>216875.2</v>
+        <v>244378.2</v>
       </c>
       <c r="Q33" s="40">
         <f t="shared" ref="Q33:Q59" si="11">Q32+0.01</f>
@@ -5200,7 +5242,7 @@
       <c r="F34" s="63">
         <v>162628.21</v>
       </c>
-      <c r="G34" s="199">
+      <c r="G34" s="63">
         <f t="shared" ref="G34:G35" si="12">F34</f>
         <v>162628.21</v>
       </c>
@@ -5214,7 +5256,7 @@
       </c>
       <c r="J34" s="82">
         <f t="shared" si="5"/>
-        <v>124629.92041200001</v>
+        <v>134620</v>
       </c>
       <c r="K34" s="82">
         <f t="shared" si="2"/>
@@ -5226,16 +5268,16 @@
       </c>
       <c r="M34" s="82">
         <f t="shared" si="7"/>
-        <v>33354.057498000002</v>
+        <v>43312.065267999998</v>
       </c>
       <c r="N34" s="82"/>
       <c r="O34" s="76">
         <f t="shared" si="8"/>
-        <v>162628.21</v>
+        <v>182576.21</v>
       </c>
       <c r="P34" s="91">
         <f t="shared" si="3"/>
-        <v>167507.21</v>
+        <v>188053.21</v>
       </c>
       <c r="Q34" s="40">
         <f t="shared" si="11"/>
@@ -5262,7 +5304,7 @@
       <c r="F35" s="63">
         <v>316292.21999999997</v>
       </c>
-      <c r="G35" s="199">
+      <c r="G35" s="63">
         <f t="shared" si="12"/>
         <v>316292.21999999997</v>
       </c>
@@ -5276,7 +5318,7 @@
       </c>
       <c r="J35" s="82">
         <f t="shared" si="5"/>
-        <v>242390.47513200005</v>
+        <v>261820.00000000003</v>
       </c>
       <c r="K35" s="82">
         <f t="shared" si="2"/>
@@ -5288,16 +5330,16 @@
       </c>
       <c r="M35" s="82">
         <f t="shared" si="7"/>
-        <v>64869.702378000009</v>
+        <v>84236.851347999997</v>
       </c>
       <c r="N35" s="82"/>
       <c r="O35" s="76">
         <f t="shared" si="8"/>
-        <v>316292.21999999997</v>
+        <v>355088.22</v>
       </c>
       <c r="P35" s="91">
         <f t="shared" ref="P35:P59" si="13">ROUND(O35*3%,0) + O35</f>
-        <v>325781.21999999997</v>
+        <v>365741.22</v>
       </c>
       <c r="Q35" s="40">
         <f t="shared" si="11"/>
@@ -5324,7 +5366,7 @@
       <c r="F36" s="63">
         <v>210877.23</v>
       </c>
-      <c r="G36" s="199">
+      <c r="G36" s="63">
         <v>217223</v>
       </c>
       <c r="H36" s="75">
@@ -5337,7 +5379,7 @@
       </c>
       <c r="J36" s="82">
         <f t="shared" si="5"/>
-        <v>160939.424784</v>
+        <v>173840</v>
       </c>
       <c r="K36" s="82">
         <f t="shared" si="2"/>
@@ -5349,16 +5391,16 @@
       </c>
       <c r="M36" s="82">
         <f t="shared" si="7"/>
-        <v>43071.381336000006</v>
+        <v>55930.540975999989</v>
       </c>
       <c r="N36" s="82"/>
       <c r="O36" s="76">
         <f t="shared" si="8"/>
-        <v>203662.23</v>
+        <v>229421.23</v>
       </c>
       <c r="P36" s="91">
         <f t="shared" si="13"/>
-        <v>209772.23</v>
+        <v>236304.23</v>
       </c>
       <c r="Q36" s="40">
         <f t="shared" si="11"/>
@@ -5383,7 +5425,7 @@
       <c r="F37" s="63">
         <v>154304.24</v>
       </c>
-      <c r="G37" s="199">
+      <c r="G37" s="63">
         <v>158933.24</v>
       </c>
       <c r="H37" s="75">
@@ -5396,7 +5438,7 @@
       </c>
       <c r="J37" s="82">
         <f t="shared" si="5"/>
-        <v>118251.22369800002</v>
+        <v>127730</v>
       </c>
       <c r="K37" s="82">
         <f t="shared" si="2"/>
@@ -5408,16 +5450,16 @@
       </c>
       <c r="M37" s="82">
         <f t="shared" si="7"/>
-        <v>31646.960067000004</v>
+        <v>41095.306022000004</v>
       </c>
       <c r="N37" s="82"/>
       <c r="O37" s="76">
         <f t="shared" si="8"/>
-        <v>149675.24</v>
+        <v>168602.23999999999</v>
       </c>
       <c r="P37" s="91">
         <f t="shared" si="13"/>
-        <v>154165.24</v>
+        <v>173660.24</v>
       </c>
       <c r="Q37" s="40">
         <f t="shared" si="11"/>
@@ -5442,7 +5484,7 @@
       <c r="F38" s="63">
         <v>53808.25</v>
       </c>
-      <c r="G38" s="199"/>
+      <c r="G38" s="63"/>
       <c r="H38" s="75">
         <f t="shared" si="1"/>
         <v>53808.25</v>
@@ -5453,7 +5495,7 @@
       </c>
       <c r="J38" s="82">
         <f t="shared" si="5"/>
-        <v>21589.435032000001</v>
+        <v>23320</v>
       </c>
       <c r="K38" s="82">
         <f t="shared" si="2"/>
@@ -5465,16 +5507,16 @@
       </c>
       <c r="M38" s="82">
         <f t="shared" si="7"/>
-        <v>5777.8682280000012</v>
+        <v>7502.8774480000002</v>
       </c>
       <c r="N38" s="82"/>
       <c r="O38" s="76">
         <f t="shared" si="8"/>
-        <v>83594.25</v>
+        <v>87050.25</v>
       </c>
       <c r="P38" s="91">
         <f t="shared" si="13"/>
-        <v>86102.25</v>
+        <v>89662.25</v>
       </c>
       <c r="Q38" s="40">
         <f t="shared" si="11"/>
@@ -5502,7 +5544,7 @@
       <c r="F39" s="63">
         <v>35215.26</v>
       </c>
-      <c r="G39" s="199">
+      <c r="G39" s="63">
         <f t="shared" ref="G39:G40" si="15">F39</f>
         <v>35215.26</v>
       </c>
@@ -5516,7 +5558,7 @@
       </c>
       <c r="J39" s="82">
         <f t="shared" si="5"/>
-        <v>26986.793790000003</v>
+        <v>29150.000000000004</v>
       </c>
       <c r="K39" s="82">
         <f t="shared" si="2"/>
@@ -5528,16 +5570,16 @@
       </c>
       <c r="M39" s="82">
         <f t="shared" si="7"/>
-        <v>7222.335285000001</v>
+        <v>9378.5968099999991</v>
       </c>
       <c r="N39" s="82"/>
       <c r="O39" s="76">
         <f t="shared" si="8"/>
-        <v>35215.26</v>
+        <v>39534.26</v>
       </c>
       <c r="P39" s="91">
         <f t="shared" si="13"/>
-        <v>36271.26</v>
+        <v>40720.26</v>
       </c>
       <c r="Q39" s="40">
         <f t="shared" si="11"/>
@@ -5562,7 +5604,7 @@
       <c r="F40" s="63">
         <v>32741.27</v>
       </c>
-      <c r="G40" s="199">
+      <c r="G40" s="63">
         <f t="shared" si="15"/>
         <v>32741.27</v>
       </c>
@@ -5576,7 +5618,7 @@
       </c>
       <c r="J40" s="82">
         <f t="shared" si="5"/>
-        <v>26005.455834000004</v>
+        <v>28090</v>
       </c>
       <c r="K40" s="82">
         <f t="shared" si="2"/>
@@ -5588,16 +5630,16 @@
       </c>
       <c r="M40" s="82">
         <f t="shared" si="7"/>
-        <v>6959.7049110000007</v>
+        <v>9037.5569259999993</v>
       </c>
       <c r="N40" s="82"/>
       <c r="O40" s="76">
         <f t="shared" si="8"/>
-        <v>33934.269999999997</v>
+        <v>38097.269999999997</v>
       </c>
       <c r="P40" s="91">
         <f t="shared" si="13"/>
-        <v>34952.269999999997</v>
+        <v>39240.269999999997</v>
       </c>
       <c r="Q40" s="40">
         <f t="shared" si="11"/>
@@ -5635,7 +5677,7 @@
       </c>
       <c r="J41" s="82">
         <f t="shared" si="5"/>
-        <v>14229.400362</v>
+        <v>15370</v>
       </c>
       <c r="K41" s="82">
         <f t="shared" si="2"/>
@@ -5647,16 +5689,16 @@
       </c>
       <c r="M41" s="82">
         <f t="shared" si="7"/>
-        <v>3808.1404230000003</v>
+        <v>4945.0783179999989</v>
       </c>
       <c r="N41" s="82"/>
       <c r="O41" s="76">
         <f t="shared" si="8"/>
-        <v>37693.279999999999</v>
+        <v>39971.279999999999</v>
       </c>
       <c r="P41" s="91">
         <f t="shared" si="13"/>
-        <v>38824.28</v>
+        <v>41170.28</v>
       </c>
       <c r="Q41" s="40">
         <f t="shared" si="11"/>
@@ -5683,7 +5725,7 @@
       <c r="F42" s="63">
         <v>5122.29</v>
       </c>
-      <c r="G42" s="199">
+      <c r="G42" s="63">
         <f t="shared" ref="G42:G43" si="16">F42</f>
         <v>5122.29</v>
       </c>
@@ -5697,7 +5739,7 @@
       </c>
       <c r="J42" s="82">
         <f t="shared" si="5"/>
-        <v>3925.3518240000003</v>
+        <v>4240</v>
       </c>
       <c r="K42" s="82">
         <f t="shared" si="2"/>
@@ -5709,16 +5751,16 @@
       </c>
       <c r="M42" s="82">
         <f t="shared" si="7"/>
-        <v>1050.5214960000001</v>
+        <v>1364.1595360000001</v>
       </c>
       <c r="N42" s="82"/>
       <c r="O42" s="76">
         <f t="shared" si="8"/>
-        <v>5122.29</v>
+        <v>5750.29</v>
       </c>
       <c r="P42" s="91">
         <f t="shared" si="13"/>
-        <v>5276.29</v>
+        <v>5923.29</v>
       </c>
       <c r="Q42" s="40">
         <f t="shared" si="11"/>
@@ -5743,7 +5785,7 @@
       <c r="F43" s="63">
         <v>4942.3</v>
       </c>
-      <c r="G43" s="199">
+      <c r="G43" s="63">
         <f t="shared" si="16"/>
         <v>4942.3</v>
       </c>
@@ -5757,7 +5799,7 @@
       </c>
       <c r="J43" s="82">
         <f t="shared" si="5"/>
-        <v>3925.3518240000003</v>
+        <v>4240</v>
       </c>
       <c r="K43" s="82">
         <f t="shared" si="2"/>
@@ -5769,16 +5811,16 @@
       </c>
       <c r="M43" s="82">
         <f t="shared" si="7"/>
-        <v>1050.5214960000001</v>
+        <v>1364.1595360000001</v>
       </c>
       <c r="N43" s="82"/>
       <c r="O43" s="76">
         <f t="shared" si="8"/>
-        <v>5122.3</v>
+        <v>5750.3</v>
       </c>
       <c r="P43" s="91">
         <f t="shared" si="13"/>
-        <v>5276.3</v>
+        <v>5923.3</v>
       </c>
       <c r="Q43" s="40">
         <f t="shared" si="11"/>
@@ -5805,7 +5847,7 @@
       <c r="F44" s="63">
         <v>5122.3100000000004</v>
       </c>
-      <c r="G44" s="199">
+      <c r="G44" s="63">
         <f>F44</f>
         <v>5122.3100000000004</v>
       </c>
@@ -5819,7 +5861,7 @@
       </c>
       <c r="J44" s="82">
         <f t="shared" si="5"/>
-        <v>3925.3518240000003</v>
+        <v>4240</v>
       </c>
       <c r="K44" s="82">
         <f t="shared" si="2"/>
@@ -5831,16 +5873,16 @@
       </c>
       <c r="M44" s="82">
         <f t="shared" si="7"/>
-        <v>1050.5214960000001</v>
+        <v>1364.1595360000001</v>
       </c>
       <c r="N44" s="82"/>
       <c r="O44" s="76">
         <f t="shared" si="8"/>
-        <v>5122.3100000000004</v>
+        <v>5750.31</v>
       </c>
       <c r="P44" s="91">
         <f t="shared" si="13"/>
-        <v>5276.31</v>
+        <v>5923.31</v>
       </c>
       <c r="Q44" s="40">
         <f t="shared" si="11"/>
@@ -5868,7 +5910,7 @@
       <c r="F45" s="63">
         <v>5122.32</v>
       </c>
-      <c r="G45" s="199">
+      <c r="G45" s="63">
         <f>F45</f>
         <v>5122.32</v>
       </c>
@@ -5882,7 +5924,7 @@
       </c>
       <c r="J45" s="82">
         <f t="shared" si="5"/>
-        <v>3925.3518240000003</v>
+        <v>4240</v>
       </c>
       <c r="K45" s="82">
         <f t="shared" si="2"/>
@@ -5894,16 +5936,16 @@
       </c>
       <c r="M45" s="82">
         <f t="shared" si="7"/>
-        <v>1050.5214960000001</v>
+        <v>1364.1595360000001</v>
       </c>
       <c r="N45" s="82"/>
       <c r="O45" s="76">
         <f t="shared" si="8"/>
-        <v>5122.32</v>
+        <v>5750.32</v>
       </c>
       <c r="P45" s="91">
         <f t="shared" si="13"/>
-        <v>5276.32</v>
+        <v>5923.32</v>
       </c>
       <c r="Q45" s="40">
         <f t="shared" si="11"/>
@@ -5936,7 +5978,7 @@
       <c r="I46" s="75"/>
       <c r="J46" s="82">
         <f t="shared" si="5"/>
-        <v>3925.3518240000003</v>
+        <v>4240</v>
       </c>
       <c r="K46" s="82">
         <f t="shared" ref="K46:K59" si="17">F$2*E46/100</f>
@@ -5948,16 +5990,16 @@
       </c>
       <c r="M46" s="82">
         <f t="shared" si="7"/>
-        <v>1050.5214960000001</v>
+        <v>1364.1595360000001</v>
       </c>
       <c r="N46" s="82"/>
       <c r="O46" s="76">
         <f t="shared" si="8"/>
-        <v>28556.33</v>
+        <v>29185.33</v>
       </c>
       <c r="P46" s="91">
         <f t="shared" si="13"/>
-        <v>29413.33</v>
+        <v>30061.33</v>
       </c>
       <c r="Q46" s="40">
         <f t="shared" si="11"/>
@@ -5982,7 +6024,7 @@
       <c r="F47" s="63">
         <v>5122.34</v>
       </c>
-      <c r="G47" s="199">
+      <c r="G47" s="63">
         <f>F47</f>
         <v>5122.34</v>
       </c>
@@ -5996,7 +6038,7 @@
       </c>
       <c r="J47" s="82">
         <f t="shared" si="5"/>
-        <v>3925.3518240000003</v>
+        <v>4240</v>
       </c>
       <c r="K47" s="82">
         <f t="shared" si="17"/>
@@ -6008,16 +6050,16 @@
       </c>
       <c r="M47" s="82">
         <f t="shared" si="7"/>
-        <v>1050.5214960000001</v>
+        <v>1364.1595360000001</v>
       </c>
       <c r="N47" s="82"/>
       <c r="O47" s="76">
         <f t="shared" si="8"/>
-        <v>5122.34</v>
+        <v>5750.34</v>
       </c>
       <c r="P47" s="91">
         <f t="shared" si="13"/>
-        <v>5276.34</v>
+        <v>5923.34</v>
       </c>
       <c r="Q47" s="40">
         <f t="shared" si="11"/>
@@ -6053,7 +6095,7 @@
       </c>
       <c r="J48" s="82">
         <f t="shared" si="5"/>
-        <v>4416.020802</v>
+        <v>4770</v>
       </c>
       <c r="K48" s="126">
         <f t="shared" si="17"/>
@@ -6065,16 +6107,16 @@
       </c>
       <c r="M48" s="82">
         <f t="shared" si="7"/>
-        <v>1181.836683</v>
+        <v>1534.679478</v>
       </c>
       <c r="N48" s="126"/>
       <c r="O48" s="76">
         <f t="shared" si="8"/>
-        <v>11698.35</v>
+        <v>12404.35</v>
       </c>
       <c r="P48" s="91">
         <f t="shared" si="13"/>
-        <v>12049.35</v>
+        <v>12776.35</v>
       </c>
       <c r="Q48" s="40">
         <f t="shared" si="11"/>
@@ -6099,7 +6141,7 @@
       <c r="F49" s="63">
         <v>50581.36</v>
       </c>
-      <c r="G49" s="199">
+      <c r="G49" s="63">
         <f>F49</f>
         <v>50581.36</v>
       </c>
@@ -6113,7 +6155,7 @@
       </c>
       <c r="J49" s="82">
         <f t="shared" si="5"/>
-        <v>38762.849262000003</v>
+        <v>41870</v>
       </c>
       <c r="K49" s="82">
         <f t="shared" si="17"/>
@@ -6125,16 +6167,16 @@
       </c>
       <c r="M49" s="82">
         <f t="shared" si="7"/>
-        <v>10373.899773000001</v>
+        <v>13471.075418</v>
       </c>
       <c r="N49" s="82"/>
       <c r="O49" s="76">
         <f t="shared" si="8"/>
-        <v>50581.36</v>
+        <v>56785.36</v>
       </c>
       <c r="P49" s="91">
         <f t="shared" si="13"/>
-        <v>52098.36</v>
+        <v>58489.36</v>
       </c>
       <c r="Q49" s="40">
         <f t="shared" si="11"/>
@@ -6170,7 +6212,7 @@
       </c>
       <c r="J50" s="82">
         <f t="shared" si="5"/>
-        <v>49066.897800000006</v>
+        <v>53000</v>
       </c>
       <c r="K50" s="82">
         <f t="shared" si="17"/>
@@ -6182,16 +6224,16 @@
       </c>
       <c r="M50" s="82">
         <f t="shared" si="7"/>
-        <v>13131.518700000001</v>
+        <v>17051.994200000001</v>
       </c>
       <c r="N50" s="82"/>
       <c r="O50" s="76">
         <f t="shared" si="8"/>
-        <v>377704.37</v>
+        <v>385558.37</v>
       </c>
       <c r="P50" s="91">
         <f t="shared" si="13"/>
-        <v>389035.37</v>
+        <v>397125.37</v>
       </c>
       <c r="Q50" s="40">
         <f t="shared" si="11"/>
@@ -6216,7 +6258,7 @@
       <c r="F51" s="63">
         <v>62106.38</v>
       </c>
-      <c r="G51" s="199">
+      <c r="G51" s="63">
         <f>F51</f>
         <v>62106.38</v>
       </c>
@@ -6230,7 +6272,7 @@
       </c>
       <c r="J51" s="82">
         <f t="shared" si="5"/>
-        <v>47594.890866000002</v>
+        <v>51410</v>
       </c>
       <c r="K51" s="82">
         <f t="shared" si="17"/>
@@ -6242,16 +6284,16 @@
       </c>
       <c r="M51" s="82">
         <f t="shared" si="7"/>
-        <v>12737.573139000002</v>
+        <v>16540.434374</v>
       </c>
       <c r="N51" s="82"/>
       <c r="O51" s="76">
         <f t="shared" si="8"/>
-        <v>62106.38</v>
+        <v>69724.38</v>
       </c>
       <c r="P51" s="91">
         <f t="shared" si="13"/>
-        <v>63969.38</v>
+        <v>71816.38</v>
       </c>
       <c r="Q51" s="40">
         <f t="shared" si="11"/>
@@ -6276,7 +6318,7 @@
       <c r="F52" s="63">
         <v>109279.39</v>
       </c>
-      <c r="G52" s="199">
+      <c r="G52" s="63">
         <v>8160</v>
       </c>
       <c r="H52" s="75">
@@ -6289,7 +6331,7 @@
       </c>
       <c r="J52" s="82">
         <f t="shared" si="5"/>
-        <v>37781.511306</v>
+        <v>40810</v>
       </c>
       <c r="K52" s="82">
         <f t="shared" si="17"/>
@@ -6301,16 +6343,16 @@
       </c>
       <c r="M52" s="82">
         <f t="shared" si="7"/>
-        <v>10111.269399000001</v>
+        <v>13130.035533999999</v>
       </c>
       <c r="N52" s="82"/>
       <c r="O52" s="76">
         <f t="shared" si="8"/>
-        <v>153453.39000000001</v>
+        <v>159501.39000000001</v>
       </c>
       <c r="P52" s="91">
         <f t="shared" si="13"/>
-        <v>158057.39000000001</v>
+        <v>164286.39000000001</v>
       </c>
       <c r="Q52" s="40">
         <f t="shared" si="11"/>
@@ -6340,7 +6382,7 @@
       <c r="F53" s="63">
         <v>49301.4</v>
       </c>
-      <c r="G53" s="199">
+      <c r="G53" s="63">
         <f>F53</f>
         <v>49301.4</v>
       </c>
@@ -6354,7 +6396,7 @@
       </c>
       <c r="J53" s="82">
         <f t="shared" si="5"/>
-        <v>37781.511306</v>
+        <v>40810</v>
       </c>
       <c r="K53" s="82">
         <f t="shared" si="17"/>
@@ -6366,16 +6408,16 @@
       </c>
       <c r="M53" s="82">
         <f t="shared" si="7"/>
-        <v>10111.269399000001</v>
+        <v>13130.035533999999</v>
       </c>
       <c r="N53" s="82"/>
       <c r="O53" s="76">
         <f t="shared" si="8"/>
-        <v>49301.4</v>
+        <v>55348.4</v>
       </c>
       <c r="P53" s="91">
         <f t="shared" si="13"/>
-        <v>50780.4</v>
+        <v>57008.4</v>
       </c>
       <c r="Q53" s="40">
         <f t="shared" si="11"/>
@@ -6415,7 +6457,7 @@
       </c>
       <c r="J54" s="82">
         <f t="shared" si="5"/>
-        <v>39744.187218000006</v>
+        <v>42930</v>
       </c>
       <c r="K54" s="82">
         <f t="shared" si="17"/>
@@ -6427,16 +6469,16 @@
       </c>
       <c r="M54" s="82">
         <f t="shared" si="7"/>
-        <v>10636.530147000001</v>
+        <v>13812.115301999998</v>
       </c>
       <c r="N54" s="82"/>
       <c r="O54" s="76">
         <f t="shared" si="8"/>
-        <v>105280.41</v>
+        <v>111641.41</v>
       </c>
       <c r="P54" s="91">
         <f t="shared" si="13"/>
-        <v>108438.41</v>
+        <v>114990.41</v>
       </c>
       <c r="Q54" s="40">
         <f t="shared" si="11"/>
@@ -6463,7 +6505,7 @@
       <c r="F55" s="63">
         <v>49301.42</v>
       </c>
-      <c r="G55" s="199">
+      <c r="G55" s="63">
         <f>F55</f>
         <v>49301.42</v>
       </c>
@@ -6474,7 +6516,7 @@
       <c r="I55" s="75"/>
       <c r="J55" s="82">
         <f t="shared" si="5"/>
-        <v>37781.511306</v>
+        <v>40810</v>
       </c>
       <c r="K55" s="82">
         <f t="shared" si="17"/>
@@ -6486,16 +6528,16 @@
       </c>
       <c r="M55" s="82">
         <f t="shared" si="7"/>
-        <v>10111.269399000001</v>
+        <v>13130.035533999999</v>
       </c>
       <c r="N55" s="82"/>
       <c r="O55" s="76">
         <f t="shared" si="8"/>
-        <v>49301.42</v>
+        <v>55348.42</v>
       </c>
       <c r="P55" s="91">
         <f t="shared" si="13"/>
-        <v>50780.42</v>
+        <v>57008.42</v>
       </c>
       <c r="Q55" s="40">
         <f t="shared" si="11"/>
@@ -6534,7 +6576,7 @@
       </c>
       <c r="J56" s="82">
         <f t="shared" si="5"/>
-        <v>37781.511306</v>
+        <v>40810</v>
       </c>
       <c r="K56" s="82">
         <f t="shared" si="17"/>
@@ -6546,16 +6588,16 @@
       </c>
       <c r="M56" s="82">
         <f t="shared" si="7"/>
-        <v>10111.269399000001</v>
+        <v>13130.035533999999</v>
       </c>
       <c r="N56" s="82"/>
       <c r="O56" s="76">
         <f t="shared" si="8"/>
-        <v>288756.43</v>
+        <v>294804.43</v>
       </c>
       <c r="P56" s="91">
         <f t="shared" si="13"/>
-        <v>297419.43</v>
+        <v>303648.43</v>
       </c>
       <c r="Q56" s="40">
         <f t="shared" si="11"/>
@@ -6591,7 +6633,7 @@
       </c>
       <c r="J57" s="82">
         <f t="shared" si="5"/>
-        <v>37781.511306</v>
+        <v>40810</v>
       </c>
       <c r="K57" s="82">
         <f t="shared" si="17"/>
@@ -6603,16 +6645,16 @@
       </c>
       <c r="M57" s="82">
         <f t="shared" si="7"/>
-        <v>10111.269399000001</v>
+        <v>13130.035533999999</v>
       </c>
       <c r="N57" s="82"/>
       <c r="O57" s="76">
         <f t="shared" si="8"/>
-        <v>219500.44</v>
+        <v>225547.44</v>
       </c>
       <c r="P57" s="91">
         <f t="shared" si="13"/>
-        <v>226085.44</v>
+        <v>232313.44</v>
       </c>
       <c r="Q57" s="40">
         <f t="shared" si="11"/>
@@ -6639,7 +6681,7 @@
       <c r="F58" s="63">
         <v>49301.45</v>
       </c>
-      <c r="G58" s="199">
+      <c r="G58" s="63">
         <f t="shared" ref="G58" si="18">F58</f>
         <v>49301.45</v>
       </c>
@@ -6653,7 +6695,7 @@
       </c>
       <c r="J58" s="82">
         <f t="shared" si="5"/>
-        <v>37781.511306</v>
+        <v>40810</v>
       </c>
       <c r="K58" s="82">
         <f t="shared" si="17"/>
@@ -6665,16 +6707,16 @@
       </c>
       <c r="M58" s="82">
         <f t="shared" si="7"/>
-        <v>10111.269399000001</v>
+        <v>13130.035533999999</v>
       </c>
       <c r="N58" s="82"/>
       <c r="O58" s="76">
         <f t="shared" si="8"/>
-        <v>49301.45</v>
+        <v>55348.45</v>
       </c>
       <c r="P58" s="91">
         <f t="shared" si="13"/>
-        <v>50780.45</v>
+        <v>57008.45</v>
       </c>
       <c r="Q58" s="40">
         <f t="shared" si="11"/>
@@ -6699,7 +6741,7 @@
       <c r="F59" s="63">
         <v>128840.46</v>
       </c>
-      <c r="G59" s="199">
+      <c r="G59" s="63">
         <f>137000-8160</f>
         <v>128840</v>
       </c>
@@ -6713,7 +6755,7 @@
       </c>
       <c r="J59" s="82">
         <f t="shared" si="5"/>
-        <v>42197.532108000007</v>
+        <v>45580</v>
       </c>
       <c r="K59" s="82">
         <f t="shared" si="17"/>
@@ -6725,16 +6767,16 @@
       </c>
       <c r="M59" s="82">
         <f t="shared" si="7"/>
-        <v>11293.106082000002</v>
+        <v>14664.715011999999</v>
       </c>
       <c r="N59" s="82"/>
       <c r="O59" s="76">
         <f t="shared" si="8"/>
-        <v>55063.46</v>
+        <v>61817.46</v>
       </c>
       <c r="P59" s="91">
         <f t="shared" si="13"/>
-        <v>56715.46</v>
+        <v>63672.46</v>
       </c>
       <c r="Q59" s="40">
         <f t="shared" si="11"/>
@@ -6790,7 +6832,7 @@
       </c>
       <c r="J61" s="89">
         <f t="shared" si="19"/>
-        <v>4906689.7799999956</v>
+        <v>5300000</v>
       </c>
       <c r="K61" s="89">
         <f t="shared" si="19"/>
@@ -6802,16 +6844,16 @@
       </c>
       <c r="M61" s="89">
         <f t="shared" si="19"/>
-        <v>1313151.8700000008</v>
+        <v>1705199.4200000009</v>
       </c>
       <c r="N61" s="90"/>
       <c r="O61" s="95">
         <f>SUM(O14:O60)</f>
-        <v>10257414.809999999</v>
+        <v>11042768.810000001</v>
       </c>
       <c r="P61" s="92">
         <f>SUM(P14:P60)</f>
-        <v>10565140.810000001</v>
+        <v>11374054.810000001</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6820,99 +6862,103 @@
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="64" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="230" t="s">
+      <c r="C64" s="233" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="230"/>
-      <c r="E64" s="230"/>
-      <c r="F64" s="230"/>
-      <c r="G64" s="230"/>
-      <c r="H64" s="230"/>
-      <c r="I64" s="230"/>
-      <c r="J64" s="230"/>
-      <c r="K64" s="230"/>
-      <c r="L64" s="230"/>
-      <c r="M64" s="230"/>
-      <c r="N64" s="230"/>
-      <c r="O64" s="230"/>
+      <c r="D64" s="233"/>
+      <c r="E64" s="233"/>
+      <c r="F64" s="233"/>
+      <c r="G64" s="233"/>
+      <c r="H64" s="233"/>
+      <c r="I64" s="233"/>
+      <c r="J64" s="233"/>
+      <c r="K64" s="233"/>
+      <c r="L64" s="233"/>
+      <c r="M64" s="233"/>
+      <c r="N64" s="233"/>
+      <c r="O64" s="233"/>
     </row>
     <row r="65" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="230"/>
-      <c r="D65" s="230"/>
-      <c r="E65" s="230"/>
-      <c r="F65" s="230"/>
-      <c r="G65" s="230"/>
-      <c r="H65" s="230"/>
-      <c r="I65" s="230"/>
-      <c r="J65" s="230"/>
-      <c r="K65" s="230"/>
-      <c r="L65" s="230"/>
-      <c r="M65" s="230"/>
-      <c r="N65" s="230"/>
-      <c r="O65" s="230"/>
+      <c r="C65" s="233"/>
+      <c r="D65" s="233"/>
+      <c r="E65" s="233"/>
+      <c r="F65" s="233"/>
+      <c r="G65" s="233"/>
+      <c r="H65" s="233"/>
+      <c r="I65" s="233"/>
+      <c r="J65" s="233"/>
+      <c r="K65" s="233"/>
+      <c r="L65" s="233"/>
+      <c r="M65" s="233"/>
+      <c r="N65" s="233"/>
+      <c r="O65" s="233"/>
     </row>
     <row r="66" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="230"/>
-      <c r="D66" s="230"/>
-      <c r="E66" s="230"/>
-      <c r="F66" s="230"/>
-      <c r="G66" s="230"/>
-      <c r="H66" s="230"/>
-      <c r="I66" s="230"/>
-      <c r="J66" s="230"/>
-      <c r="K66" s="230"/>
-      <c r="L66" s="230"/>
-      <c r="M66" s="230"/>
-      <c r="N66" s="230"/>
-      <c r="O66" s="230"/>
+      <c r="C66" s="233"/>
+      <c r="D66" s="233"/>
+      <c r="E66" s="233"/>
+      <c r="F66" s="233"/>
+      <c r="G66" s="233"/>
+      <c r="H66" s="233"/>
+      <c r="I66" s="233"/>
+      <c r="J66" s="233"/>
+      <c r="K66" s="233"/>
+      <c r="L66" s="233"/>
+      <c r="M66" s="233"/>
+      <c r="N66" s="233"/>
+      <c r="O66" s="233"/>
     </row>
     <row r="67" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="230"/>
-      <c r="D67" s="230"/>
-      <c r="E67" s="230"/>
-      <c r="F67" s="230"/>
-      <c r="G67" s="230"/>
-      <c r="H67" s="230"/>
-      <c r="I67" s="230"/>
-      <c r="J67" s="230"/>
-      <c r="K67" s="230"/>
-      <c r="L67" s="230"/>
-      <c r="M67" s="230"/>
-      <c r="N67" s="230"/>
-      <c r="O67" s="230"/>
+      <c r="C67" s="233"/>
+      <c r="D67" s="233"/>
+      <c r="E67" s="233"/>
+      <c r="F67" s="233"/>
+      <c r="G67" s="233"/>
+      <c r="H67" s="233"/>
+      <c r="I67" s="233"/>
+      <c r="J67" s="233"/>
+      <c r="K67" s="233"/>
+      <c r="L67" s="233"/>
+      <c r="M67" s="233"/>
+      <c r="N67" s="233"/>
+      <c r="O67" s="233"/>
     </row>
     <row r="68" spans="3:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="230"/>
-      <c r="D68" s="230"/>
-      <c r="E68" s="230"/>
-      <c r="F68" s="230"/>
-      <c r="G68" s="230"/>
-      <c r="H68" s="230"/>
-      <c r="I68" s="230"/>
-      <c r="J68" s="230"/>
-      <c r="K68" s="230"/>
-      <c r="L68" s="230"/>
-      <c r="M68" s="230"/>
-      <c r="N68" s="230"/>
-      <c r="O68" s="230"/>
+      <c r="C68" s="233"/>
+      <c r="D68" s="233"/>
+      <c r="E68" s="233"/>
+      <c r="F68" s="233"/>
+      <c r="G68" s="233"/>
+      <c r="H68" s="233"/>
+      <c r="I68" s="233"/>
+      <c r="J68" s="233"/>
+      <c r="K68" s="233"/>
+      <c r="L68" s="233"/>
+      <c r="M68" s="233"/>
+      <c r="N68" s="233"/>
+      <c r="O68" s="233"/>
     </row>
     <row r="69" spans="3:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="230"/>
-      <c r="D69" s="230"/>
-      <c r="E69" s="230"/>
-      <c r="F69" s="230"/>
-      <c r="G69" s="230"/>
-      <c r="H69" s="230"/>
-      <c r="I69" s="230"/>
-      <c r="J69" s="230"/>
-      <c r="K69" s="230"/>
-      <c r="L69" s="230"/>
-      <c r="M69" s="230"/>
-      <c r="N69" s="230"/>
-      <c r="O69" s="230"/>
+      <c r="C69" s="233"/>
+      <c r="D69" s="233"/>
+      <c r="E69" s="233"/>
+      <c r="F69" s="233"/>
+      <c r="G69" s="233"/>
+      <c r="H69" s="233"/>
+      <c r="I69" s="233"/>
+      <c r="J69" s="233"/>
+      <c r="K69" s="233"/>
+      <c r="L69" s="233"/>
+      <c r="M69" s="233"/>
+      <c r="N69" s="233"/>
+      <c r="O69" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="J1:P5"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="P12:P13"/>
@@ -6929,10 +6975,6 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="A11:P11"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6997,7 +7039,7 @@
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J6" s="115"/>
       <c r="K6" s="187"/>
@@ -7012,28 +7054,28 @@
       <c r="L7" s="20"/>
     </row>
     <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="265" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
-      <c r="G8" s="266"/>
-      <c r="H8" s="266"/>
-      <c r="I8" s="266"/>
-      <c r="J8" s="267"/>
+      <c r="C8" s="257" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="258"/>
+      <c r="E8" s="258"/>
+      <c r="F8" s="258"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="258"/>
+      <c r="I8" s="258"/>
+      <c r="J8" s="259"/>
       <c r="K8" s="187"/>
       <c r="L8" s="20"/>
     </row>
     <row r="9" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="268"/>
-      <c r="D9" s="269"/>
-      <c r="E9" s="269"/>
-      <c r="F9" s="269"/>
-      <c r="G9" s="269"/>
-      <c r="H9" s="269"/>
-      <c r="I9" s="269"/>
-      <c r="J9" s="270"/>
+      <c r="C9" s="260"/>
+      <c r="D9" s="261"/>
+      <c r="E9" s="261"/>
+      <c r="F9" s="261"/>
+      <c r="G9" s="261"/>
+      <c r="H9" s="261"/>
+      <c r="I9" s="261"/>
+      <c r="J9" s="262"/>
       <c r="K9" s="187"/>
     </row>
     <row r="11" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7089,26 +7131,26 @@
       <c r="J15" s="115"/>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="265" t="s">
-        <v>190</v>
-      </c>
-      <c r="D16" s="266"/>
-      <c r="E16" s="266"/>
-      <c r="F16" s="266"/>
-      <c r="G16" s="266"/>
-      <c r="H16" s="266"/>
-      <c r="I16" s="266"/>
-      <c r="J16" s="267"/>
+      <c r="C16" s="257" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16" s="258"/>
+      <c r="E16" s="258"/>
+      <c r="F16" s="258"/>
+      <c r="G16" s="258"/>
+      <c r="H16" s="258"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="259"/>
     </row>
     <row r="17" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="268"/>
-      <c r="D17" s="269"/>
-      <c r="E17" s="269"/>
-      <c r="F17" s="269"/>
-      <c r="G17" s="269"/>
-      <c r="H17" s="269"/>
-      <c r="I17" s="269"/>
-      <c r="J17" s="270"/>
+      <c r="C17" s="260"/>
+      <c r="D17" s="261"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="261"/>
+      <c r="H17" s="261"/>
+      <c r="I17" s="261"/>
+      <c r="J17" s="262"/>
     </row>
   </sheetData>
   <mergeCells count="2">
